--- a/baseline/data_processing_elements-FRA.xlsx
+++ b/baseline/data_processing_elements-FRA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C7D0A20-92FF-4C51-A291-00663868B573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001A0AB1-13F7-4D7F-8E42-7C06865F247F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCDECE63-0FFC-4822-923F-34FACAF497E3}"/>
   </bookViews>
@@ -96,12 +96,6 @@
   </si>
   <si>
     <t>Unit (abbreviated)</t>
-  </si>
-  <si>
-    <t>`Mlstr_harmo::comment`</t>
-  </si>
-  <si>
-    <t>`Mlstr_harmo::status`</t>
   </si>
   <si>
     <t>Mlstr_harmo::status_detail</t>
@@ -2552,6 +2546,12 @@
 temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
 na.rm = TRUE)) %&gt;%
 mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
+  </si>
+  <si>
+    <t>Mlstr_harmo::comment</t>
+  </si>
+  <si>
+    <t>Mlstr_harmo::status</t>
   </si>
 </sst>
 </file>
@@ -2988,19 +2988,19 @@
         <v>18</v>
       </c>
       <c r="T1" t="s">
+        <v>668</v>
+      </c>
+      <c r="U1" t="s">
+        <v>669</v>
+      </c>
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
-      </c>
-      <c r="W1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
@@ -3008,52 +3008,52 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" t="s">
+      <c r="K2" t="s">
         <v>28</v>
       </c>
-      <c r="I2" t="s">
+      <c r="L2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>30</v>
       </c>
-      <c r="L2" t="s">
+      <c r="O2" t="s">
         <v>31</v>
       </c>
-      <c r="M2" t="s">
+      <c r="P2" t="s">
         <v>32</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>33</v>
       </c>
-      <c r="P2" t="s">
+      <c r="U2" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="V2" t="s">
         <v>35</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>36</v>
       </c>
-      <c r="V2" t="s">
+      <c r="X2" t="s">
         <v>37</v>
-      </c>
-      <c r="W2" t="s">
-        <v>38</v>
-      </c>
-      <c r="X2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
@@ -3061,37 +3061,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
         <v>40</v>
       </c>
-      <c r="D3" t="s">
+      <c r="K3" t="s">
         <v>41</v>
       </c>
-      <c r="E3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="U3" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" t="s">
         <v>42</v>
       </c>
-      <c r="K3" t="s">
+      <c r="W3" t="s">
         <v>43</v>
       </c>
-      <c r="U3" t="s">
-        <v>36</v>
-      </c>
-      <c r="V3" t="s">
-        <v>44</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
       <c r="X3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -3099,37 +3099,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
         <v>46</v>
       </c>
-      <c r="D4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>48</v>
-      </c>
       <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U4" t="s">
+        <v>34</v>
+      </c>
+      <c r="V4" t="s">
+        <v>42</v>
+      </c>
+      <c r="W4" t="s">
         <v>43</v>
       </c>
-      <c r="U4" t="s">
-        <v>36</v>
-      </c>
-      <c r="V4" t="s">
-        <v>44</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
       <c r="X4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -3137,34 +3137,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
         <v>49</v>
       </c>
-      <c r="D5" t="s">
+      <c r="I5" t="s">
         <v>50</v>
       </c>
-      <c r="E5" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" t="s">
-        <v>52</v>
-      </c>
       <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="U5" t="s">
+        <v>34</v>
+      </c>
+      <c r="V5" t="s">
+        <v>42</v>
+      </c>
+      <c r="W5" t="s">
         <v>43</v>
-      </c>
-      <c r="U5" t="s">
-        <v>36</v>
-      </c>
-      <c r="V5" t="s">
-        <v>44</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -3175,58 +3175,58 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>54</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" t="s">
         <v>55</v>
       </c>
-      <c r="F6" t="s">
+      <c r="I6" t="s">
         <v>56</v>
       </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
         <v>57</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>58</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>59</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
         <v>60</v>
       </c>
-      <c r="M6" t="s">
+      <c r="P6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" t="s">
+        <v>33</v>
+      </c>
+      <c r="U6" t="s">
+        <v>34</v>
+      </c>
+      <c r="V6" t="s">
+        <v>42</v>
+      </c>
+      <c r="W6" t="s">
         <v>61</v>
       </c>
-      <c r="N6" t="s">
+      <c r="X6" t="s">
         <v>62</v>
-      </c>
-      <c r="P6" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R6" t="s">
-        <v>35</v>
-      </c>
-      <c r="U6" t="s">
-        <v>36</v>
-      </c>
-      <c r="V6" t="s">
-        <v>44</v>
-      </c>
-      <c r="W6" t="s">
-        <v>63</v>
-      </c>
-      <c r="X6" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="30" x14ac:dyDescent="0.25">
@@ -3234,55 +3234,55 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" t="s">
         <v>65</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E7" t="s">
+      <c r="K7" t="s">
         <v>67</v>
       </c>
-      <c r="F7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J7" s="1" t="s">
+      <c r="L7" t="s">
         <v>68</v>
       </c>
-      <c r="K7" t="s">
+      <c r="M7" t="s">
         <v>69</v>
       </c>
-      <c r="L7" t="s">
+      <c r="N7" t="s">
         <v>70</v>
       </c>
-      <c r="M7" t="s">
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>32</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="N7" t="s">
+      <c r="U7" t="s">
+        <v>34</v>
+      </c>
+      <c r="V7" t="s">
+        <v>42</v>
+      </c>
+      <c r="W7" t="s">
+        <v>61</v>
+      </c>
+      <c r="X7" t="s">
         <v>72</v>
-      </c>
-      <c r="P7" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>34</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="U7" t="s">
-        <v>36</v>
-      </c>
-      <c r="V7" t="s">
-        <v>44</v>
-      </c>
-      <c r="W7" t="s">
-        <v>63</v>
-      </c>
-      <c r="X7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
@@ -3290,58 +3290,58 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" t="s">
         <v>75</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" t="s">
         <v>76</v>
       </c>
-      <c r="E8" t="s">
+      <c r="I8" t="s">
         <v>77</v>
       </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="K8" t="s">
         <v>78</v>
       </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
         <v>79</v>
       </c>
-      <c r="K8" t="s">
+      <c r="M8" t="s">
         <v>80</v>
       </c>
-      <c r="L8" t="s">
+      <c r="N8" t="s">
         <v>81</v>
       </c>
-      <c r="M8" t="s">
+      <c r="P8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q8" t="s">
         <v>82</v>
       </c>
-      <c r="N8" t="s">
+      <c r="S8" t="s">
+        <v>76</v>
+      </c>
+      <c r="U8" t="s">
+        <v>34</v>
+      </c>
+      <c r="V8" t="s">
+        <v>35</v>
+      </c>
+      <c r="W8" t="s">
         <v>83</v>
       </c>
-      <c r="P8" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>84</v>
-      </c>
-      <c r="S8" t="s">
-        <v>78</v>
-      </c>
-      <c r="U8" t="s">
-        <v>36</v>
-      </c>
-      <c r="V8" t="s">
-        <v>37</v>
-      </c>
-      <c r="W8" t="s">
-        <v>85</v>
-      </c>
       <c r="X8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="345" x14ac:dyDescent="0.25">
@@ -3349,40 +3349,40 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" t="s">
         <v>86</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" t="s">
         <v>87</v>
       </c>
-      <c r="E9" t="s">
+      <c r="J9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" t="s">
-        <v>89</v>
-      </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" t="s">
+        <v>41</v>
+      </c>
+      <c r="U9" t="s">
+        <v>89</v>
+      </c>
+      <c r="V9" t="s">
         <v>90</v>
       </c>
-      <c r="K9" t="s">
-        <v>43</v>
-      </c>
-      <c r="U9" t="s">
-        <v>91</v>
-      </c>
-      <c r="V9" t="s">
-        <v>92</v>
-      </c>
       <c r="W9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="30" x14ac:dyDescent="0.25">
@@ -3390,40 +3390,40 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" t="s">
         <v>93</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" t="s">
-        <v>89</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="K10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3431,40 +3431,40 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D11" t="s">
-        <v>98</v>
-      </c>
-      <c r="E11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="J11" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3472,40 +3472,40 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3513,40 +3513,40 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3554,40 +3554,40 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" t="s">
-        <v>105</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="J14" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3595,40 +3595,40 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="J15" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3636,40 +3636,40 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V16" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3677,40 +3677,40 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3718,40 +3718,40 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K18" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3759,40 +3759,40 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3800,61 +3800,61 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" t="s">
         <v>118</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E20" t="s">
+      <c r="J20" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-      <c r="I20" s="1" t="s">
+      <c r="K20" t="s">
         <v>121</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="L20" t="s">
         <v>122</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
         <v>123</v>
       </c>
-      <c r="L20" t="s">
+      <c r="N20" t="s">
         <v>124</v>
       </c>
-      <c r="M20" t="s">
+      <c r="P20" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="N20" t="s">
+      <c r="T20" t="s">
         <v>126</v>
       </c>
-      <c r="P20" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q20" t="s">
+      <c r="U20" t="s">
         <v>34</v>
       </c>
-      <c r="R20" s="1" t="s">
+      <c r="V20" t="s">
+        <v>42</v>
+      </c>
+      <c r="W20" t="s">
         <v>127</v>
       </c>
-      <c r="T20" t="s">
+      <c r="X20" t="s">
         <v>128</v>
-      </c>
-      <c r="U20" t="s">
-        <v>36</v>
-      </c>
-      <c r="V20" t="s">
-        <v>44</v>
-      </c>
-      <c r="W20" t="s">
-        <v>129</v>
-      </c>
-      <c r="X20" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3862,61 +3862,61 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" t="s">
         <v>131</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" t="s">
         <v>132</v>
       </c>
-      <c r="E21" t="s">
+      <c r="J21" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
+        <v>121</v>
+      </c>
+      <c r="L21" t="s">
+        <v>122</v>
+      </c>
+      <c r="M21" t="s">
+        <v>123</v>
+      </c>
+      <c r="N21" t="s">
+        <v>124</v>
+      </c>
+      <c r="P21" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>32</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="T21" t="s">
         <v>134</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="U21" t="s">
+        <v>34</v>
+      </c>
+      <c r="V21" t="s">
+        <v>42</v>
+      </c>
+      <c r="W21" t="s">
+        <v>127</v>
+      </c>
+      <c r="X21" t="s">
         <v>135</v>
-      </c>
-      <c r="K21" t="s">
-        <v>123</v>
-      </c>
-      <c r="L21" t="s">
-        <v>124</v>
-      </c>
-      <c r="M21" t="s">
-        <v>125</v>
-      </c>
-      <c r="N21" t="s">
-        <v>126</v>
-      </c>
-      <c r="P21" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>34</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="T21" t="s">
-        <v>136</v>
-      </c>
-      <c r="U21" t="s">
-        <v>36</v>
-      </c>
-      <c r="V21" t="s">
-        <v>44</v>
-      </c>
-      <c r="W21" t="s">
-        <v>129</v>
-      </c>
-      <c r="X21" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -3924,37 +3924,37 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" t="s">
+        <v>137</v>
+      </c>
+      <c r="F22" t="s">
         <v>138</v>
       </c>
-      <c r="D22" t="s">
+      <c r="G22" t="s">
         <v>139</v>
       </c>
-      <c r="E22" t="s">
-        <v>139</v>
-      </c>
-      <c r="F22" t="s">
-        <v>140</v>
-      </c>
-      <c r="G22" t="s">
-        <v>141</v>
-      </c>
       <c r="K22" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V22" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -3962,52 +3962,52 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" t="s">
         <v>142</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" t="s">
         <v>143</v>
       </c>
-      <c r="E23" t="s">
+      <c r="L23" t="s">
         <v>144</v>
       </c>
-      <c r="F23" t="s">
-        <v>28</v>
-      </c>
-      <c r="K23" t="s">
+      <c r="M23" t="s">
         <v>145</v>
       </c>
-      <c r="L23" t="s">
+      <c r="N23" t="s">
         <v>146</v>
       </c>
-      <c r="M23" t="s">
+      <c r="P23" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="N23" t="s">
+      <c r="U23" t="s">
+        <v>34</v>
+      </c>
+      <c r="V23" t="s">
+        <v>42</v>
+      </c>
+      <c r="W23" t="s">
+        <v>127</v>
+      </c>
+      <c r="X23" t="s">
         <v>148</v>
-      </c>
-      <c r="P23" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>34</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="U23" t="s">
-        <v>36</v>
-      </c>
-      <c r="V23" t="s">
-        <v>44</v>
-      </c>
-      <c r="W23" t="s">
-        <v>129</v>
-      </c>
-      <c r="X23" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -4015,58 +4015,58 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" t="s">
         <v>151</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" t="s">
         <v>152</v>
       </c>
-      <c r="E24" t="s">
+      <c r="J24" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="K24" t="s">
+        <v>121</v>
+      </c>
+      <c r="L24" t="s">
+        <v>122</v>
+      </c>
+      <c r="M24" t="s">
+        <v>123</v>
+      </c>
+      <c r="N24" t="s">
+        <v>124</v>
+      </c>
+      <c r="P24" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="U24" t="s">
+        <v>34</v>
+      </c>
+      <c r="V24" t="s">
+        <v>42</v>
+      </c>
+      <c r="W24" t="s">
+        <v>127</v>
+      </c>
+      <c r="X24" t="s">
         <v>154</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="K24" t="s">
-        <v>123</v>
-      </c>
-      <c r="L24" t="s">
-        <v>124</v>
-      </c>
-      <c r="M24" t="s">
-        <v>125</v>
-      </c>
-      <c r="N24" t="s">
-        <v>126</v>
-      </c>
-      <c r="P24" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>34</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="U24" t="s">
-        <v>36</v>
-      </c>
-      <c r="V24" t="s">
-        <v>44</v>
-      </c>
-      <c r="W24" t="s">
-        <v>129</v>
-      </c>
-      <c r="X24" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="180" x14ac:dyDescent="0.25">
@@ -4074,55 +4074,55 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F25" t="s">
+        <v>49</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D25" t="s">
+      <c r="K25" t="s">
         <v>158</v>
       </c>
-      <c r="E25" t="s">
-        <v>158</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J25" s="1" t="s">
+      <c r="L25" t="s">
         <v>159</v>
       </c>
-      <c r="K25" t="s">
+      <c r="M25" t="s">
         <v>160</v>
       </c>
-      <c r="L25" t="s">
+      <c r="N25" t="s">
         <v>161</v>
       </c>
-      <c r="M25" t="s">
+      <c r="P25" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="N25" t="s">
+      <c r="U25" t="s">
+        <v>34</v>
+      </c>
+      <c r="V25" t="s">
+        <v>42</v>
+      </c>
+      <c r="W25" t="s">
+        <v>127</v>
+      </c>
+      <c r="X25" t="s">
         <v>163</v>
-      </c>
-      <c r="P25" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>34</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="U25" t="s">
-        <v>36</v>
-      </c>
-      <c r="V25" t="s">
-        <v>44</v>
-      </c>
-      <c r="W25" t="s">
-        <v>129</v>
-      </c>
-      <c r="X25" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="30" x14ac:dyDescent="0.25">
@@ -4130,40 +4130,40 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" t="s">
+        <v>165</v>
+      </c>
+      <c r="E26" t="s">
         <v>166</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" t="s">
         <v>167</v>
       </c>
-      <c r="E26" t="s">
+      <c r="J26" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F26" t="s">
-        <v>51</v>
-      </c>
-      <c r="I26" t="s">
-        <v>169</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="K26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
@@ -4171,61 +4171,61 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
+        <v>169</v>
+      </c>
+      <c r="D27" t="s">
+        <v>170</v>
+      </c>
+      <c r="E27" t="s">
+        <v>170</v>
+      </c>
+      <c r="F27" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27" t="s">
         <v>171</v>
       </c>
-      <c r="D27" t="s">
+      <c r="I27" t="s">
         <v>172</v>
       </c>
-      <c r="E27" t="s">
-        <v>172</v>
-      </c>
-      <c r="F27" t="s">
-        <v>140</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="K27" t="s">
         <v>173</v>
       </c>
-      <c r="I27" t="s">
+      <c r="L27" t="s">
         <v>174</v>
       </c>
-      <c r="K27" t="s">
+      <c r="M27" t="s">
         <v>175</v>
       </c>
-      <c r="L27" t="s">
+      <c r="N27" t="s">
         <v>176</v>
       </c>
-      <c r="M27" t="s">
+      <c r="P27" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>82</v>
+      </c>
+      <c r="R27" t="s">
         <v>177</v>
       </c>
-      <c r="N27" t="s">
-        <v>178</v>
-      </c>
-      <c r="P27" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>84</v>
-      </c>
-      <c r="R27" t="s">
-        <v>179</v>
-      </c>
       <c r="S27" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="U27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="90" x14ac:dyDescent="0.25">
@@ -4233,37 +4233,37 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" t="s">
+        <v>179</v>
+      </c>
+      <c r="E28" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" t="s">
+        <v>49</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D28" t="s">
+      <c r="K28" t="s">
+        <v>173</v>
+      </c>
+      <c r="U28" t="s">
+        <v>34</v>
+      </c>
+      <c r="V28" t="s">
+        <v>42</v>
+      </c>
+      <c r="W28" t="s">
+        <v>61</v>
+      </c>
+      <c r="X28" t="s">
         <v>181</v>
-      </c>
-      <c r="E28" t="s">
-        <v>181</v>
-      </c>
-      <c r="F28" t="s">
-        <v>51</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="K28" t="s">
-        <v>175</v>
-      </c>
-      <c r="U28" t="s">
-        <v>36</v>
-      </c>
-      <c r="V28" t="s">
-        <v>44</v>
-      </c>
-      <c r="W28" t="s">
-        <v>63</v>
-      </c>
-      <c r="X28" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -4271,61 +4271,61 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" t="s">
+        <v>183</v>
+      </c>
+      <c r="F29" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" t="s">
         <v>184</v>
       </c>
-      <c r="D29" t="s">
+      <c r="I29" t="s">
+        <v>172</v>
+      </c>
+      <c r="K29" t="s">
         <v>185</v>
       </c>
-      <c r="E29" t="s">
-        <v>185</v>
-      </c>
-      <c r="F29" t="s">
-        <v>140</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="L29" t="s">
         <v>186</v>
       </c>
-      <c r="I29" t="s">
-        <v>174</v>
-      </c>
-      <c r="K29" t="s">
+      <c r="M29" t="s">
         <v>187</v>
       </c>
-      <c r="L29" t="s">
+      <c r="N29" t="s">
         <v>188</v>
       </c>
-      <c r="M29" t="s">
-        <v>189</v>
-      </c>
-      <c r="N29" t="s">
-        <v>190</v>
-      </c>
       <c r="P29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R29" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="S29" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="U29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V29" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X29" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="90" x14ac:dyDescent="0.25">
@@ -4333,37 +4333,37 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" t="s">
+        <v>190</v>
+      </c>
+      <c r="E30" t="s">
+        <v>190</v>
+      </c>
+      <c r="F30" t="s">
+        <v>49</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K30" t="s">
+        <v>185</v>
+      </c>
+      <c r="U30" t="s">
+        <v>34</v>
+      </c>
+      <c r="V30" t="s">
+        <v>42</v>
+      </c>
+      <c r="W30" t="s">
+        <v>61</v>
+      </c>
+      <c r="X30" t="s">
         <v>191</v>
-      </c>
-      <c r="D30" t="s">
-        <v>192</v>
-      </c>
-      <c r="E30" t="s">
-        <v>192</v>
-      </c>
-      <c r="F30" t="s">
-        <v>51</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="K30" t="s">
-        <v>187</v>
-      </c>
-      <c r="U30" t="s">
-        <v>36</v>
-      </c>
-      <c r="V30" t="s">
-        <v>44</v>
-      </c>
-      <c r="W30" t="s">
-        <v>63</v>
-      </c>
-      <c r="X30" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
@@ -4371,61 +4371,61 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" t="s">
+        <v>193</v>
+      </c>
+      <c r="E31" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" t="s">
+        <v>138</v>
+      </c>
+      <c r="G31" t="s">
         <v>194</v>
       </c>
-      <c r="D31" t="s">
+      <c r="I31" t="s">
         <v>195</v>
       </c>
-      <c r="E31" t="s">
-        <v>195</v>
-      </c>
-      <c r="F31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="K31" t="s">
         <v>196</v>
       </c>
-      <c r="I31" t="s">
+      <c r="L31" t="s">
         <v>197</v>
       </c>
-      <c r="K31" t="s">
+      <c r="M31" t="s">
         <v>198</v>
       </c>
-      <c r="L31" t="s">
+      <c r="N31" t="s">
         <v>199</v>
       </c>
-      <c r="M31" t="s">
-        <v>200</v>
-      </c>
-      <c r="N31" t="s">
-        <v>201</v>
-      </c>
       <c r="P31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R31" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="S31" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="U31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
@@ -4433,61 +4433,61 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" t="s">
+        <v>201</v>
+      </c>
+      <c r="E32" t="s">
+        <v>201</v>
+      </c>
+      <c r="F32" t="s">
+        <v>138</v>
+      </c>
+      <c r="G32" t="s">
+        <v>171</v>
+      </c>
+      <c r="I32" t="s">
+        <v>172</v>
+      </c>
+      <c r="K32" t="s">
         <v>202</v>
       </c>
-      <c r="D32" t="s">
+      <c r="L32" t="s">
         <v>203</v>
       </c>
-      <c r="E32" t="s">
-        <v>203</v>
-      </c>
-      <c r="F32" t="s">
-        <v>140</v>
-      </c>
-      <c r="G32" t="s">
-        <v>173</v>
-      </c>
-      <c r="I32" t="s">
-        <v>174</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="M32" t="s">
         <v>204</v>
       </c>
-      <c r="L32" t="s">
+      <c r="N32" t="s">
         <v>205</v>
       </c>
-      <c r="M32" t="s">
+      <c r="P32" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>82</v>
+      </c>
+      <c r="R32" t="s">
+        <v>177</v>
+      </c>
+      <c r="T32" t="s">
         <v>206</v>
       </c>
-      <c r="N32" t="s">
-        <v>207</v>
-      </c>
-      <c r="P32" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>84</v>
-      </c>
-      <c r="R32" t="s">
-        <v>179</v>
-      </c>
-      <c r="T32" t="s">
-        <v>208</v>
-      </c>
       <c r="U32" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V32" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W32" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X32" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="90" x14ac:dyDescent="0.25">
@@ -4495,55 +4495,55 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C33" t="s">
+        <v>207</v>
+      </c>
+      <c r="D33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E33" t="s">
+        <v>208</v>
+      </c>
+      <c r="F33" t="s">
+        <v>49</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K33" t="s">
+        <v>202</v>
+      </c>
+      <c r="L33" t="s">
+        <v>203</v>
+      </c>
+      <c r="M33" t="s">
+        <v>204</v>
+      </c>
+      <c r="N33" t="s">
+        <v>205</v>
+      </c>
+      <c r="P33" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>82</v>
+      </c>
+      <c r="R33" t="s">
+        <v>177</v>
+      </c>
+      <c r="U33" t="s">
+        <v>34</v>
+      </c>
+      <c r="V33" t="s">
+        <v>42</v>
+      </c>
+      <c r="W33" t="s">
+        <v>61</v>
+      </c>
+      <c r="X33" t="s">
         <v>209</v>
-      </c>
-      <c r="D33" t="s">
-        <v>210</v>
-      </c>
-      <c r="E33" t="s">
-        <v>210</v>
-      </c>
-      <c r="F33" t="s">
-        <v>51</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="K33" t="s">
-        <v>204</v>
-      </c>
-      <c r="L33" t="s">
-        <v>205</v>
-      </c>
-      <c r="M33" t="s">
-        <v>206</v>
-      </c>
-      <c r="N33" t="s">
-        <v>207</v>
-      </c>
-      <c r="P33" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>84</v>
-      </c>
-      <c r="R33" t="s">
-        <v>179</v>
-      </c>
-      <c r="U33" t="s">
-        <v>36</v>
-      </c>
-      <c r="V33" t="s">
-        <v>44</v>
-      </c>
-      <c r="W33" t="s">
-        <v>63</v>
-      </c>
-      <c r="X33" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -4551,55 +4551,55 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" t="s">
+        <v>211</v>
+      </c>
+      <c r="E34" t="s">
+        <v>211</v>
+      </c>
+      <c r="F34" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34" t="s">
         <v>212</v>
       </c>
-      <c r="D34" t="s">
+      <c r="K34" t="s">
         <v>213</v>
       </c>
-      <c r="E34" t="s">
-        <v>213</v>
-      </c>
-      <c r="F34" t="s">
-        <v>140</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="L34" t="s">
         <v>214</v>
       </c>
-      <c r="K34" t="s">
+      <c r="M34" t="s">
         <v>215</v>
       </c>
-      <c r="L34" t="s">
+      <c r="N34" t="s">
         <v>216</v>
       </c>
-      <c r="M34" t="s">
-        <v>217</v>
-      </c>
-      <c r="N34" t="s">
-        <v>218</v>
-      </c>
       <c r="Q34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R34" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="S34" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="U34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X34" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
@@ -4607,37 +4607,37 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
+        <v>217</v>
+      </c>
+      <c r="D35" t="s">
+        <v>218</v>
+      </c>
+      <c r="E35" t="s">
+        <v>218</v>
+      </c>
+      <c r="F35" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" t="s">
+        <v>213</v>
+      </c>
+      <c r="L35" t="s">
+        <v>214</v>
+      </c>
+      <c r="U35" t="s">
+        <v>34</v>
+      </c>
+      <c r="V35" t="s">
+        <v>42</v>
+      </c>
+      <c r="W35" t="s">
+        <v>61</v>
+      </c>
+      <c r="X35" t="s">
         <v>219</v>
-      </c>
-      <c r="D35" t="s">
-        <v>220</v>
-      </c>
-      <c r="E35" t="s">
-        <v>220</v>
-      </c>
-      <c r="F35" t="s">
-        <v>28</v>
-      </c>
-      <c r="K35" t="s">
-        <v>215</v>
-      </c>
-      <c r="L35" t="s">
-        <v>216</v>
-      </c>
-      <c r="U35" t="s">
-        <v>36</v>
-      </c>
-      <c r="V35" t="s">
-        <v>44</v>
-      </c>
-      <c r="W35" t="s">
-        <v>63</v>
-      </c>
-      <c r="X35" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -4645,58 +4645,58 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
+        <v>220</v>
+      </c>
+      <c r="D36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E36" t="s">
         <v>222</v>
       </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
+        <v>138</v>
+      </c>
+      <c r="G36" t="s">
         <v>223</v>
       </c>
-      <c r="E36" t="s">
+      <c r="I36" t="s">
         <v>224</v>
       </c>
-      <c r="F36" t="s">
-        <v>140</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="K36" t="s">
         <v>225</v>
       </c>
-      <c r="I36" t="s">
+      <c r="L36" t="s">
         <v>226</v>
       </c>
-      <c r="K36" t="s">
+      <c r="N36" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="L36" t="s">
+      <c r="Q36" t="s">
+        <v>82</v>
+      </c>
+      <c r="R36" t="s">
+        <v>177</v>
+      </c>
+      <c r="S36" t="s">
+        <v>223</v>
+      </c>
+      <c r="T36" t="s">
         <v>228</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="U36" t="s">
+        <v>34</v>
+      </c>
+      <c r="V36" t="s">
+        <v>42</v>
+      </c>
+      <c r="W36" t="s">
+        <v>61</v>
+      </c>
+      <c r="X36" t="s">
         <v>229</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>84</v>
-      </c>
-      <c r="R36" t="s">
-        <v>179</v>
-      </c>
-      <c r="S36" t="s">
-        <v>225</v>
-      </c>
-      <c r="T36" t="s">
-        <v>230</v>
-      </c>
-      <c r="U36" t="s">
-        <v>36</v>
-      </c>
-      <c r="V36" t="s">
-        <v>44</v>
-      </c>
-      <c r="W36" t="s">
-        <v>63</v>
-      </c>
-      <c r="X36" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -4704,58 +4704,58 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
+        <v>230</v>
+      </c>
+      <c r="D37" t="s">
+        <v>231</v>
+      </c>
+      <c r="E37" t="s">
         <v>232</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
+        <v>138</v>
+      </c>
+      <c r="G37" t="s">
+        <v>223</v>
+      </c>
+      <c r="I37" t="s">
+        <v>224</v>
+      </c>
+      <c r="K37" t="s">
         <v>233</v>
       </c>
-      <c r="E37" t="s">
+      <c r="L37" t="s">
         <v>234</v>
       </c>
-      <c r="F37" t="s">
-        <v>140</v>
-      </c>
-      <c r="G37" t="s">
-        <v>225</v>
-      </c>
-      <c r="I37" t="s">
-        <v>226</v>
-      </c>
-      <c r="K37" t="s">
+      <c r="N37" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="L37" t="s">
+      <c r="Q37" t="s">
+        <v>82</v>
+      </c>
+      <c r="R37" t="s">
+        <v>177</v>
+      </c>
+      <c r="S37" t="s">
+        <v>223</v>
+      </c>
+      <c r="T37" t="s">
+        <v>228</v>
+      </c>
+      <c r="U37" t="s">
+        <v>34</v>
+      </c>
+      <c r="V37" t="s">
+        <v>42</v>
+      </c>
+      <c r="W37" t="s">
+        <v>61</v>
+      </c>
+      <c r="X37" t="s">
         <v>236</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>84</v>
-      </c>
-      <c r="R37" t="s">
-        <v>179</v>
-      </c>
-      <c r="S37" t="s">
-        <v>225</v>
-      </c>
-      <c r="T37" t="s">
-        <v>230</v>
-      </c>
-      <c r="U37" t="s">
-        <v>36</v>
-      </c>
-      <c r="V37" t="s">
-        <v>44</v>
-      </c>
-      <c r="W37" t="s">
-        <v>63</v>
-      </c>
-      <c r="X37" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
@@ -4763,40 +4763,40 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
+        <v>237</v>
+      </c>
+      <c r="D38" t="s">
+        <v>238</v>
+      </c>
+      <c r="E38" t="s">
+        <v>238</v>
+      </c>
+      <c r="F38" t="s">
+        <v>138</v>
+      </c>
+      <c r="G38" t="s">
         <v>239</v>
       </c>
-      <c r="D38" t="s">
-        <v>240</v>
-      </c>
-      <c r="E38" t="s">
-        <v>240</v>
-      </c>
-      <c r="F38" t="s">
-        <v>140</v>
-      </c>
-      <c r="G38" t="s">
-        <v>241</v>
-      </c>
       <c r="I38" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K38" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V38" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -4804,64 +4804,64 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C39" t="s">
+        <v>240</v>
+      </c>
+      <c r="D39" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" t="s">
+        <v>241</v>
+      </c>
+      <c r="F39" t="s">
+        <v>138</v>
+      </c>
+      <c r="G39" t="s">
         <v>242</v>
       </c>
-      <c r="D39" t="s">
+      <c r="I39" t="s">
         <v>243</v>
       </c>
-      <c r="E39" t="s">
-        <v>243</v>
-      </c>
-      <c r="F39" t="s">
-        <v>140</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="K39" t="s">
         <v>244</v>
       </c>
-      <c r="I39" t="s">
+      <c r="L39" t="s">
         <v>245</v>
       </c>
-      <c r="K39" t="s">
+      <c r="M39" t="s">
         <v>246</v>
       </c>
-      <c r="L39" t="s">
+      <c r="N39" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="M39" t="s">
+      <c r="P39" t="s">
         <v>248</v>
       </c>
-      <c r="N39" s="1" t="s">
+      <c r="Q39" t="s">
+        <v>82</v>
+      </c>
+      <c r="R39" t="s">
+        <v>177</v>
+      </c>
+      <c r="S39" t="s">
         <v>249</v>
       </c>
-      <c r="P39" t="s">
+      <c r="T39" t="s">
         <v>250</v>
       </c>
-      <c r="Q39" t="s">
-        <v>84</v>
-      </c>
-      <c r="R39" t="s">
-        <v>179</v>
-      </c>
-      <c r="S39" t="s">
-        <v>251</v>
-      </c>
-      <c r="T39" t="s">
-        <v>252</v>
-      </c>
       <c r="U39" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V39" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X39" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="90" x14ac:dyDescent="0.25">
@@ -4869,34 +4869,34 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
+        <v>251</v>
+      </c>
+      <c r="D40" t="s">
+        <v>252</v>
+      </c>
+      <c r="E40" t="s">
+        <v>252</v>
+      </c>
+      <c r="F40" t="s">
+        <v>49</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D40" t="s">
-        <v>254</v>
-      </c>
-      <c r="E40" t="s">
-        <v>254</v>
-      </c>
-      <c r="F40" t="s">
-        <v>51</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="K40" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40" t="s">
+        <v>34</v>
+      </c>
+      <c r="V40" t="s">
+        <v>35</v>
+      </c>
+      <c r="W40" t="s">
         <v>43</v>
-      </c>
-      <c r="U40" t="s">
-        <v>36</v>
-      </c>
-      <c r="V40" t="s">
-        <v>37</v>
-      </c>
-      <c r="W40" t="s">
-        <v>45</v>
       </c>
       <c r="X40">
         <v>2</v>
@@ -4907,37 +4907,37 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C41" t="s">
+        <v>254</v>
+      </c>
+      <c r="D41" t="s">
+        <v>255</v>
+      </c>
+      <c r="E41" t="s">
+        <v>255</v>
+      </c>
+      <c r="F41" t="s">
+        <v>138</v>
+      </c>
+      <c r="G41" t="s">
         <v>256</v>
       </c>
-      <c r="D41" t="s">
-        <v>257</v>
-      </c>
-      <c r="E41" t="s">
-        <v>257</v>
-      </c>
-      <c r="F41" t="s">
-        <v>140</v>
-      </c>
-      <c r="G41" t="s">
-        <v>258</v>
-      </c>
       <c r="K41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U41" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V41" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W41" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X41" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
@@ -4945,37 +4945,37 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C42" t="s">
+        <v>257</v>
+      </c>
+      <c r="D42" t="s">
+        <v>258</v>
+      </c>
+      <c r="E42" t="s">
+        <v>258</v>
+      </c>
+      <c r="F42" t="s">
+        <v>138</v>
+      </c>
+      <c r="G42" t="s">
         <v>259</v>
       </c>
-      <c r="D42" t="s">
-        <v>260</v>
-      </c>
-      <c r="E42" t="s">
-        <v>260</v>
-      </c>
-      <c r="F42" t="s">
-        <v>140</v>
-      </c>
-      <c r="G42" t="s">
-        <v>261</v>
-      </c>
       <c r="K42" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V42" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X42" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
@@ -4983,46 +4983,46 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
+        <v>260</v>
+      </c>
+      <c r="D43" t="s">
+        <v>261</v>
+      </c>
+      <c r="E43" t="s">
+        <v>261</v>
+      </c>
+      <c r="F43" t="s">
+        <v>138</v>
+      </c>
+      <c r="G43" t="s">
         <v>262</v>
       </c>
-      <c r="D43" t="s">
+      <c r="K43" t="s">
         <v>263</v>
       </c>
-      <c r="E43" t="s">
-        <v>263</v>
-      </c>
-      <c r="F43" t="s">
-        <v>140</v>
-      </c>
-      <c r="G43" t="s">
+      <c r="L43" t="s">
+        <v>261</v>
+      </c>
+      <c r="M43" t="s">
         <v>264</v>
       </c>
-      <c r="K43" t="s">
+      <c r="N43" t="s">
         <v>265</v>
       </c>
-      <c r="L43" t="s">
-        <v>263</v>
-      </c>
-      <c r="M43" t="s">
-        <v>266</v>
-      </c>
-      <c r="N43" t="s">
-        <v>267</v>
-      </c>
       <c r="U43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V43" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
@@ -5030,46 +5030,46 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
+        <v>266</v>
+      </c>
+      <c r="D44" t="s">
+        <v>267</v>
+      </c>
+      <c r="E44" t="s">
+        <v>267</v>
+      </c>
+      <c r="F44" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" t="s">
+        <v>262</v>
+      </c>
+      <c r="K44" t="s">
         <v>268</v>
       </c>
-      <c r="D44" t="s">
+      <c r="L44" t="s">
+        <v>267</v>
+      </c>
+      <c r="M44" t="s">
         <v>269</v>
       </c>
-      <c r="E44" t="s">
-        <v>269</v>
-      </c>
-      <c r="F44" t="s">
-        <v>140</v>
-      </c>
-      <c r="G44" t="s">
-        <v>264</v>
-      </c>
-      <c r="K44" t="s">
+      <c r="N44" t="s">
         <v>270</v>
       </c>
-      <c r="L44" t="s">
-        <v>269</v>
-      </c>
-      <c r="M44" t="s">
-        <v>271</v>
-      </c>
-      <c r="N44" t="s">
-        <v>272</v>
-      </c>
       <c r="U44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W44" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X44" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
@@ -5077,46 +5077,46 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
+        <v>271</v>
+      </c>
+      <c r="D45" t="s">
+        <v>272</v>
+      </c>
+      <c r="E45" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" t="s">
+        <v>262</v>
+      </c>
+      <c r="K45" t="s">
         <v>273</v>
       </c>
-      <c r="D45" t="s">
+      <c r="L45" t="s">
+        <v>272</v>
+      </c>
+      <c r="M45" t="s">
         <v>274</v>
       </c>
-      <c r="E45" t="s">
-        <v>274</v>
-      </c>
-      <c r="F45" t="s">
-        <v>140</v>
-      </c>
-      <c r="G45" t="s">
-        <v>264</v>
-      </c>
-      <c r="K45" t="s">
+      <c r="N45" t="s">
         <v>275</v>
       </c>
-      <c r="L45" t="s">
-        <v>274</v>
-      </c>
-      <c r="M45" t="s">
-        <v>276</v>
-      </c>
-      <c r="N45" t="s">
-        <v>277</v>
-      </c>
       <c r="U45" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X45" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="180" x14ac:dyDescent="0.25">
@@ -5124,43 +5124,43 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
+        <v>276</v>
+      </c>
+      <c r="D46" t="s">
+        <v>277</v>
+      </c>
+      <c r="E46" t="s">
+        <v>277</v>
+      </c>
+      <c r="F46" t="s">
+        <v>138</v>
+      </c>
+      <c r="G46" t="s">
+        <v>262</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D46" t="s">
+      <c r="K46" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E46" t="s">
-        <v>279</v>
-      </c>
-      <c r="F46" t="s">
-        <v>140</v>
-      </c>
-      <c r="G46" t="s">
-        <v>264</v>
-      </c>
-      <c r="I46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="U46" t="s">
+        <v>34</v>
+      </c>
+      <c r="V46" t="s">
+        <v>42</v>
+      </c>
+      <c r="W46" t="s">
+        <v>61</v>
+      </c>
+      <c r="X46" t="s">
         <v>281</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="U46" t="s">
-        <v>36</v>
-      </c>
-      <c r="V46" t="s">
-        <v>44</v>
-      </c>
-      <c r="W46" t="s">
-        <v>63</v>
-      </c>
-      <c r="X46" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
@@ -5168,46 +5168,46 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
+        <v>282</v>
+      </c>
+      <c r="D47" t="s">
+        <v>283</v>
+      </c>
+      <c r="E47" t="s">
+        <v>283</v>
+      </c>
+      <c r="F47" t="s">
+        <v>138</v>
+      </c>
+      <c r="G47" t="s">
+        <v>262</v>
+      </c>
+      <c r="K47" t="s">
         <v>284</v>
       </c>
-      <c r="D47" t="s">
+      <c r="L47" t="s">
+        <v>283</v>
+      </c>
+      <c r="M47" t="s">
         <v>285</v>
       </c>
-      <c r="E47" t="s">
-        <v>285</v>
-      </c>
-      <c r="F47" t="s">
-        <v>140</v>
-      </c>
-      <c r="G47" t="s">
-        <v>264</v>
-      </c>
-      <c r="K47" t="s">
+      <c r="N47" t="s">
         <v>286</v>
       </c>
-      <c r="L47" t="s">
-        <v>285</v>
-      </c>
-      <c r="M47" t="s">
-        <v>287</v>
-      </c>
-      <c r="N47" t="s">
-        <v>288</v>
-      </c>
       <c r="U47" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V47" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W47" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X47" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
@@ -5215,46 +5215,46 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
+        <v>287</v>
+      </c>
+      <c r="D48" t="s">
+        <v>288</v>
+      </c>
+      <c r="E48" t="s">
+        <v>288</v>
+      </c>
+      <c r="F48" t="s">
+        <v>138</v>
+      </c>
+      <c r="G48" t="s">
         <v>289</v>
       </c>
-      <c r="D48" t="s">
+      <c r="K48" t="s">
         <v>290</v>
       </c>
-      <c r="E48" t="s">
-        <v>290</v>
-      </c>
-      <c r="F48" t="s">
-        <v>140</v>
-      </c>
-      <c r="G48" t="s">
+      <c r="L48" t="s">
+        <v>288</v>
+      </c>
+      <c r="M48" t="s">
         <v>291</v>
       </c>
-      <c r="K48" t="s">
+      <c r="N48" t="s">
         <v>292</v>
       </c>
-      <c r="L48" t="s">
-        <v>290</v>
-      </c>
-      <c r="M48" t="s">
-        <v>293</v>
-      </c>
-      <c r="N48" t="s">
-        <v>294</v>
-      </c>
       <c r="U48" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V48" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X48" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -5262,40 +5262,40 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
+        <v>293</v>
+      </c>
+      <c r="D49" t="s">
+        <v>294</v>
+      </c>
+      <c r="E49" t="s">
         <v>295</v>
       </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
+        <v>138</v>
+      </c>
+      <c r="G49" t="s">
         <v>296</v>
       </c>
-      <c r="E49" t="s">
+      <c r="I49" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="F49" t="s">
-        <v>140</v>
-      </c>
-      <c r="G49" t="s">
-        <v>298</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="K49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U49" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V49" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W49" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X49" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:24" ht="75" x14ac:dyDescent="0.25">
@@ -5303,40 +5303,40 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C50" t="s">
+        <v>298</v>
+      </c>
+      <c r="D50" t="s">
+        <v>299</v>
+      </c>
+      <c r="E50" t="s">
         <v>300</v>
       </c>
-      <c r="D50" t="s">
+      <c r="F50" t="s">
+        <v>49</v>
+      </c>
+      <c r="I50" t="s">
         <v>301</v>
       </c>
-      <c r="E50" t="s">
+      <c r="J50" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="F50" t="s">
-        <v>51</v>
-      </c>
-      <c r="I50" t="s">
-        <v>303</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="K50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U50" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V50" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W50" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X50" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
@@ -5344,40 +5344,40 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
+        <v>303</v>
+      </c>
+      <c r="D51" t="s">
+        <v>304</v>
+      </c>
+      <c r="E51" t="s">
+        <v>304</v>
+      </c>
+      <c r="F51" t="s">
+        <v>138</v>
+      </c>
+      <c r="G51" t="s">
+        <v>296</v>
+      </c>
+      <c r="I51" t="s">
         <v>305</v>
       </c>
-      <c r="D51" t="s">
-        <v>306</v>
-      </c>
-      <c r="E51" t="s">
-        <v>306</v>
-      </c>
-      <c r="F51" t="s">
-        <v>140</v>
-      </c>
-      <c r="G51" t="s">
-        <v>298</v>
-      </c>
-      <c r="I51" t="s">
-        <v>307</v>
-      </c>
       <c r="K51" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U51" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V51" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W51" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X51" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:24" ht="120" x14ac:dyDescent="0.25">
@@ -5385,55 +5385,55 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C52" t="s">
+        <v>306</v>
+      </c>
+      <c r="D52" t="s">
+        <v>307</v>
+      </c>
+      <c r="E52" t="s">
         <v>308</v>
       </c>
-      <c r="D52" t="s">
+      <c r="F52" t="s">
+        <v>49</v>
+      </c>
+      <c r="I52" t="s">
         <v>309</v>
       </c>
-      <c r="E52" t="s">
+      <c r="J52" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K52" t="s">
         <v>310</v>
       </c>
-      <c r="F52" t="s">
-        <v>51</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="L52" t="s">
         <v>311</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="K52" t="s">
+      <c r="N52" t="s">
         <v>312</v>
       </c>
-      <c r="L52" t="s">
+      <c r="Q52" t="s">
+        <v>32</v>
+      </c>
+      <c r="R52" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="N52" t="s">
+      <c r="T52" t="s">
         <v>314</v>
       </c>
-      <c r="Q52" t="s">
-        <v>34</v>
-      </c>
-      <c r="R52" s="1" t="s">
+      <c r="U52" t="s">
+        <v>89</v>
+      </c>
+      <c r="V52" t="s">
         <v>315</v>
       </c>
-      <c r="T52" t="s">
-        <v>316</v>
-      </c>
-      <c r="U52" t="s">
-        <v>91</v>
-      </c>
-      <c r="V52" t="s">
-        <v>317</v>
-      </c>
       <c r="W52" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X52" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.25">
@@ -5441,37 +5441,37 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C53" t="s">
+        <v>316</v>
+      </c>
+      <c r="D53" t="s">
+        <v>317</v>
+      </c>
+      <c r="E53" t="s">
+        <v>317</v>
+      </c>
+      <c r="F53" t="s">
+        <v>138</v>
+      </c>
+      <c r="G53" t="s">
         <v>318</v>
       </c>
-      <c r="D53" t="s">
-        <v>319</v>
-      </c>
-      <c r="E53" t="s">
-        <v>319</v>
-      </c>
-      <c r="F53" t="s">
-        <v>140</v>
-      </c>
-      <c r="G53" t="s">
-        <v>320</v>
-      </c>
       <c r="K53" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U53" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V53" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W53" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X53" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -5479,52 +5479,52 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C54" t="s">
+        <v>319</v>
+      </c>
+      <c r="D54" t="s">
+        <v>320</v>
+      </c>
+      <c r="E54" t="s">
+        <v>320</v>
+      </c>
+      <c r="F54" t="s">
+        <v>138</v>
+      </c>
+      <c r="G54" t="s">
         <v>321</v>
       </c>
-      <c r="D54" t="s">
+      <c r="I54" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="E54" t="s">
-        <v>322</v>
-      </c>
-      <c r="F54" t="s">
-        <v>140</v>
-      </c>
-      <c r="G54" t="s">
+      <c r="K54" t="s">
         <v>323</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="L54" t="s">
         <v>324</v>
       </c>
-      <c r="K54" t="s">
+      <c r="M54" t="s">
         <v>325</v>
       </c>
-      <c r="L54" t="s">
+      <c r="N54" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="M54" t="s">
-        <v>327</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="Q54" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U54" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V54" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:24" ht="120" x14ac:dyDescent="0.25">
@@ -5532,37 +5532,37 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C55" t="s">
+        <v>327</v>
+      </c>
+      <c r="D55" t="s">
+        <v>328</v>
+      </c>
+      <c r="E55" t="s">
+        <v>328</v>
+      </c>
+      <c r="F55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J55" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D55" t="s">
-        <v>330</v>
-      </c>
-      <c r="E55" t="s">
-        <v>330</v>
-      </c>
-      <c r="F55" t="s">
-        <v>51</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="K55" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U55" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V55" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W55" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X55" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:24" ht="270" x14ac:dyDescent="0.25">
@@ -5570,58 +5570,58 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C56" t="s">
+        <v>330</v>
+      </c>
+      <c r="D56" t="s">
+        <v>331</v>
+      </c>
+      <c r="E56" t="s">
+        <v>331</v>
+      </c>
+      <c r="F56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D56" t="s">
+      <c r="J56" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="E56" t="s">
-        <v>333</v>
-      </c>
-      <c r="F56" t="s">
-        <v>51</v>
-      </c>
-      <c r="I56" s="1" t="s">
+      <c r="K56" t="s">
         <v>334</v>
       </c>
-      <c r="J56" s="1" t="s">
+      <c r="L56" t="s">
         <v>335</v>
       </c>
-      <c r="K56" t="s">
+      <c r="M56" t="s">
         <v>336</v>
       </c>
-      <c r="L56" t="s">
+      <c r="N56" t="s">
         <v>337</v>
       </c>
-      <c r="M56" t="s">
+      <c r="P56" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>32</v>
+      </c>
+      <c r="R56" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="N56" t="s">
+      <c r="U56" t="s">
+        <v>34</v>
+      </c>
+      <c r="V56" t="s">
+        <v>35</v>
+      </c>
+      <c r="W56" t="s">
+        <v>127</v>
+      </c>
+      <c r="X56" t="s">
         <v>339</v>
-      </c>
-      <c r="P56" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>34</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="U56" t="s">
-        <v>36</v>
-      </c>
-      <c r="V56" t="s">
-        <v>37</v>
-      </c>
-      <c r="W56" t="s">
-        <v>129</v>
-      </c>
-      <c r="X56" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="105" x14ac:dyDescent="0.25">
@@ -5629,58 +5629,58 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C57" t="s">
+        <v>340</v>
+      </c>
+      <c r="D57" t="s">
+        <v>341</v>
+      </c>
+      <c r="E57" t="s">
+        <v>341</v>
+      </c>
+      <c r="F57" t="s">
+        <v>49</v>
+      </c>
+      <c r="I57" t="s">
         <v>342</v>
       </c>
-      <c r="D57" t="s">
+      <c r="J57" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="E57" t="s">
-        <v>343</v>
-      </c>
-      <c r="F57" t="s">
-        <v>51</v>
-      </c>
-      <c r="I57" t="s">
-        <v>344</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="K57" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L57" t="s">
+        <v>335</v>
+      </c>
+      <c r="M57" t="s">
+        <v>336</v>
+      </c>
+      <c r="N57" t="s">
         <v>337</v>
       </c>
-      <c r="M57" t="s">
+      <c r="P57" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>32</v>
+      </c>
+      <c r="R57" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="N57" t="s">
-        <v>339</v>
-      </c>
-      <c r="P57" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>34</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="U57" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V57" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W57" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X57" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:24" ht="240" x14ac:dyDescent="0.25">
@@ -5688,40 +5688,40 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C58" t="s">
+        <v>344</v>
+      </c>
+      <c r="D58" t="s">
+        <v>345</v>
+      </c>
+      <c r="E58" t="s">
+        <v>345</v>
+      </c>
+      <c r="F58" t="s">
+        <v>138</v>
+      </c>
+      <c r="G58" t="s">
         <v>346</v>
       </c>
-      <c r="D58" t="s">
+      <c r="I58" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="E58" t="s">
-        <v>347</v>
-      </c>
-      <c r="F58" t="s">
-        <v>140</v>
-      </c>
-      <c r="G58" t="s">
-        <v>348</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="K58" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U58" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V58" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="W58" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X58" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="1:24" ht="225" x14ac:dyDescent="0.25">
@@ -5729,58 +5729,58 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C59" t="s">
+        <v>348</v>
+      </c>
+      <c r="D59" t="s">
+        <v>349</v>
+      </c>
+      <c r="E59" t="s">
+        <v>349</v>
+      </c>
+      <c r="F59" t="s">
+        <v>138</v>
+      </c>
+      <c r="G59" t="s">
+        <v>139</v>
+      </c>
+      <c r="K59" t="s">
         <v>350</v>
       </c>
-      <c r="D59" t="s">
+      <c r="L59" t="s">
         <v>351</v>
       </c>
-      <c r="E59" t="s">
-        <v>351</v>
-      </c>
-      <c r="F59" t="s">
-        <v>140</v>
-      </c>
-      <c r="G59" t="s">
-        <v>141</v>
-      </c>
-      <c r="K59" t="s">
+      <c r="M59" t="s">
         <v>352</v>
       </c>
-      <c r="L59" t="s">
+      <c r="N59" t="s">
         <v>353</v>
       </c>
-      <c r="M59" t="s">
+      <c r="P59" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="N59" t="s">
+      <c r="Q59" t="s">
+        <v>32</v>
+      </c>
+      <c r="R59" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="P59" s="1" t="s">
+      <c r="T59" t="s">
         <v>356</v>
       </c>
-      <c r="Q59" t="s">
+      <c r="U59" t="s">
         <v>34</v>
       </c>
-      <c r="R59" s="1" t="s">
+      <c r="V59" t="s">
+        <v>42</v>
+      </c>
+      <c r="W59" t="s">
+        <v>127</v>
+      </c>
+      <c r="X59" t="s">
         <v>357</v>
-      </c>
-      <c r="T59" t="s">
-        <v>358</v>
-      </c>
-      <c r="U59" t="s">
-        <v>36</v>
-      </c>
-      <c r="V59" t="s">
-        <v>44</v>
-      </c>
-      <c r="W59" t="s">
-        <v>129</v>
-      </c>
-      <c r="X59" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="60" spans="1:24" ht="390" x14ac:dyDescent="0.25">
@@ -5788,58 +5788,58 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C60" t="s">
+        <v>358</v>
+      </c>
+      <c r="D60" t="s">
+        <v>359</v>
+      </c>
+      <c r="E60" t="s">
+        <v>359</v>
+      </c>
+      <c r="F60" t="s">
+        <v>49</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D60" t="s">
+      <c r="J60" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="E60" t="s">
-        <v>361</v>
-      </c>
-      <c r="F60" t="s">
-        <v>51</v>
-      </c>
-      <c r="I60" s="1" t="s">
+      <c r="K60" t="s">
+        <v>350</v>
+      </c>
+      <c r="L60" t="s">
+        <v>351</v>
+      </c>
+      <c r="M60" t="s">
+        <v>352</v>
+      </c>
+      <c r="N60" t="s">
+        <v>353</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>32</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="U60" t="s">
+        <v>34</v>
+      </c>
+      <c r="V60" t="s">
+        <v>35</v>
+      </c>
+      <c r="W60" t="s">
+        <v>127</v>
+      </c>
+      <c r="X60" t="s">
         <v>362</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="K60" t="s">
-        <v>352</v>
-      </c>
-      <c r="L60" t="s">
-        <v>353</v>
-      </c>
-      <c r="M60" t="s">
-        <v>354</v>
-      </c>
-      <c r="N60" t="s">
-        <v>355</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>34</v>
-      </c>
-      <c r="R60" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="U60" t="s">
-        <v>36</v>
-      </c>
-      <c r="V60" t="s">
-        <v>37</v>
-      </c>
-      <c r="W60" t="s">
-        <v>129</v>
-      </c>
-      <c r="X60" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="61" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -5847,58 +5847,58 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C61" t="s">
+        <v>363</v>
+      </c>
+      <c r="D61" t="s">
+        <v>364</v>
+      </c>
+      <c r="E61" t="s">
+        <v>364</v>
+      </c>
+      <c r="F61" t="s">
+        <v>49</v>
+      </c>
+      <c r="I61" t="s">
         <v>365</v>
       </c>
-      <c r="D61" t="s">
+      <c r="J61" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E61" t="s">
-        <v>366</v>
-      </c>
-      <c r="F61" t="s">
-        <v>51</v>
-      </c>
-      <c r="I61" t="s">
+      <c r="K61" t="s">
         <v>367</v>
       </c>
-      <c r="J61" s="1" t="s">
+      <c r="L61" t="s">
         <v>368</v>
       </c>
-      <c r="K61" t="s">
+      <c r="M61" t="s">
         <v>369</v>
       </c>
-      <c r="L61" t="s">
+      <c r="N61" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="M61" t="s">
+      <c r="P61" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>32</v>
+      </c>
+      <c r="R61" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="N61" s="1" t="s">
+      <c r="U61" t="s">
+        <v>34</v>
+      </c>
+      <c r="V61" t="s">
+        <v>42</v>
+      </c>
+      <c r="W61" t="s">
+        <v>127</v>
+      </c>
+      <c r="X61" t="s">
         <v>372</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>34</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="U61" t="s">
-        <v>36</v>
-      </c>
-      <c r="V61" t="s">
-        <v>44</v>
-      </c>
-      <c r="W61" t="s">
-        <v>129</v>
-      </c>
-      <c r="X61" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="62" spans="1:24" ht="150" x14ac:dyDescent="0.25">
@@ -5906,40 +5906,40 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C62" t="s">
+        <v>373</v>
+      </c>
+      <c r="D62" t="s">
+        <v>374</v>
+      </c>
+      <c r="E62" t="s">
+        <v>374</v>
+      </c>
+      <c r="F62" t="s">
+        <v>49</v>
+      </c>
+      <c r="I62" t="s">
         <v>375</v>
       </c>
-      <c r="D62" t="s">
+      <c r="J62" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="E62" t="s">
-        <v>376</v>
-      </c>
-      <c r="F62" t="s">
-        <v>51</v>
-      </c>
-      <c r="I62" t="s">
-        <v>377</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="K62" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U62" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V62" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W62" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X62" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:24" ht="150" x14ac:dyDescent="0.25">
@@ -5947,58 +5947,58 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C63" t="s">
+        <v>377</v>
+      </c>
+      <c r="D63" t="s">
+        <v>378</v>
+      </c>
+      <c r="E63" t="s">
+        <v>378</v>
+      </c>
+      <c r="F63" t="s">
+        <v>49</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="K63" t="s">
         <v>379</v>
       </c>
-      <c r="D63" t="s">
+      <c r="L63" t="s">
         <v>380</v>
       </c>
-      <c r="E63" t="s">
-        <v>380</v>
-      </c>
-      <c r="F63" t="s">
-        <v>51</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="K63" t="s">
+      <c r="M63" t="s">
         <v>381</v>
       </c>
-      <c r="L63" t="s">
+      <c r="N63" t="s">
         <v>382</v>
       </c>
-      <c r="M63" t="s">
+      <c r="P63" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="N63" t="s">
+      <c r="Q63" t="s">
+        <v>32</v>
+      </c>
+      <c r="R63" t="s">
         <v>384</v>
       </c>
-      <c r="P63" s="1" t="s">
+      <c r="T63" t="s">
         <v>385</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="U63" t="s">
         <v>34</v>
       </c>
-      <c r="R63" t="s">
+      <c r="V63" t="s">
+        <v>42</v>
+      </c>
+      <c r="W63" t="s">
+        <v>127</v>
+      </c>
+      <c r="X63" t="s">
         <v>386</v>
-      </c>
-      <c r="T63" t="s">
-        <v>387</v>
-      </c>
-      <c r="U63" t="s">
-        <v>36</v>
-      </c>
-      <c r="V63" t="s">
-        <v>44</v>
-      </c>
-      <c r="W63" t="s">
-        <v>129</v>
-      </c>
-      <c r="X63" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="64" spans="1:24" ht="150" x14ac:dyDescent="0.25">
@@ -6006,37 +6006,37 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C64" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E64" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K64" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U64" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V64" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W64" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X64" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6044,58 +6044,58 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C65" t="s">
+        <v>389</v>
+      </c>
+      <c r="D65" t="s">
+        <v>390</v>
+      </c>
+      <c r="E65" t="s">
         <v>391</v>
       </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
+        <v>49</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="E65" t="s">
+      <c r="K65" t="s">
         <v>393</v>
       </c>
-      <c r="F65" t="s">
-        <v>51</v>
-      </c>
-      <c r="J65" s="1" t="s">
+      <c r="L65" t="s">
         <v>394</v>
       </c>
-      <c r="K65" t="s">
+      <c r="M65" t="s">
         <v>395</v>
       </c>
-      <c r="L65" t="s">
+      <c r="N65" t="s">
         <v>396</v>
       </c>
-      <c r="M65" t="s">
+      <c r="P65" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>32</v>
+      </c>
+      <c r="R65" t="s">
+        <v>384</v>
+      </c>
+      <c r="T65" t="s">
         <v>397</v>
       </c>
-      <c r="N65" t="s">
+      <c r="U65" t="s">
+        <v>34</v>
+      </c>
+      <c r="V65" t="s">
+        <v>35</v>
+      </c>
+      <c r="W65" t="s">
+        <v>61</v>
+      </c>
+      <c r="X65" t="s">
         <v>398</v>
-      </c>
-      <c r="P65" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q65" t="s">
-        <v>34</v>
-      </c>
-      <c r="R65" t="s">
-        <v>386</v>
-      </c>
-      <c r="T65" t="s">
-        <v>399</v>
-      </c>
-      <c r="U65" t="s">
-        <v>36</v>
-      </c>
-      <c r="V65" t="s">
-        <v>37</v>
-      </c>
-      <c r="W65" t="s">
-        <v>63</v>
-      </c>
-      <c r="X65" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:24" ht="135" x14ac:dyDescent="0.25">
@@ -6103,40 +6103,40 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C66" t="s">
+        <v>399</v>
+      </c>
+      <c r="D66" t="s">
+        <v>400</v>
+      </c>
+      <c r="E66" t="s">
         <v>401</v>
       </c>
-      <c r="D66" t="s">
+      <c r="F66" t="s">
+        <v>49</v>
+      </c>
+      <c r="I66" t="s">
+        <v>375</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E66" t="s">
-        <v>403</v>
-      </c>
-      <c r="F66" t="s">
-        <v>51</v>
-      </c>
-      <c r="I66" t="s">
-        <v>377</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="K66" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V66" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:24" ht="135" x14ac:dyDescent="0.25">
@@ -6144,40 +6144,40 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C67" t="s">
+        <v>403</v>
+      </c>
+      <c r="D67" t="s">
+        <v>404</v>
+      </c>
+      <c r="E67" t="s">
         <v>405</v>
       </c>
-      <c r="D67" t="s">
-        <v>406</v>
-      </c>
-      <c r="E67" t="s">
-        <v>407</v>
-      </c>
       <c r="F67" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I67" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K67" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U67" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V67" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W67" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X67" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6185,61 +6185,61 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C68" t="s">
+        <v>406</v>
+      </c>
+      <c r="D68" t="s">
+        <v>407</v>
+      </c>
+      <c r="E68" t="s">
         <v>408</v>
       </c>
-      <c r="D68" t="s">
+      <c r="F68" t="s">
+        <v>138</v>
+      </c>
+      <c r="G68" t="s">
+        <v>139</v>
+      </c>
+      <c r="I68" t="s">
+        <v>375</v>
+      </c>
+      <c r="K68" t="s">
         <v>409</v>
       </c>
-      <c r="E68" t="s">
+      <c r="L68" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="F68" t="s">
-        <v>140</v>
-      </c>
-      <c r="G68" t="s">
-        <v>141</v>
-      </c>
-      <c r="I68" t="s">
-        <v>377</v>
-      </c>
-      <c r="K68" t="s">
+      <c r="M68" t="s">
         <v>411</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="N68" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="M68" t="s">
+      <c r="P68" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>32</v>
+      </c>
+      <c r="R68" t="s">
+        <v>384</v>
+      </c>
+      <c r="T68" t="s">
         <v>413</v>
       </c>
-      <c r="N68" s="1" t="s">
+      <c r="U68" t="s">
+        <v>34</v>
+      </c>
+      <c r="V68" t="s">
+        <v>42</v>
+      </c>
+      <c r="W68" t="s">
+        <v>61</v>
+      </c>
+      <c r="X68" t="s">
         <v>414</v>
-      </c>
-      <c r="P68" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>34</v>
-      </c>
-      <c r="R68" t="s">
-        <v>386</v>
-      </c>
-      <c r="T68" t="s">
-        <v>415</v>
-      </c>
-      <c r="U68" t="s">
-        <v>36</v>
-      </c>
-      <c r="V68" t="s">
-        <v>44</v>
-      </c>
-      <c r="W68" t="s">
-        <v>63</v>
-      </c>
-      <c r="X68" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="69" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6247,58 +6247,58 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C69" t="s">
+        <v>415</v>
+      </c>
+      <c r="D69" t="s">
+        <v>416</v>
+      </c>
+      <c r="E69" t="s">
         <v>417</v>
       </c>
-      <c r="D69" t="s">
+      <c r="F69" t="s">
+        <v>49</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="E69" t="s">
+      <c r="K69" t="s">
+        <v>409</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="M69" t="s">
+        <v>411</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="P69" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>32</v>
+      </c>
+      <c r="R69" t="s">
+        <v>384</v>
+      </c>
+      <c r="T69" t="s">
         <v>419</v>
       </c>
-      <c r="F69" t="s">
-        <v>51</v>
-      </c>
-      <c r="J69" s="1" t="s">
+      <c r="U69" t="s">
+        <v>34</v>
+      </c>
+      <c r="V69" t="s">
+        <v>42</v>
+      </c>
+      <c r="W69" t="s">
         <v>420</v>
       </c>
-      <c r="K69" t="s">
-        <v>411</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="M69" t="s">
-        <v>413</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="P69" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>34</v>
-      </c>
-      <c r="R69" t="s">
-        <v>386</v>
-      </c>
-      <c r="T69" t="s">
+      <c r="X69" s="1" t="s">
         <v>421</v>
-      </c>
-      <c r="U69" t="s">
-        <v>36</v>
-      </c>
-      <c r="V69" t="s">
-        <v>44</v>
-      </c>
-      <c r="W69" t="s">
-        <v>422</v>
-      </c>
-      <c r="X69" s="1" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="70" spans="1:24" ht="390" x14ac:dyDescent="0.25">
@@ -6306,61 +6306,61 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C70" t="s">
+        <v>422</v>
+      </c>
+      <c r="D70" t="s">
+        <v>423</v>
+      </c>
+      <c r="E70" t="s">
+        <v>423</v>
+      </c>
+      <c r="F70" t="s">
+        <v>49</v>
+      </c>
+      <c r="I70" t="s">
         <v>424</v>
       </c>
-      <c r="D70" t="s">
+      <c r="J70" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="E70" t="s">
-        <v>425</v>
-      </c>
-      <c r="F70" t="s">
-        <v>51</v>
-      </c>
-      <c r="I70" t="s">
+      <c r="K70" t="s">
         <v>426</v>
       </c>
-      <c r="J70" s="1" t="s">
+      <c r="L70" t="s">
         <v>427</v>
       </c>
-      <c r="K70" t="s">
+      <c r="M70" t="s">
         <v>428</v>
       </c>
-      <c r="L70" t="s">
+      <c r="N70" t="s">
         <v>429</v>
       </c>
-      <c r="M70" t="s">
+      <c r="P70" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>32</v>
+      </c>
+      <c r="R70" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="N70" t="s">
+      <c r="T70" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="P70" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q70" t="s">
-        <v>34</v>
-      </c>
-      <c r="R70" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="T70" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="U70" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V70" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="W70" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X70" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6368,61 +6368,61 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C71" t="s">
+        <v>432</v>
+      </c>
+      <c r="D71" t="s">
+        <v>433</v>
+      </c>
+      <c r="E71" t="s">
         <v>434</v>
       </c>
-      <c r="D71" t="s">
+      <c r="F71" t="s">
+        <v>49</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="E71" t="s">
+      <c r="J71" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="F71" t="s">
-        <v>51</v>
-      </c>
-      <c r="I71" s="1" t="s">
+      <c r="K71" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="J71" s="1" t="s">
+      <c r="L71" t="s">
         <v>438</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="M71" t="s">
         <v>439</v>
       </c>
-      <c r="L71" t="s">
+      <c r="N71" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="M71" t="s">
+      <c r="P71" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="N71" s="1" t="s">
+      <c r="Q71" t="s">
+        <v>32</v>
+      </c>
+      <c r="R71" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="P71" s="1" t="s">
+      <c r="T71" t="s">
         <v>443</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="U71" t="s">
         <v>34</v>
       </c>
-      <c r="R71" s="1" t="s">
+      <c r="V71" t="s">
+        <v>42</v>
+      </c>
+      <c r="W71" t="s">
+        <v>420</v>
+      </c>
+      <c r="X71" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="T71" t="s">
-        <v>445</v>
-      </c>
-      <c r="U71" t="s">
-        <v>36</v>
-      </c>
-      <c r="V71" t="s">
-        <v>44</v>
-      </c>
-      <c r="W71" t="s">
-        <v>422</v>
-      </c>
-      <c r="X71" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="72" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6430,61 +6430,61 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C72" t="s">
+        <v>445</v>
+      </c>
+      <c r="D72" t="s">
+        <v>446</v>
+      </c>
+      <c r="E72" t="s">
+        <v>446</v>
+      </c>
+      <c r="F72" t="s">
+        <v>49</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="D72" t="s">
+      <c r="J72" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K72" t="s">
         <v>448</v>
       </c>
-      <c r="E72" t="s">
-        <v>448</v>
-      </c>
-      <c r="F72" t="s">
-        <v>51</v>
-      </c>
-      <c r="I72" s="1" t="s">
+      <c r="L72" t="s">
         <v>449</v>
       </c>
-      <c r="J72" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K72" t="s">
+      <c r="M72" t="s">
+        <v>439</v>
+      </c>
+      <c r="N72" t="s">
         <v>450</v>
       </c>
-      <c r="L72" t="s">
+      <c r="P72" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>32</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="T72" t="s">
         <v>451</v>
       </c>
-      <c r="M72" t="s">
-        <v>441</v>
-      </c>
-      <c r="N72" t="s">
+      <c r="U72" t="s">
+        <v>34</v>
+      </c>
+      <c r="V72" t="s">
+        <v>42</v>
+      </c>
+      <c r="W72" t="s">
+        <v>127</v>
+      </c>
+      <c r="X72" t="s">
         <v>452</v>
-      </c>
-      <c r="P72" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>34</v>
-      </c>
-      <c r="R72" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="T72" t="s">
-        <v>453</v>
-      </c>
-      <c r="U72" t="s">
-        <v>36</v>
-      </c>
-      <c r="V72" t="s">
-        <v>44</v>
-      </c>
-      <c r="W72" t="s">
-        <v>129</v>
-      </c>
-      <c r="X72" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="73" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6492,58 +6492,58 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C73" t="s">
+        <v>453</v>
+      </c>
+      <c r="D73" t="s">
+        <v>454</v>
+      </c>
+      <c r="E73" t="s">
+        <v>454</v>
+      </c>
+      <c r="F73" t="s">
+        <v>49</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D73" t="s">
+      <c r="J73" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K73" t="s">
+        <v>448</v>
+      </c>
+      <c r="L73" t="s">
+        <v>449</v>
+      </c>
+      <c r="M73" t="s">
         <v>456</v>
       </c>
-      <c r="E73" t="s">
-        <v>456</v>
-      </c>
-      <c r="F73" t="s">
-        <v>51</v>
-      </c>
-      <c r="I73" s="1" t="s">
+      <c r="N73" t="s">
         <v>457</v>
       </c>
-      <c r="J73" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K73" t="s">
-        <v>450</v>
-      </c>
-      <c r="L73" t="s">
-        <v>451</v>
-      </c>
-      <c r="M73" t="s">
-        <v>458</v>
-      </c>
-      <c r="N73" t="s">
-        <v>459</v>
-      </c>
       <c r="P73" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q73" t="s">
+        <v>32</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="U73" t="s">
         <v>34</v>
       </c>
-      <c r="R73" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="U73" t="s">
-        <v>36</v>
-      </c>
       <c r="V73" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W73" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X73" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="74" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6551,58 +6551,58 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C74" t="s">
+        <v>458</v>
+      </c>
+      <c r="D74" t="s">
+        <v>459</v>
+      </c>
+      <c r="E74" t="s">
+        <v>459</v>
+      </c>
+      <c r="F74" t="s">
+        <v>49</v>
+      </c>
+      <c r="I74" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="D74" t="s">
+      <c r="J74" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K74" t="s">
         <v>461</v>
       </c>
-      <c r="E74" t="s">
-        <v>461</v>
-      </c>
-      <c r="F74" t="s">
-        <v>51</v>
-      </c>
-      <c r="I74" s="1" t="s">
+      <c r="L74" t="s">
         <v>462</v>
       </c>
-      <c r="J74" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K74" t="s">
+      <c r="M74" t="s">
+        <v>456</v>
+      </c>
+      <c r="N74" t="s">
         <v>463</v>
       </c>
-      <c r="L74" t="s">
-        <v>464</v>
-      </c>
-      <c r="M74" t="s">
-        <v>458</v>
-      </c>
-      <c r="N74" t="s">
-        <v>465</v>
-      </c>
       <c r="P74" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q74" t="s">
+        <v>32</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="U74" t="s">
         <v>34</v>
       </c>
-      <c r="R74" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="U74" t="s">
-        <v>36</v>
-      </c>
       <c r="V74" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W74" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X74" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="75" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6610,58 +6610,58 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C75" t="s">
+        <v>464</v>
+      </c>
+      <c r="D75" t="s">
+        <v>465</v>
+      </c>
+      <c r="E75" t="s">
+        <v>465</v>
+      </c>
+      <c r="F75" t="s">
+        <v>49</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="D75" t="s">
+      <c r="J75" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K75" t="s">
         <v>467</v>
       </c>
-      <c r="E75" t="s">
-        <v>467</v>
-      </c>
-      <c r="F75" t="s">
-        <v>51</v>
-      </c>
-      <c r="I75" s="1" t="s">
+      <c r="L75" t="s">
         <v>468</v>
       </c>
-      <c r="J75" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K75" t="s">
+      <c r="M75" t="s">
+        <v>456</v>
+      </c>
+      <c r="N75" t="s">
         <v>469</v>
       </c>
-      <c r="L75" t="s">
-        <v>470</v>
-      </c>
-      <c r="M75" t="s">
-        <v>458</v>
-      </c>
-      <c r="N75" t="s">
-        <v>471</v>
-      </c>
       <c r="P75" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q75" t="s">
+        <v>32</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="U75" t="s">
         <v>34</v>
       </c>
-      <c r="R75" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="U75" t="s">
-        <v>36</v>
-      </c>
       <c r="V75" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W75" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X75" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="76" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6669,58 +6669,58 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C76" t="s">
+        <v>470</v>
+      </c>
+      <c r="D76" t="s">
+        <v>471</v>
+      </c>
+      <c r="E76" t="s">
+        <v>471</v>
+      </c>
+      <c r="F76" t="s">
+        <v>49</v>
+      </c>
+      <c r="I76" t="s">
         <v>472</v>
       </c>
-      <c r="D76" t="s">
-        <v>473</v>
-      </c>
-      <c r="E76" t="s">
-        <v>473</v>
-      </c>
-      <c r="F76" t="s">
-        <v>51</v>
-      </c>
-      <c r="I76" t="s">
-        <v>474</v>
-      </c>
       <c r="J76" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K76" t="s">
+        <v>41</v>
+      </c>
+      <c r="L76" t="s">
         <v>438</v>
       </c>
-      <c r="K76" t="s">
-        <v>43</v>
-      </c>
-      <c r="L76" t="s">
+      <c r="M76" t="s">
+        <v>439</v>
+      </c>
+      <c r="N76" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="M76" t="s">
+      <c r="P76" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="N76" s="1" t="s">
+      <c r="Q76" t="s">
+        <v>32</v>
+      </c>
+      <c r="R76" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="P76" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>34</v>
-      </c>
-      <c r="R76" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="U76" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V76" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W76" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X76" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6728,58 +6728,58 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C77" t="s">
+        <v>473</v>
+      </c>
+      <c r="D77" t="s">
+        <v>474</v>
+      </c>
+      <c r="E77" t="s">
+        <v>474</v>
+      </c>
+      <c r="F77" t="s">
+        <v>49</v>
+      </c>
+      <c r="I77" t="s">
         <v>475</v>
       </c>
-      <c r="D77" t="s">
-        <v>476</v>
-      </c>
-      <c r="E77" t="s">
-        <v>476</v>
-      </c>
-      <c r="F77" t="s">
-        <v>51</v>
-      </c>
-      <c r="I77" t="s">
-        <v>477</v>
-      </c>
       <c r="J77" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K77" t="s">
+        <v>41</v>
+      </c>
+      <c r="L77" t="s">
         <v>438</v>
       </c>
-      <c r="K77" t="s">
-        <v>43</v>
-      </c>
-      <c r="L77" t="s">
+      <c r="M77" t="s">
+        <v>439</v>
+      </c>
+      <c r="N77" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="M77" t="s">
+      <c r="P77" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="N77" s="1" t="s">
+      <c r="Q77" t="s">
+        <v>32</v>
+      </c>
+      <c r="R77" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="P77" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>34</v>
-      </c>
-      <c r="R77" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="U77" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V77" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W77" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X77" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="78" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6787,58 +6787,58 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C78" t="s">
+        <v>476</v>
+      </c>
+      <c r="D78" t="s">
+        <v>477</v>
+      </c>
+      <c r="E78" t="s">
+        <v>477</v>
+      </c>
+      <c r="F78" t="s">
+        <v>49</v>
+      </c>
+      <c r="I78" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="D78" t="s">
+      <c r="J78" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K78" t="s">
         <v>479</v>
       </c>
-      <c r="E78" t="s">
-        <v>479</v>
-      </c>
-      <c r="F78" t="s">
-        <v>51</v>
-      </c>
-      <c r="I78" s="1" t="s">
+      <c r="L78" t="s">
         <v>480</v>
       </c>
-      <c r="J78" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K78" t="s">
+      <c r="M78" t="s">
+        <v>456</v>
+      </c>
+      <c r="N78" t="s">
         <v>481</v>
       </c>
-      <c r="L78" t="s">
-        <v>482</v>
-      </c>
-      <c r="M78" t="s">
-        <v>458</v>
-      </c>
-      <c r="N78" t="s">
-        <v>483</v>
-      </c>
       <c r="P78" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q78" t="s">
+        <v>32</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="U78" t="s">
         <v>34</v>
       </c>
-      <c r="R78" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="U78" t="s">
-        <v>36</v>
-      </c>
       <c r="V78" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W78" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X78" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="79" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6846,58 +6846,58 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C79" t="s">
+        <v>482</v>
+      </c>
+      <c r="D79" t="s">
+        <v>483</v>
+      </c>
+      <c r="E79" t="s">
+        <v>483</v>
+      </c>
+      <c r="F79" t="s">
+        <v>49</v>
+      </c>
+      <c r="I79" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="D79" t="s">
+      <c r="J79" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K79" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="E79" t="s">
-        <v>485</v>
-      </c>
-      <c r="F79" t="s">
-        <v>51</v>
-      </c>
-      <c r="I79" s="1" t="s">
+      <c r="L79" t="s">
+        <v>480</v>
+      </c>
+      <c r="M79" t="s">
+        <v>456</v>
+      </c>
+      <c r="N79" t="s">
+        <v>481</v>
+      </c>
+      <c r="P79" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>32</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="U79" t="s">
+        <v>34</v>
+      </c>
+      <c r="V79" t="s">
+        <v>42</v>
+      </c>
+      <c r="W79" t="s">
+        <v>420</v>
+      </c>
+      <c r="X79" s="1" t="s">
         <v>486</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="L79" t="s">
-        <v>482</v>
-      </c>
-      <c r="M79" t="s">
-        <v>458</v>
-      </c>
-      <c r="N79" t="s">
-        <v>483</v>
-      </c>
-      <c r="P79" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>34</v>
-      </c>
-      <c r="R79" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="U79" t="s">
-        <v>36</v>
-      </c>
-      <c r="V79" t="s">
-        <v>44</v>
-      </c>
-      <c r="W79" t="s">
-        <v>422</v>
-      </c>
-      <c r="X79" s="1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="80" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6905,58 +6905,58 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C80" t="s">
+        <v>487</v>
+      </c>
+      <c r="D80" t="s">
+        <v>488</v>
+      </c>
+      <c r="E80" t="s">
         <v>489</v>
       </c>
-      <c r="D80" t="s">
+      <c r="F80" t="s">
+        <v>49</v>
+      </c>
+      <c r="I80" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="E80" t="s">
+      <c r="J80" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K80" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="F80" t="s">
-        <v>51</v>
-      </c>
-      <c r="I80" s="1" t="s">
+      <c r="L80" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K80" s="1" t="s">
+      <c r="M80" t="s">
         <v>493</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="N80" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="M80" t="s">
+      <c r="P80" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="N80" s="1" t="s">
+      <c r="Q80" t="s">
+        <v>32</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="U80" t="s">
+        <v>34</v>
+      </c>
+      <c r="V80" t="s">
+        <v>42</v>
+      </c>
+      <c r="W80" t="s">
+        <v>420</v>
+      </c>
+      <c r="X80" s="1" t="s">
         <v>496</v>
-      </c>
-      <c r="P80" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>34</v>
-      </c>
-      <c r="R80" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="U80" t="s">
-        <v>36</v>
-      </c>
-      <c r="V80" t="s">
-        <v>44</v>
-      </c>
-      <c r="W80" t="s">
-        <v>422</v>
-      </c>
-      <c r="X80" s="1" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="81" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6964,61 +6964,61 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C81" t="s">
+        <v>497</v>
+      </c>
+      <c r="D81" t="s">
+        <v>498</v>
+      </c>
+      <c r="E81" t="s">
         <v>499</v>
       </c>
-      <c r="D81" t="s">
+      <c r="F81" t="s">
+        <v>49</v>
+      </c>
+      <c r="I81" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="E81" t="s">
+      <c r="J81" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K81" t="s">
         <v>501</v>
       </c>
-      <c r="F81" t="s">
-        <v>51</v>
-      </c>
-      <c r="I81" s="1" t="s">
+      <c r="L81" t="s">
         <v>502</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K81" t="s">
+      <c r="M81" t="s">
+        <v>456</v>
+      </c>
+      <c r="N81" t="s">
         <v>503</v>
       </c>
-      <c r="L81" t="s">
+      <c r="P81" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>32</v>
+      </c>
+      <c r="R81" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="M81" t="s">
-        <v>458</v>
-      </c>
-      <c r="N81" t="s">
+      <c r="T81" t="s">
         <v>505</v>
       </c>
-      <c r="P81" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>34</v>
-      </c>
-      <c r="R81" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="T81" t="s">
-        <v>507</v>
-      </c>
       <c r="U81" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V81" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="W81" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X81" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82" spans="1:24" ht="75" x14ac:dyDescent="0.25">
@@ -7026,61 +7026,61 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C82" t="s">
+        <v>506</v>
+      </c>
+      <c r="D82" t="s">
+        <v>507</v>
+      </c>
+      <c r="E82" t="s">
+        <v>507</v>
+      </c>
+      <c r="F82" t="s">
+        <v>49</v>
+      </c>
+      <c r="I82" t="s">
         <v>508</v>
       </c>
-      <c r="D82" t="s">
+      <c r="J82" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="E82" t="s">
-        <v>509</v>
-      </c>
-      <c r="F82" t="s">
-        <v>51</v>
-      </c>
-      <c r="I82" t="s">
-        <v>510</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="K82" t="s">
+        <v>501</v>
+      </c>
+      <c r="L82" t="s">
+        <v>502</v>
+      </c>
+      <c r="M82" t="s">
+        <v>456</v>
+      </c>
+      <c r="N82" t="s">
         <v>503</v>
       </c>
-      <c r="L82" t="s">
+      <c r="P82" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>32</v>
+      </c>
+      <c r="R82" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="M82" t="s">
-        <v>458</v>
-      </c>
-      <c r="N82" t="s">
+      <c r="T82" t="s">
         <v>505</v>
       </c>
-      <c r="P82" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>34</v>
-      </c>
-      <c r="R82" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="T82" t="s">
-        <v>507</v>
-      </c>
       <c r="U82" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V82" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="W82" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X82" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="83" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7088,58 +7088,58 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C83" t="s">
+        <v>510</v>
+      </c>
+      <c r="D83" t="s">
+        <v>511</v>
+      </c>
+      <c r="E83" t="s">
+        <v>511</v>
+      </c>
+      <c r="F83" t="s">
+        <v>49</v>
+      </c>
+      <c r="I83" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="D83" t="s">
+      <c r="J83" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K83" t="s">
         <v>513</v>
       </c>
-      <c r="E83" t="s">
-        <v>513</v>
-      </c>
-      <c r="F83" t="s">
-        <v>51</v>
-      </c>
-      <c r="I83" s="1" t="s">
+      <c r="L83" t="s">
         <v>514</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K83" t="s">
+      <c r="M83" t="s">
+        <v>456</v>
+      </c>
+      <c r="N83" t="s">
         <v>515</v>
       </c>
-      <c r="L83" t="s">
-        <v>516</v>
-      </c>
-      <c r="M83" t="s">
-        <v>458</v>
-      </c>
-      <c r="N83" t="s">
-        <v>517</v>
-      </c>
       <c r="P83" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q83" t="s">
+        <v>32</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U83" t="s">
         <v>34</v>
       </c>
-      <c r="R83" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U83" t="s">
-        <v>36</v>
-      </c>
       <c r="V83" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W83" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X83" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="84" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7147,58 +7147,58 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C84" t="s">
+        <v>516</v>
+      </c>
+      <c r="D84" t="s">
+        <v>517</v>
+      </c>
+      <c r="E84" t="s">
+        <v>517</v>
+      </c>
+      <c r="F84" t="s">
+        <v>49</v>
+      </c>
+      <c r="I84" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="D84" t="s">
+      <c r="J84" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K84" t="s">
+        <v>513</v>
+      </c>
+      <c r="L84" t="s">
+        <v>514</v>
+      </c>
+      <c r="M84" t="s">
+        <v>456</v>
+      </c>
+      <c r="N84" t="s">
+        <v>515</v>
+      </c>
+      <c r="P84" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>32</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U84" t="s">
+        <v>34</v>
+      </c>
+      <c r="V84" t="s">
+        <v>42</v>
+      </c>
+      <c r="W84" t="s">
+        <v>420</v>
+      </c>
+      <c r="X84" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="E84" t="s">
-        <v>519</v>
-      </c>
-      <c r="F84" t="s">
-        <v>51</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K84" t="s">
-        <v>515</v>
-      </c>
-      <c r="L84" t="s">
-        <v>516</v>
-      </c>
-      <c r="M84" t="s">
-        <v>458</v>
-      </c>
-      <c r="N84" t="s">
-        <v>517</v>
-      </c>
-      <c r="P84" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>34</v>
-      </c>
-      <c r="R84" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U84" t="s">
-        <v>36</v>
-      </c>
-      <c r="V84" t="s">
-        <v>44</v>
-      </c>
-      <c r="W84" t="s">
-        <v>422</v>
-      </c>
-      <c r="X84" s="1" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="85" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7206,58 +7206,58 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C85" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D85" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E85" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F85" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K85" t="s">
+        <v>513</v>
+      </c>
+      <c r="L85" t="s">
+        <v>514</v>
+      </c>
+      <c r="M85" t="s">
+        <v>456</v>
+      </c>
+      <c r="N85" t="s">
         <v>515</v>
       </c>
-      <c r="L85" t="s">
-        <v>516</v>
-      </c>
-      <c r="M85" t="s">
-        <v>458</v>
-      </c>
-      <c r="N85" t="s">
-        <v>517</v>
-      </c>
       <c r="P85" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q85" t="s">
+        <v>32</v>
+      </c>
+      <c r="R85" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U85" t="s">
         <v>34</v>
       </c>
-      <c r="R85" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U85" t="s">
-        <v>36</v>
-      </c>
       <c r="V85" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W85" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X85" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7265,58 +7265,58 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C86" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="D86" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E86" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F86" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K86" t="s">
+        <v>513</v>
+      </c>
+      <c r="L86" t="s">
+        <v>514</v>
+      </c>
+      <c r="M86" t="s">
+        <v>456</v>
+      </c>
+      <c r="N86" t="s">
         <v>515</v>
       </c>
-      <c r="L86" t="s">
-        <v>516</v>
-      </c>
-      <c r="M86" t="s">
-        <v>458</v>
-      </c>
-      <c r="N86" t="s">
-        <v>517</v>
-      </c>
       <c r="P86" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q86" t="s">
+        <v>32</v>
+      </c>
+      <c r="R86" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U86" t="s">
         <v>34</v>
       </c>
-      <c r="R86" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U86" t="s">
-        <v>36</v>
-      </c>
       <c r="V86" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W86" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X86" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="87" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7324,58 +7324,58 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C87" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D87" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E87" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F87" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K87" t="s">
+        <v>513</v>
+      </c>
+      <c r="L87" t="s">
+        <v>514</v>
+      </c>
+      <c r="M87" t="s">
+        <v>456</v>
+      </c>
+      <c r="N87" t="s">
         <v>515</v>
       </c>
-      <c r="L87" t="s">
-        <v>516</v>
-      </c>
-      <c r="M87" t="s">
-        <v>458</v>
-      </c>
-      <c r="N87" t="s">
-        <v>517</v>
-      </c>
       <c r="P87" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q87" t="s">
+        <v>32</v>
+      </c>
+      <c r="R87" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U87" t="s">
         <v>34</v>
       </c>
-      <c r="R87" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U87" t="s">
-        <v>36</v>
-      </c>
       <c r="V87" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W87" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X87" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="88" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7383,58 +7383,58 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C88" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D88" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E88" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F88" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K88" t="s">
+        <v>513</v>
+      </c>
+      <c r="L88" t="s">
+        <v>514</v>
+      </c>
+      <c r="M88" t="s">
+        <v>456</v>
+      </c>
+      <c r="N88" t="s">
         <v>515</v>
       </c>
-      <c r="L88" t="s">
-        <v>516</v>
-      </c>
-      <c r="M88" t="s">
-        <v>458</v>
-      </c>
-      <c r="N88" t="s">
-        <v>517</v>
-      </c>
       <c r="P88" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q88" t="s">
+        <v>32</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U88" t="s">
         <v>34</v>
       </c>
-      <c r="R88" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U88" t="s">
-        <v>36</v>
-      </c>
       <c r="V88" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W88" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X88" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="89" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7442,58 +7442,58 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C89" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D89" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E89" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F89" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K89" t="s">
+        <v>513</v>
+      </c>
+      <c r="L89" t="s">
+        <v>514</v>
+      </c>
+      <c r="M89" t="s">
+        <v>456</v>
+      </c>
+      <c r="N89" t="s">
         <v>515</v>
       </c>
-      <c r="L89" t="s">
-        <v>516</v>
-      </c>
-      <c r="M89" t="s">
-        <v>458</v>
-      </c>
-      <c r="N89" t="s">
-        <v>517</v>
-      </c>
       <c r="P89" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q89" t="s">
+        <v>32</v>
+      </c>
+      <c r="R89" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U89" t="s">
         <v>34</v>
       </c>
-      <c r="R89" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U89" t="s">
-        <v>36</v>
-      </c>
       <c r="V89" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W89" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X89" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7501,58 +7501,58 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C90" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D90" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E90" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F90" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K90" t="s">
+        <v>513</v>
+      </c>
+      <c r="L90" t="s">
+        <v>514</v>
+      </c>
+      <c r="M90" t="s">
+        <v>456</v>
+      </c>
+      <c r="N90" t="s">
         <v>515</v>
       </c>
-      <c r="L90" t="s">
-        <v>516</v>
-      </c>
-      <c r="M90" t="s">
-        <v>458</v>
-      </c>
-      <c r="N90" t="s">
-        <v>517</v>
-      </c>
       <c r="P90" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q90" t="s">
+        <v>32</v>
+      </c>
+      <c r="R90" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U90" t="s">
         <v>34</v>
       </c>
-      <c r="R90" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U90" t="s">
-        <v>36</v>
-      </c>
       <c r="V90" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W90" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X90" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7560,58 +7560,58 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C91" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D91" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E91" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F91" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K91" t="s">
+        <v>513</v>
+      </c>
+      <c r="L91" t="s">
+        <v>514</v>
+      </c>
+      <c r="M91" t="s">
+        <v>456</v>
+      </c>
+      <c r="N91" t="s">
         <v>515</v>
       </c>
-      <c r="L91" t="s">
-        <v>516</v>
-      </c>
-      <c r="M91" t="s">
-        <v>458</v>
-      </c>
-      <c r="N91" t="s">
-        <v>517</v>
-      </c>
       <c r="P91" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q91" t="s">
+        <v>32</v>
+      </c>
+      <c r="R91" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U91" t="s">
         <v>34</v>
       </c>
-      <c r="R91" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U91" t="s">
-        <v>36</v>
-      </c>
       <c r="V91" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W91" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X91" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7619,58 +7619,58 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C92" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D92" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E92" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F92" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K92" t="s">
+        <v>513</v>
+      </c>
+      <c r="L92" t="s">
+        <v>514</v>
+      </c>
+      <c r="M92" t="s">
+        <v>456</v>
+      </c>
+      <c r="N92" t="s">
         <v>515</v>
       </c>
-      <c r="L92" t="s">
-        <v>516</v>
-      </c>
-      <c r="M92" t="s">
-        <v>458</v>
-      </c>
-      <c r="N92" t="s">
-        <v>517</v>
-      </c>
       <c r="P92" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q92" t="s">
+        <v>32</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U92" t="s">
         <v>34</v>
       </c>
-      <c r="R92" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U92" t="s">
-        <v>36</v>
-      </c>
       <c r="V92" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W92" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X92" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="93" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7678,58 +7678,58 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C93" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D93" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E93" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F93" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K93" t="s">
+        <v>513</v>
+      </c>
+      <c r="L93" t="s">
+        <v>514</v>
+      </c>
+      <c r="M93" t="s">
+        <v>456</v>
+      </c>
+      <c r="N93" t="s">
         <v>515</v>
       </c>
-      <c r="L93" t="s">
-        <v>516</v>
-      </c>
-      <c r="M93" t="s">
-        <v>458</v>
-      </c>
-      <c r="N93" t="s">
-        <v>517</v>
-      </c>
       <c r="P93" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q93" t="s">
+        <v>32</v>
+      </c>
+      <c r="R93" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U93" t="s">
         <v>34</v>
       </c>
-      <c r="R93" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U93" t="s">
-        <v>36</v>
-      </c>
       <c r="V93" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W93" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X93" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="94" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7737,58 +7737,58 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C94" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D94" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E94" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F94" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K94" t="s">
+        <v>513</v>
+      </c>
+      <c r="L94" t="s">
+        <v>514</v>
+      </c>
+      <c r="M94" t="s">
+        <v>456</v>
+      </c>
+      <c r="N94" t="s">
         <v>515</v>
       </c>
-      <c r="L94" t="s">
-        <v>516</v>
-      </c>
-      <c r="M94" t="s">
-        <v>458</v>
-      </c>
-      <c r="N94" t="s">
-        <v>517</v>
-      </c>
       <c r="P94" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q94" t="s">
+        <v>32</v>
+      </c>
+      <c r="R94" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U94" t="s">
         <v>34</v>
       </c>
-      <c r="R94" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U94" t="s">
-        <v>36</v>
-      </c>
       <c r="V94" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W94" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X94" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7796,58 +7796,58 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C95" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D95" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E95" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F95" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K95" t="s">
+        <v>513</v>
+      </c>
+      <c r="L95" t="s">
+        <v>514</v>
+      </c>
+      <c r="M95" t="s">
+        <v>456</v>
+      </c>
+      <c r="N95" t="s">
         <v>515</v>
       </c>
-      <c r="L95" t="s">
-        <v>516</v>
-      </c>
-      <c r="M95" t="s">
-        <v>458</v>
-      </c>
-      <c r="N95" t="s">
-        <v>517</v>
-      </c>
       <c r="P95" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q95" t="s">
+        <v>32</v>
+      </c>
+      <c r="R95" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U95" t="s">
         <v>34</v>
       </c>
-      <c r="R95" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U95" t="s">
-        <v>36</v>
-      </c>
       <c r="V95" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W95" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X95" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="96" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7855,58 +7855,58 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C96" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D96" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E96" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F96" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K96" t="s">
+        <v>513</v>
+      </c>
+      <c r="L96" t="s">
+        <v>514</v>
+      </c>
+      <c r="M96" t="s">
+        <v>456</v>
+      </c>
+      <c r="N96" t="s">
         <v>515</v>
       </c>
-      <c r="L96" t="s">
-        <v>516</v>
-      </c>
-      <c r="M96" t="s">
-        <v>458</v>
-      </c>
-      <c r="N96" t="s">
-        <v>517</v>
-      </c>
       <c r="P96" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q96" t="s">
+        <v>32</v>
+      </c>
+      <c r="R96" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U96" t="s">
         <v>34</v>
       </c>
-      <c r="R96" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U96" t="s">
-        <v>36</v>
-      </c>
       <c r="V96" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W96" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X96" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="97" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7914,58 +7914,58 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C97" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D97" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E97" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F97" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K97" t="s">
+        <v>513</v>
+      </c>
+      <c r="L97" t="s">
+        <v>514</v>
+      </c>
+      <c r="M97" t="s">
+        <v>456</v>
+      </c>
+      <c r="N97" t="s">
         <v>515</v>
       </c>
-      <c r="L97" t="s">
-        <v>516</v>
-      </c>
-      <c r="M97" t="s">
-        <v>458</v>
-      </c>
-      <c r="N97" t="s">
-        <v>517</v>
-      </c>
       <c r="P97" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q97" t="s">
+        <v>32</v>
+      </c>
+      <c r="R97" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U97" t="s">
         <v>34</v>
       </c>
-      <c r="R97" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U97" t="s">
-        <v>36</v>
-      </c>
       <c r="V97" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W97" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="98" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7973,58 +7973,58 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C98" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D98" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E98" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F98" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K98" t="s">
+        <v>513</v>
+      </c>
+      <c r="L98" t="s">
+        <v>514</v>
+      </c>
+      <c r="M98" t="s">
+        <v>456</v>
+      </c>
+      <c r="N98" t="s">
         <v>515</v>
       </c>
-      <c r="L98" t="s">
-        <v>516</v>
-      </c>
-      <c r="M98" t="s">
-        <v>458</v>
-      </c>
-      <c r="N98" t="s">
-        <v>517</v>
-      </c>
       <c r="P98" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q98" t="s">
+        <v>32</v>
+      </c>
+      <c r="R98" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U98" t="s">
         <v>34</v>
       </c>
-      <c r="R98" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U98" t="s">
-        <v>36</v>
-      </c>
       <c r="V98" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W98" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X98" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8032,58 +8032,58 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C99" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D99" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E99" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F99" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K99" t="s">
+        <v>513</v>
+      </c>
+      <c r="L99" t="s">
+        <v>514</v>
+      </c>
+      <c r="M99" t="s">
+        <v>456</v>
+      </c>
+      <c r="N99" t="s">
         <v>515</v>
       </c>
-      <c r="L99" t="s">
-        <v>516</v>
-      </c>
-      <c r="M99" t="s">
-        <v>458</v>
-      </c>
-      <c r="N99" t="s">
-        <v>517</v>
-      </c>
       <c r="P99" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q99" t="s">
+        <v>32</v>
+      </c>
+      <c r="R99" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U99" t="s">
         <v>34</v>
       </c>
-      <c r="R99" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U99" t="s">
-        <v>36</v>
-      </c>
       <c r="V99" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W99" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="100" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8091,58 +8091,58 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C100" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D100" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E100" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F100" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K100" t="s">
+        <v>513</v>
+      </c>
+      <c r="L100" t="s">
+        <v>514</v>
+      </c>
+      <c r="M100" t="s">
+        <v>456</v>
+      </c>
+      <c r="N100" t="s">
         <v>515</v>
       </c>
-      <c r="L100" t="s">
-        <v>516</v>
-      </c>
-      <c r="M100" t="s">
-        <v>458</v>
-      </c>
-      <c r="N100" t="s">
-        <v>517</v>
-      </c>
       <c r="P100" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q100" t="s">
+        <v>32</v>
+      </c>
+      <c r="R100" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U100" t="s">
         <v>34</v>
       </c>
-      <c r="R100" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U100" t="s">
-        <v>36</v>
-      </c>
       <c r="V100" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W100" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X100" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8150,58 +8150,58 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D101" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E101" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F101" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K101" t="s">
+        <v>513</v>
+      </c>
+      <c r="L101" t="s">
+        <v>514</v>
+      </c>
+      <c r="M101" t="s">
+        <v>456</v>
+      </c>
+      <c r="N101" t="s">
         <v>515</v>
       </c>
-      <c r="L101" t="s">
-        <v>516</v>
-      </c>
-      <c r="M101" t="s">
-        <v>458</v>
-      </c>
-      <c r="N101" t="s">
-        <v>517</v>
-      </c>
       <c r="P101" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q101" t="s">
+        <v>32</v>
+      </c>
+      <c r="R101" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U101" t="s">
         <v>34</v>
       </c>
-      <c r="R101" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U101" t="s">
-        <v>36</v>
-      </c>
       <c r="V101" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W101" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X101" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="102" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8209,58 +8209,58 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="D102" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E102" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F102" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="K102" t="s">
+        <v>513</v>
+      </c>
+      <c r="L102" t="s">
+        <v>514</v>
+      </c>
+      <c r="M102" t="s">
+        <v>456</v>
+      </c>
+      <c r="N102" t="s">
         <v>515</v>
       </c>
-      <c r="L102" t="s">
-        <v>516</v>
-      </c>
-      <c r="M102" t="s">
-        <v>458</v>
-      </c>
-      <c r="N102" t="s">
-        <v>517</v>
-      </c>
       <c r="P102" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q102" t="s">
+        <v>32</v>
+      </c>
+      <c r="R102" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U102" t="s">
         <v>34</v>
       </c>
-      <c r="R102" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U102" t="s">
-        <v>36</v>
-      </c>
       <c r="V102" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W102" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="X102" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="103" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8268,58 +8268,58 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C103" t="s">
+        <v>556</v>
+      </c>
+      <c r="D103" t="s">
+        <v>557</v>
+      </c>
+      <c r="E103" t="s">
+        <v>557</v>
+      </c>
+      <c r="F103" t="s">
+        <v>49</v>
+      </c>
+      <c r="I103" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="D103" t="s">
+      <c r="J103" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K103" t="s">
         <v>559</v>
       </c>
-      <c r="E103" t="s">
-        <v>559</v>
-      </c>
-      <c r="F103" t="s">
-        <v>51</v>
-      </c>
-      <c r="I103" s="1" t="s">
+      <c r="L103" t="s">
         <v>560</v>
       </c>
-      <c r="J103" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K103" t="s">
+      <c r="M103" t="s">
+        <v>456</v>
+      </c>
+      <c r="N103" t="s">
         <v>561</v>
       </c>
-      <c r="L103" t="s">
-        <v>562</v>
-      </c>
-      <c r="M103" t="s">
-        <v>458</v>
-      </c>
-      <c r="N103" t="s">
-        <v>563</v>
-      </c>
       <c r="P103" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q103" t="s">
+        <v>32</v>
+      </c>
+      <c r="R103" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U103" t="s">
         <v>34</v>
       </c>
-      <c r="R103" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U103" t="s">
-        <v>36</v>
-      </c>
       <c r="V103" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W103" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X103" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8327,58 +8327,58 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C104" t="s">
+        <v>562</v>
+      </c>
+      <c r="D104" t="s">
+        <v>563</v>
+      </c>
+      <c r="E104" t="s">
         <v>564</v>
       </c>
-      <c r="D104" t="s">
+      <c r="F104" t="s">
+        <v>49</v>
+      </c>
+      <c r="I104" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="E104" t="s">
+      <c r="J104" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K104" t="s">
         <v>566</v>
       </c>
-      <c r="F104" t="s">
-        <v>51</v>
-      </c>
-      <c r="I104" s="1" t="s">
+      <c r="L104" t="s">
         <v>567</v>
       </c>
-      <c r="J104" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K104" t="s">
+      <c r="M104" t="s">
         <v>568</v>
       </c>
-      <c r="L104" t="s">
+      <c r="N104" t="s">
         <v>569</v>
       </c>
-      <c r="M104" t="s">
-        <v>570</v>
-      </c>
-      <c r="N104" t="s">
-        <v>571</v>
-      </c>
       <c r="P104" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q104" t="s">
+        <v>32</v>
+      </c>
+      <c r="R104" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U104" t="s">
         <v>34</v>
       </c>
-      <c r="R104" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U104" t="s">
-        <v>36</v>
-      </c>
       <c r="V104" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W104" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X104" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="105" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8386,58 +8386,58 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C105" t="s">
+        <v>570</v>
+      </c>
+      <c r="D105" t="s">
+        <v>571</v>
+      </c>
+      <c r="E105" t="s">
         <v>572</v>
       </c>
-      <c r="D105" t="s">
+      <c r="F105" t="s">
+        <v>49</v>
+      </c>
+      <c r="I105" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="E105" t="s">
+      <c r="J105" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="F105" t="s">
-        <v>51</v>
-      </c>
-      <c r="I105" s="1" t="s">
+      <c r="K105" t="s">
         <v>575</v>
       </c>
-      <c r="J105" s="1" t="s">
+      <c r="L105" t="s">
         <v>576</v>
       </c>
-      <c r="K105" t="s">
+      <c r="M105" t="s">
         <v>577</v>
       </c>
-      <c r="L105" t="s">
+      <c r="N105" t="s">
         <v>578</v>
       </c>
-      <c r="M105" t="s">
-        <v>579</v>
-      </c>
-      <c r="N105" t="s">
-        <v>580</v>
-      </c>
       <c r="P105" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q105" t="s">
+        <v>32</v>
+      </c>
+      <c r="R105" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="U105" t="s">
         <v>34</v>
       </c>
-      <c r="R105" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="U105" t="s">
-        <v>36</v>
-      </c>
       <c r="V105" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="W105" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="X105" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8445,61 +8445,61 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C106" t="s">
+        <v>579</v>
+      </c>
+      <c r="D106" t="s">
+        <v>580</v>
+      </c>
+      <c r="E106" t="s">
+        <v>580</v>
+      </c>
+      <c r="F106" t="s">
+        <v>49</v>
+      </c>
+      <c r="I106" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="D106" t="s">
+      <c r="J106" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K106" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E106" t="s">
-        <v>582</v>
-      </c>
-      <c r="F106" t="s">
-        <v>51</v>
-      </c>
-      <c r="I106" s="1" t="s">
+      <c r="L106" t="s">
         <v>583</v>
       </c>
-      <c r="J106" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K106" s="1" t="s">
+      <c r="M106" t="s">
         <v>584</v>
       </c>
-      <c r="L106" t="s">
+      <c r="N106" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="M106" t="s">
+      <c r="P106" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>32</v>
+      </c>
+      <c r="R106" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="N106" s="1" t="s">
+      <c r="T106" t="s">
         <v>587</v>
       </c>
-      <c r="P106" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q106" t="s">
+      <c r="U106" t="s">
         <v>34</v>
       </c>
-      <c r="R106" s="1" t="s">
+      <c r="V106" t="s">
+        <v>42</v>
+      </c>
+      <c r="W106" t="s">
+        <v>420</v>
+      </c>
+      <c r="X106" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="T106" t="s">
-        <v>589</v>
-      </c>
-      <c r="U106" t="s">
-        <v>36</v>
-      </c>
-      <c r="V106" t="s">
-        <v>44</v>
-      </c>
-      <c r="W106" t="s">
-        <v>422</v>
-      </c>
-      <c r="X106" s="1" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="107" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8507,61 +8507,61 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C107" t="s">
+        <v>589</v>
+      </c>
+      <c r="D107" t="s">
+        <v>590</v>
+      </c>
+      <c r="E107" t="s">
+        <v>590</v>
+      </c>
+      <c r="F107" t="s">
+        <v>49</v>
+      </c>
+      <c r="I107" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="D107" t="s">
+      <c r="J107" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="L107" t="s">
+        <v>583</v>
+      </c>
+      <c r="M107" t="s">
+        <v>584</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="P107" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>32</v>
+      </c>
+      <c r="R107" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="T107" t="s">
+        <v>587</v>
+      </c>
+      <c r="U107" t="s">
+        <v>34</v>
+      </c>
+      <c r="V107" t="s">
+        <v>42</v>
+      </c>
+      <c r="W107" t="s">
+        <v>420</v>
+      </c>
+      <c r="X107" s="1" t="s">
         <v>592</v>
-      </c>
-      <c r="E107" t="s">
-        <v>592</v>
-      </c>
-      <c r="F107" t="s">
-        <v>51</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="L107" t="s">
-        <v>585</v>
-      </c>
-      <c r="M107" t="s">
-        <v>586</v>
-      </c>
-      <c r="N107" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="P107" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>34</v>
-      </c>
-      <c r="R107" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="T107" t="s">
-        <v>589</v>
-      </c>
-      <c r="U107" t="s">
-        <v>36</v>
-      </c>
-      <c r="V107" t="s">
-        <v>44</v>
-      </c>
-      <c r="W107" t="s">
-        <v>422</v>
-      </c>
-      <c r="X107" s="1" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="108" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8569,61 +8569,61 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C108" t="s">
+        <v>593</v>
+      </c>
+      <c r="D108" t="s">
+        <v>594</v>
+      </c>
+      <c r="E108" t="s">
+        <v>594</v>
+      </c>
+      <c r="F108" t="s">
+        <v>49</v>
+      </c>
+      <c r="I108" t="s">
         <v>595</v>
       </c>
-      <c r="D108" t="s">
+      <c r="J108" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="L108" t="s">
+        <v>583</v>
+      </c>
+      <c r="M108" t="s">
+        <v>584</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="P108" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>32</v>
+      </c>
+      <c r="R108" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="T108" t="s">
+        <v>587</v>
+      </c>
+      <c r="U108" t="s">
+        <v>34</v>
+      </c>
+      <c r="V108" t="s">
+        <v>42</v>
+      </c>
+      <c r="W108" t="s">
+        <v>420</v>
+      </c>
+      <c r="X108" s="1" t="s">
         <v>596</v>
-      </c>
-      <c r="E108" t="s">
-        <v>596</v>
-      </c>
-      <c r="F108" t="s">
-        <v>51</v>
-      </c>
-      <c r="I108" t="s">
-        <v>597</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="L108" t="s">
-        <v>585</v>
-      </c>
-      <c r="M108" t="s">
-        <v>586</v>
-      </c>
-      <c r="N108" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="P108" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>34</v>
-      </c>
-      <c r="R108" s="1" t="s">
-        <v>588</v>
-      </c>
-      <c r="T108" t="s">
-        <v>589</v>
-      </c>
-      <c r="U108" t="s">
-        <v>36</v>
-      </c>
-      <c r="V108" t="s">
-        <v>44</v>
-      </c>
-      <c r="W108" t="s">
-        <v>422</v>
-      </c>
-      <c r="X108" s="1" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.25">
@@ -8631,37 +8631,37 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C109" t="s">
+        <v>597</v>
+      </c>
+      <c r="D109" t="s">
+        <v>598</v>
+      </c>
+      <c r="E109" t="s">
+        <v>598</v>
+      </c>
+      <c r="F109" t="s">
+        <v>49</v>
+      </c>
+      <c r="I109" t="s">
         <v>599</v>
       </c>
-      <c r="D109" t="s">
-        <v>600</v>
-      </c>
-      <c r="E109" t="s">
-        <v>600</v>
-      </c>
-      <c r="F109" t="s">
-        <v>51</v>
-      </c>
-      <c r="I109" t="s">
-        <v>601</v>
-      </c>
       <c r="K109" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U109" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V109" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W109" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X109" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.25">
@@ -8669,37 +8669,37 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C110" t="s">
+        <v>600</v>
+      </c>
+      <c r="D110" t="s">
+        <v>601</v>
+      </c>
+      <c r="E110" t="s">
+        <v>601</v>
+      </c>
+      <c r="F110" t="s">
+        <v>49</v>
+      </c>
+      <c r="I110" t="s">
         <v>602</v>
       </c>
-      <c r="D110" t="s">
-        <v>603</v>
-      </c>
-      <c r="E110" t="s">
-        <v>603</v>
-      </c>
-      <c r="F110" t="s">
-        <v>51</v>
-      </c>
-      <c r="I110" t="s">
-        <v>604</v>
-      </c>
       <c r="K110" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U110" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V110" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W110" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X110" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.25">
@@ -8707,37 +8707,37 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C111" t="s">
+        <v>603</v>
+      </c>
+      <c r="D111" t="s">
+        <v>604</v>
+      </c>
+      <c r="E111" t="s">
+        <v>604</v>
+      </c>
+      <c r="F111" t="s">
+        <v>49</v>
+      </c>
+      <c r="I111" t="s">
         <v>605</v>
       </c>
-      <c r="D111" t="s">
-        <v>606</v>
-      </c>
-      <c r="E111" t="s">
-        <v>606</v>
-      </c>
-      <c r="F111" t="s">
-        <v>51</v>
-      </c>
-      <c r="I111" t="s">
-        <v>607</v>
-      </c>
       <c r="K111" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U111" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V111" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W111" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X111" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.25">
@@ -8745,37 +8745,37 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C112" t="s">
+        <v>606</v>
+      </c>
+      <c r="D112" t="s">
+        <v>607</v>
+      </c>
+      <c r="E112" t="s">
+        <v>607</v>
+      </c>
+      <c r="F112" t="s">
+        <v>49</v>
+      </c>
+      <c r="I112" t="s">
         <v>608</v>
       </c>
-      <c r="D112" t="s">
-        <v>609</v>
-      </c>
-      <c r="E112" t="s">
-        <v>609</v>
-      </c>
-      <c r="F112" t="s">
-        <v>51</v>
-      </c>
-      <c r="I112" t="s">
-        <v>610</v>
-      </c>
       <c r="K112" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U112" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V112" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W112" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X112" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.25">
@@ -8783,37 +8783,37 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C113" t="s">
+        <v>609</v>
+      </c>
+      <c r="D113" t="s">
+        <v>610</v>
+      </c>
+      <c r="E113" t="s">
+        <v>610</v>
+      </c>
+      <c r="F113" t="s">
+        <v>49</v>
+      </c>
+      <c r="I113" t="s">
         <v>611</v>
       </c>
-      <c r="D113" t="s">
-        <v>612</v>
-      </c>
-      <c r="E113" t="s">
-        <v>612</v>
-      </c>
-      <c r="F113" t="s">
-        <v>51</v>
-      </c>
-      <c r="I113" t="s">
-        <v>613</v>
-      </c>
       <c r="K113" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U113" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V113" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W113" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X113" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="114" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8821,55 +8821,55 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C114" t="s">
+        <v>612</v>
+      </c>
+      <c r="D114" t="s">
+        <v>613</v>
+      </c>
+      <c r="E114" t="s">
+        <v>613</v>
+      </c>
+      <c r="F114" t="s">
+        <v>49</v>
+      </c>
+      <c r="I114" t="s">
+        <v>602</v>
+      </c>
+      <c r="K114" t="s">
         <v>614</v>
       </c>
-      <c r="D114" t="s">
+      <c r="L114" t="s">
         <v>615</v>
       </c>
-      <c r="E114" t="s">
-        <v>615</v>
-      </c>
-      <c r="F114" t="s">
-        <v>51</v>
-      </c>
-      <c r="I114" t="s">
-        <v>604</v>
-      </c>
-      <c r="K114" t="s">
+      <c r="M114" t="s">
         <v>616</v>
       </c>
-      <c r="L114" t="s">
+      <c r="N114" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="M114" t="s">
+      <c r="P114" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>82</v>
+      </c>
+      <c r="R114" t="s">
         <v>618</v>
       </c>
-      <c r="N114" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="P114" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>84</v>
-      </c>
-      <c r="R114" t="s">
-        <v>620</v>
-      </c>
       <c r="U114" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="V114" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W114" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="X114" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.25">
@@ -8877,37 +8877,37 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C115" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D115" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E115" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F115" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I115" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="K115" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U115" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V115" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W115" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X115" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="116" spans="1:24" ht="135" x14ac:dyDescent="0.25">
@@ -8915,43 +8915,43 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C116" t="s">
+        <v>621</v>
+      </c>
+      <c r="D116" t="s">
+        <v>622</v>
+      </c>
+      <c r="E116" t="s">
         <v>623</v>
       </c>
-      <c r="D116" t="s">
+      <c r="F116" t="s">
+        <v>49</v>
+      </c>
+      <c r="I116" t="s">
         <v>624</v>
       </c>
-      <c r="E116" t="s">
+      <c r="J116" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="F116" t="s">
-        <v>51</v>
-      </c>
-      <c r="I116" t="s">
+      <c r="K116" t="s">
+        <v>41</v>
+      </c>
+      <c r="T116" t="s">
         <v>626</v>
       </c>
-      <c r="J116" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="K116" t="s">
-        <v>43</v>
-      </c>
-      <c r="T116" t="s">
-        <v>628</v>
-      </c>
       <c r="U116" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V116" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="W116" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X116" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="117" spans="1:24" ht="225" x14ac:dyDescent="0.25">
@@ -8959,40 +8959,40 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C117" t="s">
+        <v>627</v>
+      </c>
+      <c r="D117" t="s">
+        <v>628</v>
+      </c>
+      <c r="E117" t="s">
         <v>629</v>
       </c>
-      <c r="D117" t="s">
+      <c r="F117" t="s">
+        <v>49</v>
+      </c>
+      <c r="I117" t="s">
+        <v>624</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="E117" t="s">
-        <v>631</v>
-      </c>
-      <c r="F117" t="s">
-        <v>51</v>
-      </c>
-      <c r="I117" t="s">
-        <v>626</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>632</v>
-      </c>
       <c r="K117" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U117" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V117" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W117" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X117" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="118" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -9000,40 +9000,40 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C118" t="s">
+        <v>631</v>
+      </c>
+      <c r="D118" t="s">
+        <v>632</v>
+      </c>
+      <c r="E118" t="s">
         <v>633</v>
       </c>
-      <c r="D118" t="s">
+      <c r="F118" t="s">
+        <v>49</v>
+      </c>
+      <c r="I118" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="E118" t="s">
+      <c r="J118" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="F118" t="s">
-        <v>51</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>637</v>
-      </c>
       <c r="K118" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U118" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="V118" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="W118" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="X118" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="119" spans="1:24" ht="285" x14ac:dyDescent="0.25">
@@ -9041,58 +9041,58 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C119" t="s">
+        <v>636</v>
+      </c>
+      <c r="D119" t="s">
+        <v>637</v>
+      </c>
+      <c r="E119" t="s">
         <v>638</v>
       </c>
-      <c r="D119" t="s">
+      <c r="F119" t="s">
+        <v>49</v>
+      </c>
+      <c r="I119" t="s">
         <v>639</v>
       </c>
-      <c r="E119" t="s">
+      <c r="J119" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="K119" t="s">
         <v>640</v>
       </c>
-      <c r="F119" t="s">
-        <v>51</v>
-      </c>
-      <c r="I119" t="s">
+      <c r="L119" t="s">
         <v>641</v>
       </c>
-      <c r="J119" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="K119" t="s">
+      <c r="M119" t="s">
         <v>642</v>
       </c>
-      <c r="L119" t="s">
+      <c r="N119" t="s">
         <v>643</v>
       </c>
-      <c r="M119" t="s">
+      <c r="P119" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>32</v>
+      </c>
+      <c r="R119" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="N119" t="s">
+      <c r="U119" t="s">
+        <v>34</v>
+      </c>
+      <c r="V119" t="s">
+        <v>42</v>
+      </c>
+      <c r="W119" t="s">
+        <v>127</v>
+      </c>
+      <c r="X119" t="s">
         <v>645</v>
-      </c>
-      <c r="P119" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q119" t="s">
-        <v>34</v>
-      </c>
-      <c r="R119" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="U119" t="s">
-        <v>36</v>
-      </c>
-      <c r="V119" t="s">
-        <v>44</v>
-      </c>
-      <c r="W119" t="s">
-        <v>129</v>
-      </c>
-      <c r="X119" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="120" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -9100,61 +9100,61 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C120" t="s">
+        <v>646</v>
+      </c>
+      <c r="D120" t="s">
+        <v>647</v>
+      </c>
+      <c r="E120" t="s">
         <v>648</v>
       </c>
-      <c r="D120" t="s">
+      <c r="F120" t="s">
+        <v>49</v>
+      </c>
+      <c r="I120" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="E120" t="s">
+      <c r="J120" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="K120" t="s">
         <v>650</v>
       </c>
-      <c r="F120" t="s">
-        <v>51</v>
-      </c>
-      <c r="I120" s="1" t="s">
+      <c r="L120" t="s">
         <v>651</v>
       </c>
-      <c r="J120" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="K120" t="s">
+      <c r="M120" t="s">
         <v>652</v>
       </c>
-      <c r="L120" t="s">
+      <c r="N120" t="s">
         <v>653</v>
       </c>
-      <c r="M120" t="s">
+      <c r="P120" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>32</v>
+      </c>
+      <c r="R120" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="N120" t="s">
+      <c r="T120" t="s">
         <v>655</v>
       </c>
-      <c r="P120" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q120" t="s">
+      <c r="U120" t="s">
         <v>34</v>
       </c>
-      <c r="R120" s="1" t="s">
+      <c r="V120" t="s">
+        <v>42</v>
+      </c>
+      <c r="W120" t="s">
+        <v>127</v>
+      </c>
+      <c r="X120" t="s">
         <v>656</v>
-      </c>
-      <c r="T120" t="s">
-        <v>657</v>
-      </c>
-      <c r="U120" t="s">
-        <v>36</v>
-      </c>
-      <c r="V120" t="s">
-        <v>44</v>
-      </c>
-      <c r="W120" t="s">
-        <v>129</v>
-      </c>
-      <c r="X120" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="121" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -9162,34 +9162,34 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C121" t="s">
+        <v>657</v>
+      </c>
+      <c r="D121" t="s">
+        <v>658</v>
+      </c>
+      <c r="E121" t="s">
         <v>659</v>
       </c>
-      <c r="D121" t="s">
+      <c r="F121" t="s">
+        <v>138</v>
+      </c>
+      <c r="K121" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="E121" t="s">
+      <c r="U121" t="s">
+        <v>34</v>
+      </c>
+      <c r="V121" t="s">
+        <v>42</v>
+      </c>
+      <c r="W121" t="s">
         <v>661</v>
       </c>
-      <c r="F121" t="s">
-        <v>140</v>
-      </c>
-      <c r="K121" s="1" t="s">
+      <c r="X121" s="1" t="s">
         <v>662</v>
-      </c>
-      <c r="U121" t="s">
-        <v>36</v>
-      </c>
-      <c r="V121" t="s">
-        <v>44</v>
-      </c>
-      <c r="W121" t="s">
-        <v>663</v>
-      </c>
-      <c r="X121" s="1" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="122" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -9197,37 +9197,37 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C122" t="s">
+        <v>663</v>
+      </c>
+      <c r="D122" t="s">
+        <v>664</v>
+      </c>
+      <c r="E122" t="s">
         <v>665</v>
       </c>
-      <c r="D122" t="s">
+      <c r="F122" t="s">
+        <v>49</v>
+      </c>
+      <c r="G122" t="s">
         <v>666</v>
       </c>
-      <c r="E122" t="s">
+      <c r="K122" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="U122" t="s">
+        <v>34</v>
+      </c>
+      <c r="V122" t="s">
+        <v>42</v>
+      </c>
+      <c r="W122" t="s">
+        <v>61</v>
+      </c>
+      <c r="X122" s="1" t="s">
         <v>667</v>
-      </c>
-      <c r="F122" t="s">
-        <v>51</v>
-      </c>
-      <c r="G122" t="s">
-        <v>668</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="U122" t="s">
-        <v>36</v>
-      </c>
-      <c r="V122" t="s">
-        <v>44</v>
-      </c>
-      <c r="W122" t="s">
-        <v>63</v>
-      </c>
-      <c r="X122" s="1" t="s">
-        <v>669</v>
       </c>
     </row>
   </sheetData>

--- a/baseline/data_processing_elements-FRA.xlsx
+++ b/baseline/data_processing_elements-FRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001A0AB1-13F7-4D7F-8E42-7C06865F247F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8B48E6-3774-4CAB-AA95-70A02686DF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCDECE63-0FFC-4822-923F-34FACAF497E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="670">
   <si>
     <t>index</t>
   </si>
@@ -3026,21 +3026,24 @@
         <v>27</v>
       </c>
       <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>30</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>31</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>33</v>
       </c>
       <c r="U2" t="s">

--- a/baseline/data_processing_elements-FRA.xlsx
+++ b/baseline/data_processing_elements-FRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8B48E6-3774-4CAB-AA95-70A02686DF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E32CC9-4B21-4B0E-B4D4-12415C205242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCDECE63-0FFC-4822-923F-34FACAF497E3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="671">
   <si>
     <t>index</t>
   </si>
@@ -1700,6 +1700,781 @@
 med1atc1;
 ...;
 med9atc1</t>
+  </si>
+  <si>
+    <t>dis_msk_ever</t>
+  </si>
+  <si>
+    <t>Musculoskeletal diseases ever</t>
+  </si>
+  <si>
+    <t>Musculoskeletal diseases ever (osteoporosis, arthrosis, rheumatic disorder, osteoarthritis or rheumatism, rheumatoid arthritis, osteoarthritis, other arthritis, rheumatoid arthritis)</t>
+  </si>
+  <si>
+    <t>A "No" response can be assigned if the input variables were collected in Yes/No format. 
+If the input variables do not have a "No" response but are part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned.</t>
+  </si>
+  <si>
+    <t>osteoarthrosis1;
+osteoporosis1;
+sciatica1;
+rheumatoidarthritis1</t>
+  </si>
+  <si>
+    <t>Osteoarthrosis;
+Osteoporosis;
+Sciatica (lumbar disc herniation);
+Rheumatoid arthritis</t>
+  </si>
+  <si>
+    <t>HAM_LSI;HAM_LSI;HAM_LSI;HAM_LSI;HAM_LSI</t>
+  </si>
+  <si>
+    <t>Osteoarthrosis. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of osteoarthrosis? Response options: no, yes: previously, yes: currently;
+Osteoporosiss. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of osteoporosis? Response options: no, yes: previously, yes: currently;
+Sciatica (lumbar disc herniation). Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of sciatica (lumbar disc herniation)? Response options: no, yes: previously, yes: currently ;
+Fibromyalgia. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of fibromyalgia? Response options: no, yes: previously, yes: currently ;
+Rheumatoid arthritis. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of rheumatoid arthritis? Response options: no, yes: previously, yes: currently</t>
+  </si>
+  <si>
+    <t>Cohort profile: DOI: 10.1093/gerona/glaa193
+;Cohort profile: DOI: 10.1093/gerona/glaa193
+;Cohort profile: DOI: 10.1093/gerona/glaa193
+;Cohort profile: DOI: 10.1093/gerona/glaa193
+;Cohort profile: DOI: 10.1093/gerona/glaa193</t>
+  </si>
+  <si>
+    <t>case_when(
+osteoarthrosis1 %in% c(2, 3) | osteoporosis1 %in% c(2, 3) | sciatica1 %in% c(2, 3) | rheumatoidarthritis1 %in% c(2, 3) ~ 1L;
+osteoarthrosis1 == 1 &amp; osteoporosis1 == 1 &amp; sciatica1 == 1 &amp; rheumatoidarthritis1 == 1 ~ 0L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>dis_diabetes</t>
+  </si>
+  <si>
+    <t>Diabetes</t>
+  </si>
+  <si>
+    <t>Diabetes (including gestational diabetes and other types of diabetes but excluding impaired fasting glucose and impaired glucose tolerance)</t>
+  </si>
+  <si>
+    <t>A "No" response can be assigned if the input variables were collected in Yes/No format.
+If the input variables do not have a "No" response but are part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned. 
+Add a harmonization comment about any study-specific wording for collecting information about diabetes (e.g., only Type 2 diabetes, excluding gestational diabetes).</t>
+  </si>
+  <si>
+    <t>diabetes1</t>
+  </si>
+  <si>
+    <t>Type 2 diabetes</t>
+  </si>
+  <si>
+    <t>Type 2 diabetes. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of type 2 diabetes? Response options: no, yes: previously, yes: currently.</t>
+  </si>
+  <si>
+    <t>1 = no 
+2 = yes, previously 
+3 = yes, currently</t>
+  </si>
+  <si>
+    <t>The study only ask about type 2 diabetes.</t>
+  </si>
+  <si>
+    <t>dis_diabetes_type</t>
+  </si>
+  <si>
+    <t>Diabetes type</t>
+  </si>
+  <si>
+    <t>Add a harmonization comment about any study-specific wording for collecting information about diabetes (e.g., only Type 2 diabetes collected).</t>
+  </si>
+  <si>
+    <t>1 Type 1 
+2 Type 2 
+3 Other</t>
+  </si>
+  <si>
+    <t>dis_cancer_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever</t>
+  </si>
+  <si>
+    <t>When studies do not have an "other cancer" category, a "No" cannot be generated. In this situation only 1 and NA would be present.
+Add a harmonization comment about any decisions made for harmonization.
+"Presumed no" can be specified only if a general cancer disease option is present in a select all that apply question where at least another option is selected but not this one.</t>
+  </si>
+  <si>
+    <t>malignanttumor1</t>
+  </si>
+  <si>
+    <t>Malignant tumor (cancer)</t>
+  </si>
+  <si>
+    <t>Malignant tumor (cancer). Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of malignant tumor? Response options: no, yes: previously, yes: currently</t>
+  </si>
+  <si>
+    <t>dis_cancer_bladder_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Bladder</t>
+  </si>
+  <si>
+    <t>The "No" response can be attributed only in 2 situations:
+- There is a parent variable about having any cancer, collected in Yes/No format.
+- The input variables were collected in Yes/No format for this specific cancer type
+If the input variables do not have a "No" response but are part of select all that apply section where at least another cancer type is selected, then a "Presumed no" can be assigned.</t>
+  </si>
+  <si>
+    <t>case_when(
+malignanttumor1 == 1 ~ 0L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>dis_cancer_breast_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Breast</t>
+  </si>
+  <si>
+    <t>dis_cancer_cervix_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Cervix</t>
+  </si>
+  <si>
+    <t>dis_cancer_colorectal_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Colon-Rectum</t>
+  </si>
+  <si>
+    <t>dis_cancer_kidney_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Kidney</t>
+  </si>
+  <si>
+    <t>dis_cancer_throat_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Throat/Larynx-Pharynx</t>
+  </si>
+  <si>
+    <t>dis_cancer_leukaemia_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Leukaemia</t>
+  </si>
+  <si>
+    <t>dis_cancer_lung_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Lung</t>
+  </si>
+  <si>
+    <t>dis_cancer_lymphoma_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Lymphoma</t>
+  </si>
+  <si>
+    <t>dis_cancer_prostate_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Prostate</t>
+  </si>
+  <si>
+    <t>dis_cancer_skin_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Skin</t>
+  </si>
+  <si>
+    <t>dis_cancer_stomach_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Stomach</t>
+  </si>
+  <si>
+    <t>dis_cancer_testicle_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Testicle</t>
+  </si>
+  <si>
+    <t>dis_cancer_uterus_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Uterus</t>
+  </si>
+  <si>
+    <t>dis_cancer_brain_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Brain</t>
+  </si>
+  <si>
+    <t>dis_cancer_liver_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Liver</t>
+  </si>
+  <si>
+    <t>dis_cancer_ovary_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Ovary</t>
+  </si>
+  <si>
+    <t>dis_cancer_pancreas_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Pancreas</t>
+  </si>
+  <si>
+    <t>dis_cancer_thyroid_ever</t>
+  </si>
+  <si>
+    <t>Cancer ever - Thyroid</t>
+  </si>
+  <si>
+    <t>dis_hypercholesteromia_ever</t>
+  </si>
+  <si>
+    <t>Diagnosed hypercholesteromia</t>
+  </si>
+  <si>
+    <t>A "No" response can be assigned if the input variables were collected in Yes/No format.
+If the input variables do not have a "No" response but are part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned.</t>
+  </si>
+  <si>
+    <t>highcholesterol1</t>
+  </si>
+  <si>
+    <t>High cholesterol</t>
+  </si>
+  <si>
+    <t>High cholesterol. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of high cholesterol? Response options: no, yes: previously, yes: currently.</t>
+  </si>
+  <si>
+    <t>dis_depression</t>
+  </si>
+  <si>
+    <t>Depression</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant has depression or not</t>
+  </si>
+  <si>
+    <t>Accept self-reported condition but with a note. 
+A "No" response can be assigned if the input variables were collected in Yes/No format.
+If the input variable do not have a "No" response but is part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned.</t>
+  </si>
+  <si>
+    <t>depression1</t>
+  </si>
+  <si>
+    <t>depression</t>
+  </si>
+  <si>
+    <t>HAM_Depression</t>
+  </si>
+  <si>
+    <t>Depression. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of depression? Response options: no, yes: previously, yes: currently.</t>
+  </si>
+  <si>
+    <t>dis_alzheimers_dementia</t>
+  </si>
+  <si>
+    <t>Alzheimers/Dementia</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant has Alzheimers/Dementia</t>
+  </si>
+  <si>
+    <t>A "No" response can be assigned if the input variables were collected in Yes/No format.
+If the input variable do not have a "No" response but is part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 Has not been diagnosed with Alzheimers or other dementia 
+1 Has been diagnosed with Alzheimers or other dementia 
+2 Has presumably not been diagnosed with Alzheimers or other dementia 
+</t>
+  </si>
+  <si>
+    <t>alzheimer1</t>
+  </si>
+  <si>
+    <t>Alzheimer or other dementia</t>
+  </si>
+  <si>
+    <t>HAM_Alzheimers</t>
+  </si>
+  <si>
+    <t>Alzheimer or other dementia. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of Alzheimer or other dementia? Response options: no, yes: previously, yes: currently.</t>
+  </si>
+  <si>
+    <t>med_lipid_lowering_cur</t>
+  </si>
+  <si>
+    <t>Current use of lipid lowering medication</t>
+  </si>
+  <si>
+    <t>Only include if lipid lowering medication is currently being taken. A "No" response is possible only if a Yes/No question is collected.
+If the item is in a select all that apply where at least another item is selected then it is a "Presumed no".</t>
+  </si>
+  <si>
+    <t>med1atc1;
+med2atc1;
+med3atc1;
+med4atc1;
+med5atc1;
+med6atc1;
+med7atc1;
+med8atc1;
+med9atc1</t>
+  </si>
+  <si>
+    <t>Medication 1 to 5 atc code</t>
+  </si>
+  <si>
+    <t>HAM_MedUse</t>
+  </si>
+  <si>
+    <t>ATC code (Anatomical Therapeutic Chemical classification) of the medication used. Self-reported. Participants were asked to fill in a form names of medicines that they used. The full ATC code (A10BH01 etc). If the ATC code was not found, medicine was coded as follows: 
+X01= anti-hypertensive drug
+X02= diabetes drug
+X03= analgesic (painkiller)
+X04= cholesterol medicine
+X05= hormone replacement therapy
+X06= cortisone
+X07= vitamin 
+X08= nature cure/alternative remedy
+X10= something else/unspecified
+X11= antidepressant
+X12= allergy medicine
+X13= cortisone salve</t>
+  </si>
+  <si>
+    <t>ATC code (Anatomical Therapeutic Chemical classification)
+or if ATC code missing: 
+X01= anti-hypertensive drug
+X02= diabetes drug
+X03= analgesic (painkiller)
+X04= cholesterol medicine
+X05= hormone replacement therapy
+X06= cortisone
+X07= vitamin 
+X08= nature cure/alternative remedy
+X10= something else/unspecified
+X11= antidepressant
+X12= allergy medicine
+X13= cortisone salve</t>
+  </si>
+  <si>
+    <t>Derived from list of medication taken by the participant.</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc1 == "X04" ~ 1L;
+med2atc1 == "X04" ~ 1L;
+med3atc1 == "X04" ~ 1L;
+med4atc1 == "X04" ~ 1L;
+med5atc1 == "X04" ~ 1L;
+med6atc1 == "X04" ~ 1L;
+med7atc1 == "X04" ~ 1L;
+med8atc1 == "X04" ~ 1L;
+med9atc1 == "X04" ~ 1L;
+grepl("^C10", med1atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med2atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med3atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med4atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med5atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med6atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med7atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med8atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C10", med9atc1, ignore.case = TRUE) ~ 1L;
+!is.na(med1atc1) | !is.na(med2atc1) | !is.na(med3atc1) | !is.na(med4atc1) | !is.na(med5atc1) | !is.na(med6atc1) | !is.na(med7atc1) | !is.na(med8atc1) | !is.na(med9atc1) ~ 2L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>med_blood_pressure_cur</t>
+  </si>
+  <si>
+    <t>Current use of medication to manage blood pressure</t>
+  </si>
+  <si>
+    <t>Only include if medication for hypertension or high blood pressure is currently being taken. A "No" response is possible only if a Yes/No question is collected.
+The question must be separated from a hypertension or hbp diagnosis question.
+If the item is in a select all that apply where at least another item is selected then it is a "Presumed no".</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc1 == "X01" ~ 1L;
+med2atc1 == "X01" ~ 1L;
+med3atc1 == "X01" ~ 1L;
+med4atc1 == "X01" ~ 1L;
+med5atc1 == "X01" ~ 1L;
+med6atc1 == "X01" ~ 1L;
+med7atc1 == "X01" ~ 1L;
+med8atc1 == "X01" ~ 1L;
+med9atc1 == "X01" ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med1atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med2atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med3atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med4atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med5atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med6atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med7atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med8atc1, ignore.case = TRUE) ~ 1L;
+grepl("^C02|^C03|^C07|^C08|^C09", med9atc1, ignore.case = TRUE) ~ 1L;
+!is.na(med1atc1) | !is.na(med2atc1) | !is.na(med3atc1) | !is.na(med4atc1) | !is.na(med5atc1) | !is.na(med6atc1) | !is.na(med7atc1) | !is.na(med8atc1) | !is.na(med9atc1) ~ 2L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>med_diabetes_cur</t>
+  </si>
+  <si>
+    <t>Current use of medication for diabetes</t>
+  </si>
+  <si>
+    <t>If the item is in a select all that apply where at least another item is selected then it is a "Presumed no".</t>
+  </si>
+  <si>
+    <t>case_when(
+med1atc1 == "X02" ~ 1L;
+med2atc1 == "X02" ~ 1L;
+med3atc1 == "X02" ~ 1L;
+med4atc1 == "X02" ~ 1L;
+med5atc1 == "X02" ~ 1L;
+med6atc1 == "X02" ~ 1L;
+med7atc1 == "X02" ~ 1L;
+med8atc1 == "X02" ~ 1L;
+med9atc1 == "X02" ~ 1L;
+grepl("^A10", med1atc1, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med2atc1, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med3atc1, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med4atc1, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med5atc1, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med6atc1, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med7atc1, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med8atc1, ignore.case = TRUE) ~ 1L;
+grepl("^A10", med9atc1, ignore.case = TRUE) ~ 1L;
+!is.na(med1atc1) | !is.na(med2atc1) | !is.na(med3atc1) | !is.na(med4atc1) | !is.na(med5atc1) | !is.na(med6atc1) | !is.na(med7atc1) | !is.na(med8atc1) | !is.na(med9atc1) ~ 2L;
+ELSE ~ NA_integer_)</t>
+  </si>
+  <si>
+    <t>psy_dep_cesd20</t>
+  </si>
+  <si>
+    <t>CES-D (20 items) score</t>
+  </si>
+  <si>
+    <t>If the study has the total score variable, make sure the calculation is correct. Accepted score range is 0-60</t>
+  </si>
+  <si>
+    <t>psy_dep_cesd10</t>
+  </si>
+  <si>
+    <t>CES-D (10 items) score</t>
+  </si>
+  <si>
+    <t>If the study has the total score variable, make sure the calculation is correct. Accepted score range is 0-30</t>
+  </si>
+  <si>
+    <t>psy_dep_malaise</t>
+  </si>
+  <si>
+    <t>Malaise inventory (9 items) score</t>
+  </si>
+  <si>
+    <t>If the study has the total score variable, make sure the calculation is correct. Accepted score range is 0-24</t>
+  </si>
+  <si>
+    <t>psy_dep_kessler</t>
+  </si>
+  <si>
+    <t>Kessler psychological distress score</t>
+  </si>
+  <si>
+    <t>If the study has the total score variable, make sure the calculation is correct. Accepted score range is 10-50</t>
+  </si>
+  <si>
+    <t>psy_dep_phq9</t>
+  </si>
+  <si>
+    <t>PHQ-9 score</t>
+  </si>
+  <si>
+    <t>If the study has the total score variable, make sure the calculation is correct. Accepted score range is 0-27</t>
+  </si>
+  <si>
+    <t>psy_mci_mmse_score</t>
+  </si>
+  <si>
+    <t>MMSE score</t>
+  </si>
+  <si>
+    <t>mci1</t>
+  </si>
+  <si>
+    <t>Mild cognitive impairment</t>
+  </si>
+  <si>
+    <t>HAM_MildCI</t>
+  </si>
+  <si>
+    <t>Mild cognitive impairment was assessed during a clinical study visit with the Mini-Mental State Examination (MMSE) including items to assess cognitive function (orientation, attention, memory, language and visual-spatial skills) [doi: 10.1016/0022-3956(75)90026-6]. 
+More specific tasks/questions during the test: 
+1. What is the year? (wrong answer 0 points, right answer 1 point)
+2. What is the season? (wrong answer 0 points, right answer 1 point)
+3. What is the date? (wrong answer 0 points, right answer 1 point)
+4. What is the day of the week? (wrong answer 0 points, right answer 1 point)
+5. What is the month? (wrong answer 0 points, right answer 1 point)
+6. In what country we are now? (wrong answer 0 points, right answer 1 point)
+7. In what county we are now? (wrong answer 0 points, right answer 1 point)
+8. What is the name of this city? (wrong answer 0 points, right answer 1 point)
+9. What is this place where we are now? (wrong answer 0 points, right answer 1 point)
+10. In which floor we are now? (wrong answer 0 points, right answer 1 point)
+11. Soon I will say three words and you should memorize them and then repeat them after me. Words: shirt, brown and lively (or rose, ball and key) (max 3 points for right words in right order)
+12. I would like you to count backward from 100 by sevens (93, 86, 79, 72, 65) Stop after five answers. (93: 1 point, 86: 1 point, 79: 1 point, 72: 1 point, 65: 1 point, the examiner is allowed to repeat the question if the examinee does not understand it. If the examinee makes a mistake but continues with a right answer i.e. subtracts 7 from the wrong number, it equals to one wrong answer. No paper nor pencil is allowed)
+13. What were the words that I asked you to memorize and repeat? (max 3 points: right words &amp; order)
+14. What are the names of these two objects? (showing wrist watch and then pencil) (2 points for correct answers)
+15. Now I will read out loud one sentence, repeat after me: "No ifs, ands, or buts." (1 point for the perfect sentence)
+16. Now I will give you a paper and ask you to do following tasks: Take the paper in your left hand, fold it in half, and put it on your knees (max 3 points for performing all three tasks)
+17. Please read this text and do what it says (written text: close your eyes) (1 point if the examinee successfully reads the text and does what it says)
+18. Make up and write a sentence about anything. (1 point if the sentence is understandable and includes at least a subject and predicate, writing errors do not affect the score). 
+19. Please copy this picture (two pentagons). (1 point if all 10 angles are present and two must intersect resulting in a square in the middle of the pentagons)
+Maximal score: 30 points.</t>
+  </si>
+  <si>
+    <t>Maximal score 30 points.</t>
+  </si>
+  <si>
+    <t>psy_mci_moca_score</t>
+  </si>
+  <si>
+    <t>MoCa score</t>
+  </si>
+  <si>
+    <t>phy_walking</t>
+  </si>
+  <si>
+    <t>Walking for leisure</t>
+  </si>
+  <si>
+    <t>Frequency of walking for leisure per week</t>
+  </si>
+  <si>
+    <t>Add a harmonization comment about differences between study-specific variable and DataSchema variable in source, wording, and/or collection format.</t>
+  </si>
+  <si>
+    <t>1 Less than once a week 
+2 1 to 5 times a week 
+3 6 times or more a week</t>
+  </si>
+  <si>
+    <t>The study collect frequency variables about "Walking or equivalent activity" and "Brisk walking or equivalent activity" that could include other type of low and moderate physical activity while the DataSchema variable is only about walking.</t>
+  </si>
+  <si>
+    <t>phy_occupational_pa</t>
+  </si>
+  <si>
+    <t>Occupational physical activity</t>
+  </si>
+  <si>
+    <t>Description of the typical physical activity required in the participant's occupation</t>
+  </si>
+  <si>
+    <t>1 Mostly sedentary-no physical demands
+2 Mostly standing or walking
+3 Standing and walking with lifting or carrying
+4 Strenuous physical work</t>
+  </si>
+  <si>
+    <t>phy_sport_participation</t>
+  </si>
+  <si>
+    <t>Sport participation</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant is participating in sport activity or not</t>
+  </si>
+  <si>
+    <t>When studies don't have a "other" category the "No" cannot be generated. In this situation only 1 and NA would be present. 
+Include any sport activity where the intensity was specified as being moderate or more.
+Add a harmonization comment about differences between study-specific variable and DataSchema variable in source, wording, and/or collection format.</t>
+  </si>
+  <si>
+    <t>0 No 
+1 Yes</t>
+  </si>
+  <si>
+    <t>phy_active_commuting</t>
+  </si>
+  <si>
+    <t>Active commuting</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant is engaging in active commuting</t>
+  </si>
+  <si>
+    <t>Considered commuting when at least 15 minutes.</t>
+  </si>
+  <si>
+    <t>pacommuting1</t>
+  </si>
+  <si>
+    <t>Daily commuting to work</t>
+  </si>
+  <si>
+    <t>RPA_Transport</t>
+  </si>
+  <si>
+    <t>Daily commuting to work. Self-reported. Questionnaire item: How much time daily do you use commuting to work by walking, running or cycling? Response options: 1=No exercise while commuting, 2=1min-15min, 3=15min-less than half an hour, 4=half an hour-less than an hour, 5=hour or more, 6=I'm not working right now.</t>
+  </si>
+  <si>
+    <t>1=No exercise while commuting
+2=1min-15min
+3=15min-less than half an hour
+4=half an hour-less than an hour 
+5=hour or more
+6=I'm not working right now.</t>
+  </si>
+  <si>
+    <t>recode(1=0; 2=0; 3=1; 4=1; 5=1; 6=NA; ELSE=NA)</t>
+  </si>
+  <si>
+    <t>phy_leisure_time</t>
+  </si>
+  <si>
+    <t>Leisure-time physical activity, including sport</t>
+  </si>
+  <si>
+    <t>Indicator of whether the participant is engaging in physical activity during leisure-time (including sport)</t>
+  </si>
+  <si>
+    <t>Include any physical activity where the intensity was specified as being moderate (or equivalent) or more.
+Add a harmonization comment about differences between study-specific variable and DataSchema variable in source, wording, and/or collection format.</t>
+  </si>
+  <si>
+    <t>pa_running1</t>
+  </si>
+  <si>
+    <t>weekly running or equivalent activity</t>
+  </si>
+  <si>
+    <t>RPA_Composite</t>
+  </si>
+  <si>
+    <t>Weekly running or equivalent activity. Self-reported. Questionnaire item: How much did you engage in following physical activities in a week during leisure time or commuting? 1. Running or equivalent activity. Response options for each of the physical activities: 1=Not at all, 2=Under ½ hour per week, 3=About an hour, 4=2-3 hours , 5=4 hours or more per week.</t>
+  </si>
+  <si>
+    <t>1 = Not at all 
+2 = Under ½ hour per week 
+3 = About an hour 
+4 = 2-3 hours 
+5 = 4 hours or more per week</t>
+  </si>
+  <si>
+    <t>The "No" responses was impossible to generate because the question was only about running or "equivalent activities".</t>
+  </si>
+  <si>
+    <t>recode(1=NA; 2=1; 3=1; 4=1; 5=1; ELSE=NA)</t>
+  </si>
+  <si>
+    <t>phy_mobility_limitation_SF36</t>
+  </si>
+  <si>
+    <t>Physical function SF36 subscale score</t>
+  </si>
+  <si>
+    <t>Total score of the physical function subscale of SF36</t>
+  </si>
+  <si>
+    <t>dis_vigorous1;
+dis_moderate1;
+dis_lift1;
+dis_climbseveral1;
+dis_climbone1;
+dis_bending1;
+dis_walk2km_1;
+dis_walk1km_1;
+dis_walk100m_1;
+dis_bath1</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>phy_SF36_nb_items</t>
+  </si>
+  <si>
+    <t>Number of non-missing items</t>
+  </si>
+  <si>
+    <t>Number of non-missing items in the SF36 physical function subscale</t>
+  </si>
+  <si>
+    <t>items</t>
+  </si>
+  <si>
+    <t>rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous1)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate1)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift1)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral1)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone1)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending1)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_1)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_1)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_1)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath1))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE)) %&gt;%
+mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
+  </si>
+  <si>
+    <t>Mlstr_harmo::comment</t>
+  </si>
+  <si>
+    <t>Mlstr_harmo::status</t>
+  </si>
+  <si>
+    <t>ifelse(rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous1)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate1)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift1)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral1)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone1)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending1)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_1)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_1)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_1)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath1))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE) &lt; 5,NA,
+rowMeans(mutate(.,
+temp_dis_vigorous1 = 50 * dis_vigorous1 - 50, 
+temp_dis_moderate1 = 50 * dis_moderate1 - 50,
+temp_dis_lift1 = 50 * dis_lift1 - 50,
+temp_dis_climbseveral1 = 50 * dis_climbseveral1 - 50,
+temp_dis_climbone1 = 50 * dis_climbone1 - 50,
+temp_dis_bending1 = 50 * dis_bending1 - 50,
+temp_dis_walk2km_1 = 50 * dis_walk2km_1 - 50,
+temp_dis_walk1km_1 = 50 * dis_walk1km_1 - 50,
+temp_dis_walk100m_1 = 50 * dis_walk100m_1 - 50,
+temp_dis_bath1 = 50 * dis_bath1 - 50) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE))</t>
+  </si>
+  <si>
+    <t>"FRA"</t>
   </si>
   <si>
     <t>case_when(
@@ -1761,14 +2536,14 @@
 !is.na(med8atc1) |
 !is.na(med9atc1)) &amp; 
 !grepl("^C02|^C03|^C07|^C08|^C09", med1atc1, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc2, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc4, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc5, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc6, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc7, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc8, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc9, ignore.case = TRUE) ~ 2L;
+!grepl("^C02|^C03|^C07|^C08|^C09", med2atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med3atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med4atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med5atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med6atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med7atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med8atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med9atc1, ignore.case = TRUE) ~ 2L;
 hypertension1 == 1 &amp;
 is.na(med1atc1) &amp;
 is.na(med2atc1) &amp;
@@ -1780,778 +2555,6 @@
 is.na(med8atc1) &amp;
 is.na(med9atc1) ~ 2L;
 ELSE ~ NA)</t>
-  </si>
-  <si>
-    <t>dis_msk_ever</t>
-  </si>
-  <si>
-    <t>Musculoskeletal diseases ever</t>
-  </si>
-  <si>
-    <t>Musculoskeletal diseases ever (osteoporosis, arthrosis, rheumatic disorder, osteoarthritis or rheumatism, rheumatoid arthritis, osteoarthritis, other arthritis, rheumatoid arthritis)</t>
-  </si>
-  <si>
-    <t>A "No" response can be assigned if the input variables were collected in Yes/No format. 
-If the input variables do not have a "No" response but are part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned.</t>
-  </si>
-  <si>
-    <t>osteoarthrosis1;
-osteoporosis1;
-sciatica1;
-rheumatoidarthritis1</t>
-  </si>
-  <si>
-    <t>Osteoarthrosis;
-Osteoporosis;
-Sciatica (lumbar disc herniation);
-Rheumatoid arthritis</t>
-  </si>
-  <si>
-    <t>HAM_LSI;HAM_LSI;HAM_LSI;HAM_LSI;HAM_LSI</t>
-  </si>
-  <si>
-    <t>Osteoarthrosis. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of osteoarthrosis? Response options: no, yes: previously, yes: currently;
-Osteoporosiss. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of osteoporosis? Response options: no, yes: previously, yes: currently;
-Sciatica (lumbar disc herniation). Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of sciatica (lumbar disc herniation)? Response options: no, yes: previously, yes: currently ;
-Fibromyalgia. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of fibromyalgia? Response options: no, yes: previously, yes: currently ;
-Rheumatoid arthritis. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of rheumatoid arthritis? Response options: no, yes: previously, yes: currently</t>
-  </si>
-  <si>
-    <t>Cohort profile: DOI: 10.1093/gerona/glaa193
-;Cohort profile: DOI: 10.1093/gerona/glaa193
-;Cohort profile: DOI: 10.1093/gerona/glaa193
-;Cohort profile: DOI: 10.1093/gerona/glaa193
-;Cohort profile: DOI: 10.1093/gerona/glaa193</t>
-  </si>
-  <si>
-    <t>case_when(
-osteoarthrosis1 %in% c(2, 3) | osteoporosis1 %in% c(2, 3) | sciatica1 %in% c(2, 3) | rheumatoidarthritis1 %in% c(2, 3) ~ 1L;
-osteoarthrosis1 == 1 &amp; osteoporosis1 == 1 &amp; sciatica1 == 1 &amp; rheumatoidarthritis1 == 1 ~ 0L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>dis_diabetes</t>
-  </si>
-  <si>
-    <t>Diabetes</t>
-  </si>
-  <si>
-    <t>Diabetes (including gestational diabetes and other types of diabetes but excluding impaired fasting glucose and impaired glucose tolerance)</t>
-  </si>
-  <si>
-    <t>A "No" response can be assigned if the input variables were collected in Yes/No format.
-If the input variables do not have a "No" response but are part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned. 
-Add a harmonization comment about any study-specific wording for collecting information about diabetes (e.g., only Type 2 diabetes, excluding gestational diabetes).</t>
-  </si>
-  <si>
-    <t>diabetes1</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of type 2 diabetes? Response options: no, yes: previously, yes: currently.</t>
-  </si>
-  <si>
-    <t>1 = no 
-2 = yes, previously 
-3 = yes, currently</t>
-  </si>
-  <si>
-    <t>The study only ask about type 2 diabetes.</t>
-  </si>
-  <si>
-    <t>dis_diabetes_type</t>
-  </si>
-  <si>
-    <t>Diabetes type</t>
-  </si>
-  <si>
-    <t>Add a harmonization comment about any study-specific wording for collecting information about diabetes (e.g., only Type 2 diabetes collected).</t>
-  </si>
-  <si>
-    <t>1 Type 1 
-2 Type 2 
-3 Other</t>
-  </si>
-  <si>
-    <t>dis_cancer_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever</t>
-  </si>
-  <si>
-    <t>When studies do not have an "other cancer" category, a "No" cannot be generated. In this situation only 1 and NA would be present.
-Add a harmonization comment about any decisions made for harmonization.
-"Presumed no" can be specified only if a general cancer disease option is present in a select all that apply question where at least another option is selected but not this one.</t>
-  </si>
-  <si>
-    <t>malignanttumor1</t>
-  </si>
-  <si>
-    <t>Malignant tumor (cancer)</t>
-  </si>
-  <si>
-    <t>Malignant tumor (cancer). Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of malignant tumor? Response options: no, yes: previously, yes: currently</t>
-  </si>
-  <si>
-    <t>dis_cancer_bladder_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Bladder</t>
-  </si>
-  <si>
-    <t>The "No" response can be attributed only in 2 situations:
-- There is a parent variable about having any cancer, collected in Yes/No format.
-- The input variables were collected in Yes/No format for this specific cancer type
-If the input variables do not have a "No" response but are part of select all that apply section where at least another cancer type is selected, then a "Presumed no" can be assigned.</t>
-  </si>
-  <si>
-    <t>case_when(
-malignanttumor1 == 1 ~ 0L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>dis_cancer_breast_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Breast</t>
-  </si>
-  <si>
-    <t>dis_cancer_cervix_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Cervix</t>
-  </si>
-  <si>
-    <t>dis_cancer_colorectal_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Colon-Rectum</t>
-  </si>
-  <si>
-    <t>dis_cancer_kidney_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Kidney</t>
-  </si>
-  <si>
-    <t>dis_cancer_throat_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Throat/Larynx-Pharynx</t>
-  </si>
-  <si>
-    <t>dis_cancer_leukaemia_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Leukaemia</t>
-  </si>
-  <si>
-    <t>dis_cancer_lung_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Lung</t>
-  </si>
-  <si>
-    <t>dis_cancer_lymphoma_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Lymphoma</t>
-  </si>
-  <si>
-    <t>dis_cancer_prostate_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Prostate</t>
-  </si>
-  <si>
-    <t>dis_cancer_skin_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Skin</t>
-  </si>
-  <si>
-    <t>dis_cancer_stomach_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Stomach</t>
-  </si>
-  <si>
-    <t>dis_cancer_testicle_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Testicle</t>
-  </si>
-  <si>
-    <t>dis_cancer_uterus_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Uterus</t>
-  </si>
-  <si>
-    <t>dis_cancer_brain_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Brain</t>
-  </si>
-  <si>
-    <t>dis_cancer_liver_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Liver</t>
-  </si>
-  <si>
-    <t>dis_cancer_ovary_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Ovary</t>
-  </si>
-  <si>
-    <t>dis_cancer_pancreas_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Pancreas</t>
-  </si>
-  <si>
-    <t>dis_cancer_thyroid_ever</t>
-  </si>
-  <si>
-    <t>Cancer ever - Thyroid</t>
-  </si>
-  <si>
-    <t>dis_hypercholesteromia_ever</t>
-  </si>
-  <si>
-    <t>Diagnosed hypercholesteromia</t>
-  </si>
-  <si>
-    <t>A "No" response can be assigned if the input variables were collected in Yes/No format.
-If the input variables do not have a "No" response but are part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned.</t>
-  </si>
-  <si>
-    <t>highcholesterol1</t>
-  </si>
-  <si>
-    <t>High cholesterol</t>
-  </si>
-  <si>
-    <t>High cholesterol. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of high cholesterol? Response options: no, yes: previously, yes: currently.</t>
-  </si>
-  <si>
-    <t>dis_depression</t>
-  </si>
-  <si>
-    <t>Depression</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant has depression or not</t>
-  </si>
-  <si>
-    <t>Accept self-reported condition but with a note. 
-A "No" response can be assigned if the input variables were collected in Yes/No format.
-If the input variable do not have a "No" response but is part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned.</t>
-  </si>
-  <si>
-    <t>depression1</t>
-  </si>
-  <si>
-    <t>depression</t>
-  </si>
-  <si>
-    <t>HAM_Depression</t>
-  </si>
-  <si>
-    <t>Depression. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of depression? Response options: no, yes: previously, yes: currently.</t>
-  </si>
-  <si>
-    <t>dis_alzheimers_dementia</t>
-  </si>
-  <si>
-    <t>Alzheimers/Dementia</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant has Alzheimers/Dementia</t>
-  </si>
-  <si>
-    <t>A "No" response can be assigned if the input variables were collected in Yes/No format.
-If the input variable do not have a "No" response but is part of select all that apply section where at least another condition is selected, then a "Presumed no" can be assigned.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 Has not been diagnosed with Alzheimers or other dementia 
-1 Has been diagnosed with Alzheimers or other dementia 
-2 Has presumably not been diagnosed with Alzheimers or other dementia 
-</t>
-  </si>
-  <si>
-    <t>alzheimer1</t>
-  </si>
-  <si>
-    <t>Alzheimer or other dementia</t>
-  </si>
-  <si>
-    <t>HAM_Alzheimers</t>
-  </si>
-  <si>
-    <t>Alzheimer or other dementia. Self-reported. Questionnaire item: Has a doctor/physician given you a diagnosis of Alzheimer or other dementia? Response options: no, yes: previously, yes: currently.</t>
-  </si>
-  <si>
-    <t>med_lipid_lowering_cur</t>
-  </si>
-  <si>
-    <t>Current use of lipid lowering medication</t>
-  </si>
-  <si>
-    <t>Only include if lipid lowering medication is currently being taken. A "No" response is possible only if a Yes/No question is collected.
-If the item is in a select all that apply where at least another item is selected then it is a "Presumed no".</t>
-  </si>
-  <si>
-    <t>med1atc1;
-med2atc1;
-med3atc1;
-med4atc1;
-med5atc1;
-med6atc1;
-med7atc1;
-med8atc1;
-med9atc1</t>
-  </si>
-  <si>
-    <t>Medication 1 to 5 atc code</t>
-  </si>
-  <si>
-    <t>HAM_MedUse</t>
-  </si>
-  <si>
-    <t>ATC code (Anatomical Therapeutic Chemical classification) of the medication used. Self-reported. Participants were asked to fill in a form names of medicines that they used. The full ATC code (A10BH01 etc). If the ATC code was not found, medicine was coded as follows: 
-X01= anti-hypertensive drug
-X02= diabetes drug
-X03= analgesic (painkiller)
-X04= cholesterol medicine
-X05= hormone replacement therapy
-X06= cortisone
-X07= vitamin 
-X08= nature cure/alternative remedy
-X10= something else/unspecified
-X11= antidepressant
-X12= allergy medicine
-X13= cortisone salve</t>
-  </si>
-  <si>
-    <t>ATC code (Anatomical Therapeutic Chemical classification)
-or if ATC code missing: 
-X01= anti-hypertensive drug
-X02= diabetes drug
-X03= analgesic (painkiller)
-X04= cholesterol medicine
-X05= hormone replacement therapy
-X06= cortisone
-X07= vitamin 
-X08= nature cure/alternative remedy
-X10= something else/unspecified
-X11= antidepressant
-X12= allergy medicine
-X13= cortisone salve</t>
-  </si>
-  <si>
-    <t>Derived from list of medication taken by the participant.</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc1 == "X04" ~ 1L;
-med2atc1 == "X04" ~ 1L;
-med3atc1 == "X04" ~ 1L;
-med4atc1 == "X04" ~ 1L;
-med5atc1 == "X04" ~ 1L;
-med6atc1 == "X04" ~ 1L;
-med7atc1 == "X04" ~ 1L;
-med8atc1 == "X04" ~ 1L;
-med9atc1 == "X04" ~ 1L;
-grepl("^C10", med1atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med2atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med3atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med4atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med5atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med6atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med7atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med8atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C10", med9atc1, ignore.case = TRUE) ~ 1L;
-!is.na(med1atc1) | !is.na(med2atc1) | !is.na(med3atc1) | !is.na(med4atc1) | !is.na(med5atc1) | !is.na(med6atc1) | !is.na(med7atc1) | !is.na(med8atc1) | !is.na(med9atc1) ~ 2L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>med_blood_pressure_cur</t>
-  </si>
-  <si>
-    <t>Current use of medication to manage blood pressure</t>
-  </si>
-  <si>
-    <t>Only include if medication for hypertension or high blood pressure is currently being taken. A "No" response is possible only if a Yes/No question is collected.
-The question must be separated from a hypertension or hbp diagnosis question.
-If the item is in a select all that apply where at least another item is selected then it is a "Presumed no".</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc1 == "X01" ~ 1L;
-med2atc1 == "X01" ~ 1L;
-med3atc1 == "X01" ~ 1L;
-med4atc1 == "X01" ~ 1L;
-med5atc1 == "X01" ~ 1L;
-med6atc1 == "X01" ~ 1L;
-med7atc1 == "X01" ~ 1L;
-med8atc1 == "X01" ~ 1L;
-med9atc1 == "X01" ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med1atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med2atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med3atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med4atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med5atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med6atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med7atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med8atc1, ignore.case = TRUE) ~ 1L;
-grepl("^C02|^C03|^C07|^C08|^C09", med9atc1, ignore.case = TRUE) ~ 1L;
-!is.na(med1atc1) | !is.na(med2atc1) | !is.na(med3atc1) | !is.na(med4atc1) | !is.na(med5atc1) | !is.na(med6atc1) | !is.na(med7atc1) | !is.na(med8atc1) | !is.na(med9atc1) ~ 2L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>med_diabetes_cur</t>
-  </si>
-  <si>
-    <t>Current use of medication for diabetes</t>
-  </si>
-  <si>
-    <t>If the item is in a select all that apply where at least another item is selected then it is a "Presumed no".</t>
-  </si>
-  <si>
-    <t>case_when(
-med1atc1 == "X02" ~ 1L;
-med2atc1 == "X02" ~ 1L;
-med3atc1 == "X02" ~ 1L;
-med4atc1 == "X02" ~ 1L;
-med5atc1 == "X02" ~ 1L;
-med6atc1 == "X02" ~ 1L;
-med7atc1 == "X02" ~ 1L;
-med8atc1 == "X02" ~ 1L;
-med9atc1 == "X02" ~ 1L;
-grepl("^A10", med1atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med2atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med3atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med4atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med5atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med6atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med7atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med8atc1, ignore.case = TRUE) ~ 1L;
-grepl("^A10", med9atc1, ignore.case = TRUE) ~ 1L;
-!is.na(med1atc1) | !is.na(med2atc1) | !is.na(med3atc1) | !is.na(med4atc1) | !is.na(med5atc1) | !is.na(med6atc1) | !is.na(med7atc1) | !is.na(med8atc1) | !is.na(med9atc1) ~ 2L;
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
-    <t>psy_dep_cesd20</t>
-  </si>
-  <si>
-    <t>CES-D (20 items) score</t>
-  </si>
-  <si>
-    <t>If the study has the total score variable, make sure the calculation is correct. Accepted score range is 0-60</t>
-  </si>
-  <si>
-    <t>psy_dep_cesd10</t>
-  </si>
-  <si>
-    <t>CES-D (10 items) score</t>
-  </si>
-  <si>
-    <t>If the study has the total score variable, make sure the calculation is correct. Accepted score range is 0-30</t>
-  </si>
-  <si>
-    <t>psy_dep_malaise</t>
-  </si>
-  <si>
-    <t>Malaise inventory (9 items) score</t>
-  </si>
-  <si>
-    <t>If the study has the total score variable, make sure the calculation is correct. Accepted score range is 0-24</t>
-  </si>
-  <si>
-    <t>psy_dep_kessler</t>
-  </si>
-  <si>
-    <t>Kessler psychological distress score</t>
-  </si>
-  <si>
-    <t>If the study has the total score variable, make sure the calculation is correct. Accepted score range is 10-50</t>
-  </si>
-  <si>
-    <t>psy_dep_phq9</t>
-  </si>
-  <si>
-    <t>PHQ-9 score</t>
-  </si>
-  <si>
-    <t>If the study has the total score variable, make sure the calculation is correct. Accepted score range is 0-27</t>
-  </si>
-  <si>
-    <t>psy_mci_mmse_score</t>
-  </si>
-  <si>
-    <t>MMSE score</t>
-  </si>
-  <si>
-    <t>mci1</t>
-  </si>
-  <si>
-    <t>Mild cognitive impairment</t>
-  </si>
-  <si>
-    <t>HAM_MildCI</t>
-  </si>
-  <si>
-    <t>Mild cognitive impairment was assessed during a clinical study visit with the Mini-Mental State Examination (MMSE) including items to assess cognitive function (orientation, attention, memory, language and visual-spatial skills) [doi: 10.1016/0022-3956(75)90026-6]. 
-More specific tasks/questions during the test: 
-1. What is the year? (wrong answer 0 points, right answer 1 point)
-2. What is the season? (wrong answer 0 points, right answer 1 point)
-3. What is the date? (wrong answer 0 points, right answer 1 point)
-4. What is the day of the week? (wrong answer 0 points, right answer 1 point)
-5. What is the month? (wrong answer 0 points, right answer 1 point)
-6. In what country we are now? (wrong answer 0 points, right answer 1 point)
-7. In what county we are now? (wrong answer 0 points, right answer 1 point)
-8. What is the name of this city? (wrong answer 0 points, right answer 1 point)
-9. What is this place where we are now? (wrong answer 0 points, right answer 1 point)
-10. In which floor we are now? (wrong answer 0 points, right answer 1 point)
-11. Soon I will say three words and you should memorize them and then repeat them after me. Words: shirt, brown and lively (or rose, ball and key) (max 3 points for right words in right order)
-12. I would like you to count backward from 100 by sevens (93, 86, 79, 72, 65) Stop after five answers. (93: 1 point, 86: 1 point, 79: 1 point, 72: 1 point, 65: 1 point, the examiner is allowed to repeat the question if the examinee does not understand it. If the examinee makes a mistake but continues with a right answer i.e. subtracts 7 from the wrong number, it equals to one wrong answer. No paper nor pencil is allowed)
-13. What were the words that I asked you to memorize and repeat? (max 3 points: right words &amp; order)
-14. What are the names of these two objects? (showing wrist watch and then pencil) (2 points for correct answers)
-15. Now I will read out loud one sentence, repeat after me: "No ifs, ands, or buts." (1 point for the perfect sentence)
-16. Now I will give you a paper and ask you to do following tasks: Take the paper in your left hand, fold it in half, and put it on your knees (max 3 points for performing all three tasks)
-17. Please read this text and do what it says (written text: close your eyes) (1 point if the examinee successfully reads the text and does what it says)
-18. Make up and write a sentence about anything. (1 point if the sentence is understandable and includes at least a subject and predicate, writing errors do not affect the score). 
-19. Please copy this picture (two pentagons). (1 point if all 10 angles are present and two must intersect resulting in a square in the middle of the pentagons)
-Maximal score: 30 points.</t>
-  </si>
-  <si>
-    <t>Maximal score 30 points.</t>
-  </si>
-  <si>
-    <t>psy_mci_moca_score</t>
-  </si>
-  <si>
-    <t>MoCa score</t>
-  </si>
-  <si>
-    <t>phy_walking</t>
-  </si>
-  <si>
-    <t>Walking for leisure</t>
-  </si>
-  <si>
-    <t>Frequency of walking for leisure per week</t>
-  </si>
-  <si>
-    <t>Add a harmonization comment about differences between study-specific variable and DataSchema variable in source, wording, and/or collection format.</t>
-  </si>
-  <si>
-    <t>1 Less than once a week 
-2 1 to 5 times a week 
-3 6 times or more a week</t>
-  </si>
-  <si>
-    <t>The study collect frequency variables about "Walking or equivalent activity" and "Brisk walking or equivalent activity" that could include other type of low and moderate physical activity while the DataSchema variable is only about walking.</t>
-  </si>
-  <si>
-    <t>phy_occupational_pa</t>
-  </si>
-  <si>
-    <t>Occupational physical activity</t>
-  </si>
-  <si>
-    <t>Description of the typical physical activity required in the participant's occupation</t>
-  </si>
-  <si>
-    <t>1 Mostly sedentary-no physical demands
-2 Mostly standing or walking
-3 Standing and walking with lifting or carrying
-4 Strenuous physical work</t>
-  </si>
-  <si>
-    <t>phy_sport_participation</t>
-  </si>
-  <si>
-    <t>Sport participation</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant is participating in sport activity or not</t>
-  </si>
-  <si>
-    <t>When studies don't have a "other" category the "No" cannot be generated. In this situation only 1 and NA would be present. 
-Include any sport activity where the intensity was specified as being moderate or more.
-Add a harmonization comment about differences between study-specific variable and DataSchema variable in source, wording, and/or collection format.</t>
-  </si>
-  <si>
-    <t>0 No 
-1 Yes</t>
-  </si>
-  <si>
-    <t>phy_active_commuting</t>
-  </si>
-  <si>
-    <t>Active commuting</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant is engaging in active commuting</t>
-  </si>
-  <si>
-    <t>Considered commuting when at least 15 minutes.</t>
-  </si>
-  <si>
-    <t>pacommuting1</t>
-  </si>
-  <si>
-    <t>Daily commuting to work</t>
-  </si>
-  <si>
-    <t>RPA_Transport</t>
-  </si>
-  <si>
-    <t>Daily commuting to work. Self-reported. Questionnaire item: How much time daily do you use commuting to work by walking, running or cycling? Response options: 1=No exercise while commuting, 2=1min-15min, 3=15min-less than half an hour, 4=half an hour-less than an hour, 5=hour or more, 6=I'm not working right now.</t>
-  </si>
-  <si>
-    <t>1=No exercise while commuting
-2=1min-15min
-3=15min-less than half an hour
-4=half an hour-less than an hour 
-5=hour or more
-6=I'm not working right now.</t>
-  </si>
-  <si>
-    <t>recode(1=0; 2=0; 3=1; 4=1; 5=1; 6=NA; ELSE=NA)</t>
-  </si>
-  <si>
-    <t>phy_leisure_time</t>
-  </si>
-  <si>
-    <t>Leisure-time physical activity, including sport</t>
-  </si>
-  <si>
-    <t>Indicator of whether the participant is engaging in physical activity during leisure-time (including sport)</t>
-  </si>
-  <si>
-    <t>Include any physical activity where the intensity was specified as being moderate (or equivalent) or more.
-Add a harmonization comment about differences between study-specific variable and DataSchema variable in source, wording, and/or collection format.</t>
-  </si>
-  <si>
-    <t>pa_running1</t>
-  </si>
-  <si>
-    <t>weekly running or equivalent activity</t>
-  </si>
-  <si>
-    <t>RPA_Composite</t>
-  </si>
-  <si>
-    <t>Weekly running or equivalent activity. Self-reported. Questionnaire item: How much did you engage in following physical activities in a week during leisure time or commuting? 1. Running or equivalent activity. Response options for each of the physical activities: 1=Not at all, 2=Under ½ hour per week, 3=About an hour, 4=2-3 hours , 5=4 hours or more per week.</t>
-  </si>
-  <si>
-    <t>1 = Not at all 
-2 = Under ½ hour per week 
-3 = About an hour 
-4 = 2-3 hours 
-5 = 4 hours or more per week</t>
-  </si>
-  <si>
-    <t>The "No" responses was impossible to generate because the question was only about running or "equivalent activities".</t>
-  </si>
-  <si>
-    <t>recode(1=NA; 2=1; 3=1; 4=1; 5=1; ELSE=NA)</t>
-  </si>
-  <si>
-    <t>phy_mobility_limitation_SF36</t>
-  </si>
-  <si>
-    <t>Physical function SF36 subscale score</t>
-  </si>
-  <si>
-    <t>Total score of the physical function subscale of SF36</t>
-  </si>
-  <si>
-    <t>dis_vigorous1;
-dis_moderate1;
-dis_lift1;
-dis_climbseveral1;
-dis_climbone1;
-dis_bending1;
-dis_walk2km_1;
-dis_walk1km_1;
-dis_walk100m_1;
-dis_bath1</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>ifelse(rowSums(mutate(.,
-temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous1)), 
-temp_dis_moderate1 = as.numeric(!is.na(dis_moderate1)),
-temp_dis_lift1 = as.numeric(!is.na(dis_lift1)),
-temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral1)),
-temp_dis_climbone1 = as.numeric(!is.na(dis_climbone1)),
-temp_dis_bending1 = as.numeric(!is.na(dis_bending1)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_1)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_1)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_1)),
-temp_dis_bath1 = as.numeric(!is.na(dis_bath1))) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE)) &lt; 5,NA,
-rowMeans(mutate(.,
-temp_dis_vigorous1 = 50 * dis_vigorous1 - 50, 
-temp_dis_moderate1 = 50 * dis_moderate1 - 50,
-temp_dis_lift1 = 50 * dis_lift1 - 50,
-temp_dis_climbseveral1 = 50 * dis_climbseveral1 - 50,
-temp_dis_climbone1 = 50 * dis_climbone1 - 50,
-temp_dis_bending1 = 50 * dis_bending1 - 50,
-temp_dis_walk2km_1 = 50 * dis_walk2km_1 - 50,
-temp_dis_walk1km_1 = 50 * dis_walk1km_1 - 50,
-temp_dis_walk100m_1 = 50 * dis_walk100m_1 - 50,
-temp_dis_bath1 = 50 * dis_bath1 - 50) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE))</t>
-  </si>
-  <si>
-    <t>phy_SF36_nb_items</t>
-  </si>
-  <si>
-    <t>Number of non-missing items</t>
-  </si>
-  <si>
-    <t>Number of non-missing items in the SF36 physical function subscale</t>
-  </si>
-  <si>
-    <t>items</t>
-  </si>
-  <si>
-    <t>rowSums(mutate(.,
-temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous1)), 
-temp_dis_moderate1 = as.numeric(!is.na(dis_moderate1)),
-temp_dis_lift1 = as.numeric(!is.na(dis_lift1)),
-temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral1)),
-temp_dis_climbone1 = as.numeric(!is.na(dis_climbone1)),
-temp_dis_bending1 = as.numeric(!is.na(dis_bending1)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_1)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_1)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_1)),
-temp_dis_bath1 = as.numeric(!is.na(dis_bath1))) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE)) %&gt;%
-mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
-  </si>
-  <si>
-    <t>Mlstr_harmo::comment</t>
-  </si>
-  <si>
-    <t>Mlstr_harmo::status</t>
   </si>
 </sst>
 </file>
@@ -2928,6 +2931,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DD590CF-60F3-474A-8CF6-CAFB2AFA3E98}">
   <dimension ref="A1:X122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="24" max="24" width="89.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2988,10 +2994,10 @@
         <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="U1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="V1" t="s">
         <v>19</v>
@@ -3088,13 +3094,13 @@
         <v>34</v>
       </c>
       <c r="V3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="W3" t="s">
         <v>43</v>
       </c>
       <c r="X3" t="s">
-        <v>22</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -3126,13 +3132,13 @@
         <v>34</v>
       </c>
       <c r="V4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="W4" t="s">
         <v>43</v>
       </c>
       <c r="X4" t="s">
-        <v>22</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -3164,7 +3170,7 @@
         <v>34</v>
       </c>
       <c r="V5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="W5" t="s">
         <v>43</v>
@@ -3282,7 +3288,7 @@
         <v>42</v>
       </c>
       <c r="W7" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="X7" t="s">
         <v>72</v>
@@ -6900,7 +6906,7 @@
         <v>420</v>
       </c>
       <c r="X79" s="1" t="s">
-        <v>486</v>
+        <v>670</v>
       </c>
     </row>
     <row r="80" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6911,37 +6917,37 @@
         <v>22</v>
       </c>
       <c r="C80" t="s">
+        <v>486</v>
+      </c>
+      <c r="D80" t="s">
         <v>487</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>488</v>
-      </c>
-      <c r="E80" t="s">
-        <v>489</v>
       </c>
       <c r="F80" t="s">
         <v>49</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K80" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="L80" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="M80" t="s">
         <v>492</v>
       </c>
-      <c r="M80" t="s">
+      <c r="N80" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="N80" s="1" t="s">
+      <c r="P80" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="P80" s="1" t="s">
-        <v>495</v>
       </c>
       <c r="Q80" t="s">
         <v>32</v>
@@ -6959,7 +6965,7 @@
         <v>420</v>
       </c>
       <c r="X80" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="81" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -6970,34 +6976,34 @@
         <v>22</v>
       </c>
       <c r="C81" t="s">
+        <v>496</v>
+      </c>
+      <c r="D81" t="s">
         <v>497</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>498</v>
-      </c>
-      <c r="E81" t="s">
-        <v>499</v>
       </c>
       <c r="F81" t="s">
         <v>49</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J81" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K81" t="s">
+        <v>500</v>
+      </c>
+      <c r="L81" t="s">
         <v>501</v>
-      </c>
-      <c r="L81" t="s">
-        <v>502</v>
       </c>
       <c r="M81" t="s">
         <v>456</v>
       </c>
       <c r="N81" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="P81" t="s">
         <v>31</v>
@@ -7006,10 +7012,10 @@
         <v>32</v>
       </c>
       <c r="R81" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="T81" t="s">
         <v>504</v>
-      </c>
-      <c r="T81" t="s">
-        <v>505</v>
       </c>
       <c r="U81" t="s">
         <v>89</v>
@@ -7032,34 +7038,34 @@
         <v>22</v>
       </c>
       <c r="C82" t="s">
+        <v>505</v>
+      </c>
+      <c r="D82" t="s">
         <v>506</v>
       </c>
-      <c r="D82" t="s">
-        <v>507</v>
-      </c>
       <c r="E82" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F82" t="s">
         <v>49</v>
       </c>
       <c r="I82" t="s">
+        <v>507</v>
+      </c>
+      <c r="J82" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="K82" t="s">
+        <v>500</v>
+      </c>
+      <c r="L82" t="s">
         <v>501</v>
-      </c>
-      <c r="L82" t="s">
-        <v>502</v>
       </c>
       <c r="M82" t="s">
         <v>456</v>
       </c>
       <c r="N82" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="P82" t="s">
         <v>31</v>
@@ -7068,10 +7074,10 @@
         <v>32</v>
       </c>
       <c r="R82" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="T82" t="s">
         <v>504</v>
-      </c>
-      <c r="T82" t="s">
-        <v>505</v>
       </c>
       <c r="U82" t="s">
         <v>89</v>
@@ -7094,34 +7100,34 @@
         <v>22</v>
       </c>
       <c r="C83" t="s">
+        <v>509</v>
+      </c>
+      <c r="D83" t="s">
         <v>510</v>
       </c>
-      <c r="D83" t="s">
-        <v>511</v>
-      </c>
       <c r="E83" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F83" t="s">
         <v>49</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J83" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K83" t="s">
+        <v>512</v>
+      </c>
+      <c r="L83" t="s">
         <v>513</v>
-      </c>
-      <c r="L83" t="s">
-        <v>514</v>
       </c>
       <c r="M83" t="s">
         <v>456</v>
       </c>
       <c r="N83" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P83" t="s">
         <v>31</v>
@@ -7130,7 +7136,7 @@
         <v>32</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U83" t="s">
         <v>34</v>
@@ -7153,34 +7159,34 @@
         <v>22</v>
       </c>
       <c r="C84" t="s">
+        <v>515</v>
+      </c>
+      <c r="D84" t="s">
         <v>516</v>
       </c>
-      <c r="D84" t="s">
-        <v>517</v>
-      </c>
       <c r="E84" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F84" t="s">
         <v>49</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J84" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K84" t="s">
+        <v>512</v>
+      </c>
+      <c r="L84" t="s">
         <v>513</v>
-      </c>
-      <c r="L84" t="s">
-        <v>514</v>
       </c>
       <c r="M84" t="s">
         <v>456</v>
       </c>
       <c r="N84" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P84" t="s">
         <v>31</v>
@@ -7189,7 +7195,7 @@
         <v>32</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U84" t="s">
         <v>34</v>
@@ -7201,7 +7207,7 @@
         <v>420</v>
       </c>
       <c r="X84" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="85" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7212,34 +7218,34 @@
         <v>22</v>
       </c>
       <c r="C85" t="s">
+        <v>519</v>
+      </c>
+      <c r="D85" t="s">
         <v>520</v>
       </c>
-      <c r="D85" t="s">
-        <v>521</v>
-      </c>
       <c r="E85" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F85" t="s">
         <v>49</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K85" t="s">
+        <v>512</v>
+      </c>
+      <c r="L85" t="s">
         <v>513</v>
-      </c>
-      <c r="L85" t="s">
-        <v>514</v>
       </c>
       <c r="M85" t="s">
         <v>456</v>
       </c>
       <c r="N85" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P85" t="s">
         <v>31</v>
@@ -7248,7 +7254,7 @@
         <v>32</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U85" t="s">
         <v>34</v>
@@ -7260,7 +7266,7 @@
         <v>420</v>
       </c>
       <c r="X85" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7271,34 +7277,34 @@
         <v>22</v>
       </c>
       <c r="C86" t="s">
+        <v>521</v>
+      </c>
+      <c r="D86" t="s">
         <v>522</v>
       </c>
-      <c r="D86" t="s">
-        <v>523</v>
-      </c>
       <c r="E86" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F86" t="s">
         <v>49</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K86" t="s">
+        <v>512</v>
+      </c>
+      <c r="L86" t="s">
         <v>513</v>
-      </c>
-      <c r="L86" t="s">
-        <v>514</v>
       </c>
       <c r="M86" t="s">
         <v>456</v>
       </c>
       <c r="N86" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P86" t="s">
         <v>31</v>
@@ -7307,7 +7313,7 @@
         <v>32</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U86" t="s">
         <v>34</v>
@@ -7319,7 +7325,7 @@
         <v>420</v>
       </c>
       <c r="X86" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="87" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7330,34 +7336,34 @@
         <v>22</v>
       </c>
       <c r="C87" t="s">
+        <v>523</v>
+      </c>
+      <c r="D87" t="s">
         <v>524</v>
       </c>
-      <c r="D87" t="s">
-        <v>525</v>
-      </c>
       <c r="E87" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F87" t="s">
         <v>49</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K87" t="s">
+        <v>512</v>
+      </c>
+      <c r="L87" t="s">
         <v>513</v>
-      </c>
-      <c r="L87" t="s">
-        <v>514</v>
       </c>
       <c r="M87" t="s">
         <v>456</v>
       </c>
       <c r="N87" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P87" t="s">
         <v>31</v>
@@ -7366,7 +7372,7 @@
         <v>32</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U87" t="s">
         <v>34</v>
@@ -7378,7 +7384,7 @@
         <v>420</v>
       </c>
       <c r="X87" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="88" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7389,34 +7395,34 @@
         <v>22</v>
       </c>
       <c r="C88" t="s">
+        <v>525</v>
+      </c>
+      <c r="D88" t="s">
         <v>526</v>
       </c>
-      <c r="D88" t="s">
-        <v>527</v>
-      </c>
       <c r="E88" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F88" t="s">
         <v>49</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K88" t="s">
+        <v>512</v>
+      </c>
+      <c r="L88" t="s">
         <v>513</v>
-      </c>
-      <c r="L88" t="s">
-        <v>514</v>
       </c>
       <c r="M88" t="s">
         <v>456</v>
       </c>
       <c r="N88" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P88" t="s">
         <v>31</v>
@@ -7425,7 +7431,7 @@
         <v>32</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U88" t="s">
         <v>34</v>
@@ -7437,7 +7443,7 @@
         <v>420</v>
       </c>
       <c r="X88" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="89" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7448,34 +7454,34 @@
         <v>22</v>
       </c>
       <c r="C89" t="s">
+        <v>527</v>
+      </c>
+      <c r="D89" t="s">
         <v>528</v>
       </c>
-      <c r="D89" t="s">
-        <v>529</v>
-      </c>
       <c r="E89" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F89" t="s">
         <v>49</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K89" t="s">
+        <v>512</v>
+      </c>
+      <c r="L89" t="s">
         <v>513</v>
-      </c>
-      <c r="L89" t="s">
-        <v>514</v>
       </c>
       <c r="M89" t="s">
         <v>456</v>
       </c>
       <c r="N89" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P89" t="s">
         <v>31</v>
@@ -7484,7 +7490,7 @@
         <v>32</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U89" t="s">
         <v>34</v>
@@ -7496,7 +7502,7 @@
         <v>420</v>
       </c>
       <c r="X89" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7507,34 +7513,34 @@
         <v>22</v>
       </c>
       <c r="C90" t="s">
+        <v>529</v>
+      </c>
+      <c r="D90" t="s">
         <v>530</v>
       </c>
-      <c r="D90" t="s">
-        <v>531</v>
-      </c>
       <c r="E90" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F90" t="s">
         <v>49</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K90" t="s">
+        <v>512</v>
+      </c>
+      <c r="L90" t="s">
         <v>513</v>
-      </c>
-      <c r="L90" t="s">
-        <v>514</v>
       </c>
       <c r="M90" t="s">
         <v>456</v>
       </c>
       <c r="N90" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P90" t="s">
         <v>31</v>
@@ -7543,7 +7549,7 @@
         <v>32</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U90" t="s">
         <v>34</v>
@@ -7555,7 +7561,7 @@
         <v>420</v>
       </c>
       <c r="X90" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7566,34 +7572,34 @@
         <v>22</v>
       </c>
       <c r="C91" t="s">
+        <v>531</v>
+      </c>
+      <c r="D91" t="s">
         <v>532</v>
       </c>
-      <c r="D91" t="s">
-        <v>533</v>
-      </c>
       <c r="E91" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F91" t="s">
         <v>49</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K91" t="s">
+        <v>512</v>
+      </c>
+      <c r="L91" t="s">
         <v>513</v>
-      </c>
-      <c r="L91" t="s">
-        <v>514</v>
       </c>
       <c r="M91" t="s">
         <v>456</v>
       </c>
       <c r="N91" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P91" t="s">
         <v>31</v>
@@ -7602,7 +7608,7 @@
         <v>32</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U91" t="s">
         <v>34</v>
@@ -7614,7 +7620,7 @@
         <v>420</v>
       </c>
       <c r="X91" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7625,34 +7631,34 @@
         <v>22</v>
       </c>
       <c r="C92" t="s">
+        <v>533</v>
+      </c>
+      <c r="D92" t="s">
         <v>534</v>
       </c>
-      <c r="D92" t="s">
-        <v>535</v>
-      </c>
       <c r="E92" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F92" t="s">
         <v>49</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K92" t="s">
+        <v>512</v>
+      </c>
+      <c r="L92" t="s">
         <v>513</v>
-      </c>
-      <c r="L92" t="s">
-        <v>514</v>
       </c>
       <c r="M92" t="s">
         <v>456</v>
       </c>
       <c r="N92" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P92" t="s">
         <v>31</v>
@@ -7661,7 +7667,7 @@
         <v>32</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U92" t="s">
         <v>34</v>
@@ -7673,7 +7679,7 @@
         <v>420</v>
       </c>
       <c r="X92" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="93" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7684,34 +7690,34 @@
         <v>22</v>
       </c>
       <c r="C93" t="s">
+        <v>535</v>
+      </c>
+      <c r="D93" t="s">
         <v>536</v>
       </c>
-      <c r="D93" t="s">
-        <v>537</v>
-      </c>
       <c r="E93" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F93" t="s">
         <v>49</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K93" t="s">
+        <v>512</v>
+      </c>
+      <c r="L93" t="s">
         <v>513</v>
-      </c>
-      <c r="L93" t="s">
-        <v>514</v>
       </c>
       <c r="M93" t="s">
         <v>456</v>
       </c>
       <c r="N93" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P93" t="s">
         <v>31</v>
@@ -7720,7 +7726,7 @@
         <v>32</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U93" t="s">
         <v>34</v>
@@ -7732,7 +7738,7 @@
         <v>420</v>
       </c>
       <c r="X93" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="94" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7743,34 +7749,34 @@
         <v>22</v>
       </c>
       <c r="C94" t="s">
+        <v>537</v>
+      </c>
+      <c r="D94" t="s">
         <v>538</v>
       </c>
-      <c r="D94" t="s">
-        <v>539</v>
-      </c>
       <c r="E94" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F94" t="s">
         <v>49</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K94" t="s">
+        <v>512</v>
+      </c>
+      <c r="L94" t="s">
         <v>513</v>
-      </c>
-      <c r="L94" t="s">
-        <v>514</v>
       </c>
       <c r="M94" t="s">
         <v>456</v>
       </c>
       <c r="N94" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P94" t="s">
         <v>31</v>
@@ -7779,7 +7785,7 @@
         <v>32</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U94" t="s">
         <v>34</v>
@@ -7791,7 +7797,7 @@
         <v>420</v>
       </c>
       <c r="X94" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7802,34 +7808,34 @@
         <v>22</v>
       </c>
       <c r="C95" t="s">
+        <v>539</v>
+      </c>
+      <c r="D95" t="s">
         <v>540</v>
       </c>
-      <c r="D95" t="s">
-        <v>541</v>
-      </c>
       <c r="E95" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F95" t="s">
         <v>49</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K95" t="s">
+        <v>512</v>
+      </c>
+      <c r="L95" t="s">
         <v>513</v>
-      </c>
-      <c r="L95" t="s">
-        <v>514</v>
       </c>
       <c r="M95" t="s">
         <v>456</v>
       </c>
       <c r="N95" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P95" t="s">
         <v>31</v>
@@ -7838,7 +7844,7 @@
         <v>32</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U95" t="s">
         <v>34</v>
@@ -7850,7 +7856,7 @@
         <v>420</v>
       </c>
       <c r="X95" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="96" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7861,34 +7867,34 @@
         <v>22</v>
       </c>
       <c r="C96" t="s">
+        <v>541</v>
+      </c>
+      <c r="D96" t="s">
         <v>542</v>
       </c>
-      <c r="D96" t="s">
-        <v>543</v>
-      </c>
       <c r="E96" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F96" t="s">
         <v>49</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K96" t="s">
+        <v>512</v>
+      </c>
+      <c r="L96" t="s">
         <v>513</v>
-      </c>
-      <c r="L96" t="s">
-        <v>514</v>
       </c>
       <c r="M96" t="s">
         <v>456</v>
       </c>
       <c r="N96" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P96" t="s">
         <v>31</v>
@@ -7897,7 +7903,7 @@
         <v>32</v>
       </c>
       <c r="R96" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U96" t="s">
         <v>34</v>
@@ -7909,7 +7915,7 @@
         <v>420</v>
       </c>
       <c r="X96" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="97" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7920,34 +7926,34 @@
         <v>22</v>
       </c>
       <c r="C97" t="s">
+        <v>543</v>
+      </c>
+      <c r="D97" t="s">
         <v>544</v>
       </c>
-      <c r="D97" t="s">
-        <v>545</v>
-      </c>
       <c r="E97" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F97" t="s">
         <v>49</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J97" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K97" t="s">
+        <v>512</v>
+      </c>
+      <c r="L97" t="s">
         <v>513</v>
-      </c>
-      <c r="L97" t="s">
-        <v>514</v>
       </c>
       <c r="M97" t="s">
         <v>456</v>
       </c>
       <c r="N97" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P97" t="s">
         <v>31</v>
@@ -7956,7 +7962,7 @@
         <v>32</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U97" t="s">
         <v>34</v>
@@ -7968,7 +7974,7 @@
         <v>420</v>
       </c>
       <c r="X97" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="98" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -7979,34 +7985,34 @@
         <v>22</v>
       </c>
       <c r="C98" t="s">
+        <v>545</v>
+      </c>
+      <c r="D98" t="s">
         <v>546</v>
       </c>
-      <c r="D98" t="s">
-        <v>547</v>
-      </c>
       <c r="E98" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F98" t="s">
         <v>49</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K98" t="s">
+        <v>512</v>
+      </c>
+      <c r="L98" t="s">
         <v>513</v>
-      </c>
-      <c r="L98" t="s">
-        <v>514</v>
       </c>
       <c r="M98" t="s">
         <v>456</v>
       </c>
       <c r="N98" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P98" t="s">
         <v>31</v>
@@ -8015,7 +8021,7 @@
         <v>32</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U98" t="s">
         <v>34</v>
@@ -8027,7 +8033,7 @@
         <v>420</v>
       </c>
       <c r="X98" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8038,34 +8044,34 @@
         <v>22</v>
       </c>
       <c r="C99" t="s">
+        <v>547</v>
+      </c>
+      <c r="D99" t="s">
         <v>548</v>
       </c>
-      <c r="D99" t="s">
-        <v>549</v>
-      </c>
       <c r="E99" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F99" t="s">
         <v>49</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K99" t="s">
+        <v>512</v>
+      </c>
+      <c r="L99" t="s">
         <v>513</v>
-      </c>
-      <c r="L99" t="s">
-        <v>514</v>
       </c>
       <c r="M99" t="s">
         <v>456</v>
       </c>
       <c r="N99" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P99" t="s">
         <v>31</v>
@@ -8074,7 +8080,7 @@
         <v>32</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U99" t="s">
         <v>34</v>
@@ -8086,7 +8092,7 @@
         <v>420</v>
       </c>
       <c r="X99" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="100" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8097,34 +8103,34 @@
         <v>22</v>
       </c>
       <c r="C100" t="s">
+        <v>549</v>
+      </c>
+      <c r="D100" t="s">
         <v>550</v>
       </c>
-      <c r="D100" t="s">
-        <v>551</v>
-      </c>
       <c r="E100" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F100" t="s">
         <v>49</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K100" t="s">
+        <v>512</v>
+      </c>
+      <c r="L100" t="s">
         <v>513</v>
-      </c>
-      <c r="L100" t="s">
-        <v>514</v>
       </c>
       <c r="M100" t="s">
         <v>456</v>
       </c>
       <c r="N100" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P100" t="s">
         <v>31</v>
@@ -8133,7 +8139,7 @@
         <v>32</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U100" t="s">
         <v>34</v>
@@ -8145,7 +8151,7 @@
         <v>420</v>
       </c>
       <c r="X100" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8156,34 +8162,34 @@
         <v>22</v>
       </c>
       <c r="C101" t="s">
+        <v>551</v>
+      </c>
+      <c r="D101" t="s">
         <v>552</v>
       </c>
-      <c r="D101" t="s">
-        <v>553</v>
-      </c>
       <c r="E101" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F101" t="s">
         <v>49</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K101" t="s">
+        <v>512</v>
+      </c>
+      <c r="L101" t="s">
         <v>513</v>
-      </c>
-      <c r="L101" t="s">
-        <v>514</v>
       </c>
       <c r="M101" t="s">
         <v>456</v>
       </c>
       <c r="N101" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P101" t="s">
         <v>31</v>
@@ -8192,7 +8198,7 @@
         <v>32</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U101" t="s">
         <v>34</v>
@@ -8204,7 +8210,7 @@
         <v>420</v>
       </c>
       <c r="X101" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="102" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8215,34 +8221,34 @@
         <v>22</v>
       </c>
       <c r="C102" t="s">
+        <v>553</v>
+      </c>
+      <c r="D102" t="s">
         <v>554</v>
       </c>
-      <c r="D102" t="s">
-        <v>555</v>
-      </c>
       <c r="E102" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F102" t="s">
         <v>49</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K102" t="s">
+        <v>512</v>
+      </c>
+      <c r="L102" t="s">
         <v>513</v>
-      </c>
-      <c r="L102" t="s">
-        <v>514</v>
       </c>
       <c r="M102" t="s">
         <v>456</v>
       </c>
       <c r="N102" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P102" t="s">
         <v>31</v>
@@ -8251,7 +8257,7 @@
         <v>32</v>
       </c>
       <c r="R102" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U102" t="s">
         <v>34</v>
@@ -8263,7 +8269,7 @@
         <v>420</v>
       </c>
       <c r="X102" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="103" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8274,34 +8280,34 @@
         <v>22</v>
       </c>
       <c r="C103" t="s">
+        <v>555</v>
+      </c>
+      <c r="D103" t="s">
         <v>556</v>
       </c>
-      <c r="D103" t="s">
-        <v>557</v>
-      </c>
       <c r="E103" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F103" t="s">
         <v>49</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="J103" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K103" t="s">
+        <v>558</v>
+      </c>
+      <c r="L103" t="s">
         <v>559</v>
-      </c>
-      <c r="L103" t="s">
-        <v>560</v>
       </c>
       <c r="M103" t="s">
         <v>456</v>
       </c>
       <c r="N103" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="P103" t="s">
         <v>31</v>
@@ -8310,7 +8316,7 @@
         <v>32</v>
       </c>
       <c r="R103" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U103" t="s">
         <v>34</v>
@@ -8333,34 +8339,34 @@
         <v>22</v>
       </c>
       <c r="C104" t="s">
+        <v>561</v>
+      </c>
+      <c r="D104" t="s">
         <v>562</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>563</v>
-      </c>
-      <c r="E104" t="s">
-        <v>564</v>
       </c>
       <c r="F104" t="s">
         <v>49</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="J104" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K104" t="s">
+        <v>565</v>
+      </c>
+      <c r="L104" t="s">
         <v>566</v>
       </c>
-      <c r="L104" t="s">
+      <c r="M104" t="s">
         <v>567</v>
       </c>
-      <c r="M104" t="s">
+      <c r="N104" t="s">
         <v>568</v>
-      </c>
-      <c r="N104" t="s">
-        <v>569</v>
       </c>
       <c r="P104" t="s">
         <v>31</v>
@@ -8369,7 +8375,7 @@
         <v>32</v>
       </c>
       <c r="R104" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U104" t="s">
         <v>34</v>
@@ -8392,34 +8398,34 @@
         <v>22</v>
       </c>
       <c r="C105" t="s">
+        <v>569</v>
+      </c>
+      <c r="D105" t="s">
         <v>570</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>571</v>
-      </c>
-      <c r="E105" t="s">
-        <v>572</v>
       </c>
       <c r="F105" t="s">
         <v>49</v>
       </c>
       <c r="I105" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="J105" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="J105" s="1" t="s">
+      <c r="K105" t="s">
         <v>574</v>
       </c>
-      <c r="K105" t="s">
+      <c r="L105" t="s">
         <v>575</v>
       </c>
-      <c r="L105" t="s">
+      <c r="M105" t="s">
         <v>576</v>
       </c>
-      <c r="M105" t="s">
+      <c r="N105" t="s">
         <v>577</v>
-      </c>
-      <c r="N105" t="s">
-        <v>578</v>
       </c>
       <c r="P105" t="s">
         <v>31</v>
@@ -8428,7 +8434,7 @@
         <v>32</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="U105" t="s">
         <v>34</v>
@@ -8451,34 +8457,34 @@
         <v>22</v>
       </c>
       <c r="C106" t="s">
+        <v>578</v>
+      </c>
+      <c r="D106" t="s">
         <v>579</v>
       </c>
-      <c r="D106" t="s">
-        <v>580</v>
-      </c>
       <c r="E106" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F106" t="s">
         <v>49</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="J106" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K106" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="L106" t="s">
         <v>582</v>
       </c>
-      <c r="L106" t="s">
+      <c r="M106" t="s">
         <v>583</v>
       </c>
-      <c r="M106" t="s">
+      <c r="N106" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="N106" s="1" t="s">
-        <v>585</v>
       </c>
       <c r="P106" t="s">
         <v>31</v>
@@ -8487,10 +8493,10 @@
         <v>32</v>
       </c>
       <c r="R106" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="T106" t="s">
         <v>586</v>
-      </c>
-      <c r="T106" t="s">
-        <v>587</v>
       </c>
       <c r="U106" t="s">
         <v>34</v>
@@ -8502,7 +8508,7 @@
         <v>420</v>
       </c>
       <c r="X106" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="107" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8513,34 +8519,34 @@
         <v>22</v>
       </c>
       <c r="C107" t="s">
+        <v>588</v>
+      </c>
+      <c r="D107" t="s">
         <v>589</v>
       </c>
-      <c r="D107" t="s">
-        <v>590</v>
-      </c>
       <c r="E107" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F107" t="s">
         <v>49</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J107" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K107" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="L107" t="s">
         <v>582</v>
       </c>
-      <c r="L107" t="s">
+      <c r="M107" t="s">
         <v>583</v>
       </c>
-      <c r="M107" t="s">
+      <c r="N107" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="N107" s="1" t="s">
-        <v>585</v>
       </c>
       <c r="P107" t="s">
         <v>31</v>
@@ -8549,10 +8555,10 @@
         <v>32</v>
       </c>
       <c r="R107" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="T107" t="s">
         <v>586</v>
-      </c>
-      <c r="T107" t="s">
-        <v>587</v>
       </c>
       <c r="U107" t="s">
         <v>34</v>
@@ -8564,7 +8570,7 @@
         <v>420</v>
       </c>
       <c r="X107" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="108" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -8575,34 +8581,34 @@
         <v>22</v>
       </c>
       <c r="C108" t="s">
+        <v>592</v>
+      </c>
+      <c r="D108" t="s">
         <v>593</v>
       </c>
-      <c r="D108" t="s">
-        <v>594</v>
-      </c>
       <c r="E108" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F108" t="s">
         <v>49</v>
       </c>
       <c r="I108" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="J108" s="1" t="s">
         <v>436</v>
       </c>
       <c r="K108" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="L108" t="s">
         <v>582</v>
       </c>
-      <c r="L108" t="s">
+      <c r="M108" t="s">
         <v>583</v>
       </c>
-      <c r="M108" t="s">
+      <c r="N108" s="1" t="s">
         <v>584</v>
-      </c>
-      <c r="N108" s="1" t="s">
-        <v>585</v>
       </c>
       <c r="P108" t="s">
         <v>31</v>
@@ -8611,10 +8617,10 @@
         <v>32</v>
       </c>
       <c r="R108" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="T108" t="s">
         <v>586</v>
-      </c>
-      <c r="T108" t="s">
-        <v>587</v>
       </c>
       <c r="U108" t="s">
         <v>34</v>
@@ -8626,7 +8632,7 @@
         <v>420</v>
       </c>
       <c r="X108" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.25">
@@ -8637,19 +8643,19 @@
         <v>22</v>
       </c>
       <c r="C109" t="s">
+        <v>596</v>
+      </c>
+      <c r="D109" t="s">
         <v>597</v>
       </c>
-      <c r="D109" t="s">
-        <v>598</v>
-      </c>
       <c r="E109" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F109" t="s">
         <v>49</v>
       </c>
       <c r="I109" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K109" t="s">
         <v>41</v>
@@ -8675,19 +8681,19 @@
         <v>22</v>
       </c>
       <c r="C110" t="s">
+        <v>599</v>
+      </c>
+      <c r="D110" t="s">
         <v>600</v>
       </c>
-      <c r="D110" t="s">
-        <v>601</v>
-      </c>
       <c r="E110" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F110" t="s">
         <v>49</v>
       </c>
       <c r="I110" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K110" t="s">
         <v>41</v>
@@ -8713,19 +8719,19 @@
         <v>22</v>
       </c>
       <c r="C111" t="s">
+        <v>602</v>
+      </c>
+      <c r="D111" t="s">
         <v>603</v>
       </c>
-      <c r="D111" t="s">
-        <v>604</v>
-      </c>
       <c r="E111" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F111" t="s">
         <v>49</v>
       </c>
       <c r="I111" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K111" t="s">
         <v>41</v>
@@ -8751,19 +8757,19 @@
         <v>22</v>
       </c>
       <c r="C112" t="s">
+        <v>605</v>
+      </c>
+      <c r="D112" t="s">
         <v>606</v>
       </c>
-      <c r="D112" t="s">
-        <v>607</v>
-      </c>
       <c r="E112" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F112" t="s">
         <v>49</v>
       </c>
       <c r="I112" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K112" t="s">
         <v>41</v>
@@ -8789,19 +8795,19 @@
         <v>22</v>
       </c>
       <c r="C113" t="s">
+        <v>608</v>
+      </c>
+      <c r="D113" t="s">
         <v>609</v>
       </c>
-      <c r="D113" t="s">
-        <v>610</v>
-      </c>
       <c r="E113" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F113" t="s">
         <v>49</v>
       </c>
       <c r="I113" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="K113" t="s">
         <v>41</v>
@@ -8827,31 +8833,31 @@
         <v>22</v>
       </c>
       <c r="C114" t="s">
+        <v>611</v>
+      </c>
+      <c r="D114" t="s">
         <v>612</v>
       </c>
-      <c r="D114" t="s">
-        <v>613</v>
-      </c>
       <c r="E114" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F114" t="s">
         <v>49</v>
       </c>
       <c r="I114" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K114" t="s">
+        <v>613</v>
+      </c>
+      <c r="L114" t="s">
         <v>614</v>
       </c>
-      <c r="L114" t="s">
+      <c r="M114" t="s">
         <v>615</v>
       </c>
-      <c r="M114" t="s">
+      <c r="N114" s="1" t="s">
         <v>616</v>
-      </c>
-      <c r="N114" s="1" t="s">
-        <v>617</v>
       </c>
       <c r="P114" t="s">
         <v>31</v>
@@ -8860,7 +8866,7 @@
         <v>82</v>
       </c>
       <c r="R114" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="U114" t="s">
         <v>34</v>
@@ -8883,19 +8889,19 @@
         <v>22</v>
       </c>
       <c r="C115" t="s">
+        <v>618</v>
+      </c>
+      <c r="D115" t="s">
         <v>619</v>
       </c>
-      <c r="D115" t="s">
-        <v>620</v>
-      </c>
       <c r="E115" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="F115" t="s">
         <v>49</v>
       </c>
       <c r="I115" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K115" t="s">
         <v>41</v>
@@ -8921,28 +8927,28 @@
         <v>22</v>
       </c>
       <c r="C116" t="s">
+        <v>620</v>
+      </c>
+      <c r="D116" t="s">
         <v>621</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>622</v>
-      </c>
-      <c r="E116" t="s">
-        <v>623</v>
       </c>
       <c r="F116" t="s">
         <v>49</v>
       </c>
       <c r="I116" t="s">
+        <v>623</v>
+      </c>
+      <c r="J116" s="1" t="s">
         <v>624</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>625</v>
       </c>
       <c r="K116" t="s">
         <v>41</v>
       </c>
       <c r="T116" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="U116" t="s">
         <v>89</v>
@@ -8965,22 +8971,22 @@
         <v>22</v>
       </c>
       <c r="C117" t="s">
+        <v>626</v>
+      </c>
+      <c r="D117" t="s">
         <v>627</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>628</v>
-      </c>
-      <c r="E117" t="s">
-        <v>629</v>
       </c>
       <c r="F117" t="s">
         <v>49</v>
       </c>
       <c r="I117" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K117" t="s">
         <v>41</v>
@@ -9006,22 +9012,22 @@
         <v>22</v>
       </c>
       <c r="C118" t="s">
+        <v>630</v>
+      </c>
+      <c r="D118" t="s">
         <v>631</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
         <v>632</v>
-      </c>
-      <c r="E118" t="s">
-        <v>633</v>
       </c>
       <c r="F118" t="s">
         <v>49</v>
       </c>
       <c r="I118" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="J118" s="1" t="s">
         <v>634</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>635</v>
       </c>
       <c r="K118" t="s">
         <v>41</v>
@@ -9047,34 +9053,34 @@
         <v>22</v>
       </c>
       <c r="C119" t="s">
+        <v>635</v>
+      </c>
+      <c r="D119" t="s">
         <v>636</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>637</v>
-      </c>
-      <c r="E119" t="s">
-        <v>638</v>
       </c>
       <c r="F119" t="s">
         <v>49</v>
       </c>
       <c r="I119" t="s">
+        <v>638</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="K119" t="s">
         <v>639</v>
       </c>
-      <c r="J119" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="K119" t="s">
+      <c r="L119" t="s">
         <v>640</v>
       </c>
-      <c r="L119" t="s">
+      <c r="M119" t="s">
         <v>641</v>
       </c>
-      <c r="M119" t="s">
+      <c r="N119" t="s">
         <v>642</v>
-      </c>
-      <c r="N119" t="s">
-        <v>643</v>
       </c>
       <c r="P119" t="s">
         <v>31</v>
@@ -9083,7 +9089,7 @@
         <v>32</v>
       </c>
       <c r="R119" s="1" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="U119" t="s">
         <v>34</v>
@@ -9095,7 +9101,7 @@
         <v>127</v>
       </c>
       <c r="X119" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="120" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -9106,34 +9112,34 @@
         <v>22</v>
       </c>
       <c r="C120" t="s">
+        <v>645</v>
+      </c>
+      <c r="D120" t="s">
         <v>646</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
         <v>647</v>
-      </c>
-      <c r="E120" t="s">
-        <v>648</v>
       </c>
       <c r="F120" t="s">
         <v>49</v>
       </c>
       <c r="I120" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="J120" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="K120" t="s">
         <v>649</v>
       </c>
-      <c r="J120" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="K120" t="s">
+      <c r="L120" t="s">
         <v>650</v>
       </c>
-      <c r="L120" t="s">
+      <c r="M120" t="s">
         <v>651</v>
       </c>
-      <c r="M120" t="s">
+      <c r="N120" t="s">
         <v>652</v>
-      </c>
-      <c r="N120" t="s">
-        <v>653</v>
       </c>
       <c r="P120" t="s">
         <v>31</v>
@@ -9142,10 +9148,10 @@
         <v>32</v>
       </c>
       <c r="R120" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="T120" t="s">
         <v>654</v>
-      </c>
-      <c r="T120" t="s">
-        <v>655</v>
       </c>
       <c r="U120" t="s">
         <v>34</v>
@@ -9157,7 +9163,7 @@
         <v>127</v>
       </c>
       <c r="X120" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="121" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
@@ -9168,19 +9174,19 @@
         <v>22</v>
       </c>
       <c r="C121" t="s">
+        <v>656</v>
+      </c>
+      <c r="D121" t="s">
         <v>657</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
         <v>658</v>
-      </c>
-      <c r="E121" t="s">
-        <v>659</v>
       </c>
       <c r="F121" t="s">
         <v>138</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="U121" t="s">
         <v>34</v>
@@ -9189,13 +9195,13 @@
         <v>42</v>
       </c>
       <c r="W121" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="X121" s="1" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="122" spans="1:24" ht="409.5" x14ac:dyDescent="0.25">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" ht="270" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -9203,22 +9209,22 @@
         <v>22</v>
       </c>
       <c r="C122" t="s">
+        <v>661</v>
+      </c>
+      <c r="D122" t="s">
+        <v>662</v>
+      </c>
+      <c r="E122" t="s">
         <v>663</v>
-      </c>
-      <c r="D122" t="s">
-        <v>664</v>
-      </c>
-      <c r="E122" t="s">
-        <v>665</v>
       </c>
       <c r="F122" t="s">
         <v>49</v>
       </c>
       <c r="G122" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="U122" t="s">
         <v>34</v>
@@ -9230,7 +9236,7 @@
         <v>61</v>
       </c>
       <c r="X122" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
   </sheetData>

--- a/baseline/data_processing_elements-FRA.xlsx
+++ b/baseline/data_processing_elements-FRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E32CC9-4B21-4B0E-B4D4-12415C205242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F9DE9E-7778-42D0-A571-A191D0FC2144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCDECE63-0FFC-4822-923F-34FACAF497E3}"/>
   </bookViews>
@@ -2508,14 +2508,14 @@
 med8atc1 != "X01"&amp;
 med9atc1 != "X01" &amp;
 !grepl("^C02|^C03|^C07|^C08|^C09", med1atc1, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc2, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc3, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc4, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc5, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc6, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc7, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc8, ignore.case = TRUE) &amp;
-!grepl("^C02|^C03|^C07|^C08|^C09", med1atc9, ignore.case = TRUE) ~ 0L;
+!grepl("^C02|^C03|^C07|^C08|^C09", med2atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med3atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med4atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med5atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med6atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med7atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med8atc1, ignore.case = TRUE) &amp;
+!grepl("^C02|^C03|^C07|^C08|^C09", med9atc1, ignore.case = TRUE) ~ 0L;
 is.na(hypertension1) &amp;
 med1atc1 != "X01" &amp;
 med2atc1 != "X01" &amp;

--- a/baseline/data_processing_elements-FRA.xlsx
+++ b/baseline/data_processing_elements-FRA.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF48816-2EFE-4463-8AC6-C514F138B51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CF1CCA-1863-4B33-A3BC-34CA21583BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCDECE63-0FFC-4822-923F-34FACAF497E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$Z$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1647,23 +1650,6 @@
   </si>
   <si>
     <t>items</t>
-  </si>
-  <si>
-    <t>rowSums(mutate(.,
-temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous1)), 
-temp_dis_moderate1 = as.numeric(!is.na(dis_moderate1)),
-temp_dis_lift1 = as.numeric(!is.na(dis_lift1)),
-temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral1)),
-temp_dis_climbone1 = as.numeric(!is.na(dis_climbone1)),
-temp_dis_bending1 = as.numeric(!is.na(dis_bending1)),
-temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_1)),
-temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_1)),
-temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_1)),
-temp_dis_bath1 = as.numeric(!is.na(dis_bath1))) %&gt;%
-select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
-temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE)) %&gt;%
-mutate(phy_SF36_nb_items = if_else(phy_SF36_nb_items == 0, NA, phy_SF36_nb_items)</t>
   </si>
   <si>
     <t>Mlstr_harmo::comment</t>
@@ -2770,6 +2756,36 @@
   </si>
   <si>
     <t>cog_mci_moca</t>
+  </si>
+  <si>
+    <t>ifelse( rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous1)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate1)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift1)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral1)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone1)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending1)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_1)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_1)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_1)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath1))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE)) == 0,NA,
+rowSums(mutate(.,
+temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous1)), 
+temp_dis_moderate1 = as.numeric(!is.na(dis_moderate1)),
+temp_dis_lift1 = as.numeric(!is.na(dis_lift1)),
+temp_dis_climbseveral1 = as.numeric(!is.na(dis_climbseveral1)),
+temp_dis_climbone1 = as.numeric(!is.na(dis_climbone1)),
+temp_dis_bending1 = as.numeric(!is.na(dis_bending1)),
+temp_dis_walk2km_1 = as.numeric(!is.na(dis_walk2km_1)),
+temp_dis_walk1km_1 = as.numeric(!is.na(dis_walk1km_1)),
+temp_dis_walk100m_1 = as.numeric(!is.na(dis_walk100m_1)),
+temp_dis_bath1 = as.numeric(!is.na(dis_bath1))) %&gt;%
+select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
+temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
+na.rm = TRUE)))</t>
   </si>
 </sst>
 </file>
@@ -3179,6 +3195,7 @@
     <col min="5" max="5" width="57.5703125" customWidth="1"/>
     <col min="10" max="10" width="48.7109375" customWidth="1"/>
     <col min="12" max="12" width="26.5703125" customWidth="1"/>
+    <col min="13" max="13" width="41.42578125" customWidth="1"/>
     <col min="26" max="26" width="89.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3241,10 +3258,10 @@
         <v>18</v>
       </c>
       <c r="V1" t="s">
+        <v>447</v>
+      </c>
+      <c r="W1" t="s">
         <v>448</v>
-      </c>
-      <c r="W1" t="s">
-        <v>449</v>
       </c>
       <c r="X1" t="s">
         <v>19</v>
@@ -3264,13 +3281,13 @@
         <v>22</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>23</v>
@@ -3279,7 +3296,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -3331,7 +3348,7 @@
         <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>23</v>
@@ -3340,7 +3357,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="3"/>
@@ -3357,7 +3374,7 @@
         <v>38</v>
       </c>
       <c r="Z3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="135" x14ac:dyDescent="0.25">
@@ -3374,7 +3391,7 @@
         <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>23</v>
@@ -3383,7 +3400,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="3"/>
@@ -3400,7 +3417,7 @@
         <v>38</v>
       </c>
       <c r="Z4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -3417,7 +3434,7 @@
         <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>43</v>
@@ -3426,7 +3443,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="3"/>
@@ -3457,7 +3474,7 @@
         <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>45</v>
@@ -3471,10 +3488,10 @@
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" t="s">
@@ -3536,7 +3553,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M7" t="s">
         <v>57</v>
@@ -3586,7 +3603,7 @@
         <v>64</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>43</v>
@@ -3597,10 +3614,10 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" t="s">
@@ -3645,13 +3662,13 @@
         <v>22</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>43</v>
@@ -3660,13 +3677,13 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="M9" t="s">
         <v>36</v>
@@ -3692,7 +3709,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>75</v>
@@ -3707,13 +3724,13 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>471</v>
-      </c>
       <c r="L10" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M10" t="s">
         <v>36</v>
@@ -3745,7 +3762,7 @@
         <v>78</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>43</v>
@@ -3753,16 +3770,16 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="L11" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M11" t="s">
         <v>36</v>
@@ -3791,10 +3808,10 @@
         <v>79</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>43</v>
@@ -3802,16 +3819,16 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="K12" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M12" t="s">
         <v>36</v>
@@ -3843,7 +3860,7 @@
         <v>81</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>43</v>
@@ -3851,16 +3868,16 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>484</v>
-      </c>
       <c r="K13" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M13" t="s">
         <v>36</v>
@@ -3892,7 +3909,7 @@
         <v>83</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>43</v>
@@ -3900,16 +3917,16 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>487</v>
-      </c>
       <c r="K14" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M14" t="s">
         <v>36</v>
@@ -3941,7 +3958,7 @@
         <v>85</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>43</v>
@@ -3949,16 +3966,16 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="K15" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M15" t="s">
         <v>36</v>
@@ -3990,7 +4007,7 @@
         <v>87</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>43</v>
@@ -3998,16 +4015,16 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="K16" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M16" t="s">
         <v>36</v>
@@ -4039,7 +4056,7 @@
         <v>89</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>43</v>
@@ -4047,16 +4064,16 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>496</v>
-      </c>
       <c r="K17" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M17" t="s">
         <v>36</v>
@@ -4085,10 +4102,10 @@
         <v>90</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>43</v>
@@ -4096,16 +4113,16 @@
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="K18" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M18" t="s">
         <v>36</v>
@@ -4134,10 +4151,10 @@
         <v>91</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>43</v>
@@ -4145,16 +4162,16 @@
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>505</v>
-      </c>
       <c r="L19" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M19" t="s">
         <v>36</v>
@@ -4186,7 +4203,7 @@
         <v>93</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>43</v>
@@ -4195,11 +4212,11 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="M20" t="s">
         <v>94</v>
@@ -4261,13 +4278,13 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="M21" t="s">
         <v>94</v>
@@ -4317,10 +4334,10 @@
         <v>107</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>108</v>
@@ -4422,7 +4439,7 @@
         <v>120</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>43</v>
@@ -4431,11 +4448,11 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M24" t="s">
         <v>94</v>
@@ -4485,7 +4502,7 @@
         <v>123</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>43</v>
@@ -4496,7 +4513,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="M25" t="s">
         <v>124</v>
@@ -4543,10 +4560,10 @@
         <v>130</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>43</v>
@@ -4555,13 +4572,13 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="K26" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="K26" s="2" t="s">
+      <c r="L26" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="M26" t="s">
         <v>36</v>
@@ -4587,10 +4604,10 @@
         <v>22</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>131</v>
@@ -4604,10 +4621,10 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" t="s">
@@ -4655,13 +4672,13 @@
         <v>22</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>43</v>
@@ -4672,7 +4689,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M28" t="s">
         <v>133</v>
@@ -4698,10 +4715,10 @@
         <v>22</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>139</v>
@@ -4715,10 +4732,10 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" t="s">
@@ -4766,13 +4783,13 @@
         <v>22</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>43</v>
@@ -4783,7 +4800,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M30" t="s">
         <v>141</v>
@@ -4809,13 +4826,13 @@
         <v>22</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>108</v>
@@ -4826,10 +4843,10 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="K31" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="L31" s="3"/>
       <c r="M31" t="s">
@@ -4877,13 +4894,13 @@
         <v>22</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>151</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>108</v>
@@ -4894,10 +4911,10 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="K32" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" t="s">
@@ -4945,13 +4962,13 @@
         <v>22</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>43</v>
@@ -4962,7 +4979,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M33" t="s">
         <v>152</v>
@@ -5006,13 +5023,13 @@
         <v>22</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>158</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>108</v>
@@ -5067,13 +5084,13 @@
         <v>22</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>23</v>
@@ -5111,13 +5128,13 @@
         <v>22</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>165</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>108</v>
@@ -5128,10 +5145,10 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="L36" s="3"/>
       <c r="M36" t="s">
@@ -5176,13 +5193,13 @@
         <v>22</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>172</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>108</v>
@@ -5193,10 +5210,10 @@
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="K37" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="L37" s="3"/>
       <c r="M37" t="s">
@@ -5241,13 +5258,13 @@
         <v>22</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>177</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>108</v>
@@ -5258,10 +5275,10 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L38" s="3"/>
       <c r="M38" t="s">
@@ -5288,13 +5305,13 @@
         <v>22</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>108</v>
@@ -5305,10 +5322,10 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="K39" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="L39" s="3"/>
       <c r="M39" t="s">
@@ -5362,10 +5379,10 @@
         <v>187</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>43</v>
@@ -5376,7 +5393,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="M40" t="s">
         <v>36</v>
@@ -5402,13 +5419,13 @@
         <v>22</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>108</v>
@@ -5445,13 +5462,13 @@
         <v>22</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>108</v>
@@ -5488,7 +5505,7 @@
         <v>22</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>190</v>
@@ -5543,10 +5560,10 @@
         <v>195</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>108</v>
@@ -5595,10 +5612,10 @@
         <v>200</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>108</v>
@@ -5647,10 +5664,10 @@
         <v>205</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>108</v>
@@ -5661,7 +5678,7 @@
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="K46" s="2"/>
       <c r="L46" s="3"/>
@@ -5692,7 +5709,7 @@
         <v>22</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>209</v>
@@ -5744,13 +5761,13 @@
         <v>22</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>108</v>
@@ -5799,10 +5816,10 @@
         <v>218</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>108</v>
@@ -5813,10 +5830,10 @@
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="K49" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="L49" s="3"/>
       <c r="M49" t="s">
@@ -5846,10 +5863,10 @@
         <v>220</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>43</v>
@@ -5859,10 +5876,10 @@
       <c r="I50" s="3"/>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="L50" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="M50" t="s">
         <v>36</v>
@@ -5891,10 +5908,10 @@
         <v>221</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>108</v>
@@ -5905,10 +5922,10 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s">
@@ -5938,10 +5955,10 @@
         <v>222</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>43</v>
@@ -5950,13 +5967,13 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="K52" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>566</v>
-      </c>
       <c r="L52" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="M52" t="s">
         <v>223</v>
@@ -5997,7 +6014,7 @@
         <v>22</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>229</v>
@@ -6043,10 +6060,10 @@
         <v>231</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>108</v>
@@ -6057,10 +6074,10 @@
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="K54" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>569</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s">
@@ -6102,10 +6119,10 @@
         <v>237</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>43</v>
@@ -6116,7 +6133,7 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="M55" t="s">
         <v>36</v>
@@ -6157,13 +6174,13 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="K56" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="L56" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="L56" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="M56" t="s">
         <v>240</v>
@@ -6223,10 +6240,10 @@
       <c r="I57" s="3"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="M57" t="s">
         <v>36</v>
@@ -6273,10 +6290,10 @@
         <v>248</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>108</v>
@@ -6287,10 +6304,10 @@
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s">
@@ -6396,11 +6413,11 @@
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K60" s="2"/>
       <c r="L60" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M60" t="s">
         <v>252</v>
@@ -6447,10 +6464,10 @@
         <v>263</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>581</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>43</v>
@@ -6460,10 +6477,10 @@
       <c r="I61" s="3"/>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="L61" s="2" t="s">
         <v>582</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>583</v>
       </c>
       <c r="M61" t="s">
         <v>264</v>
@@ -6507,7 +6524,7 @@
         <v>22</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>270</v>
@@ -6526,7 +6543,7 @@
       </c>
       <c r="K62" s="2"/>
       <c r="L62" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M62" t="s">
         <v>36</v>
@@ -6552,13 +6569,13 @@
         <v>22</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>43</v>
@@ -6569,7 +6586,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
       <c r="L63" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M63" t="s">
         <v>272</v>
@@ -6616,13 +6633,13 @@
         <v>22</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>43</v>
@@ -6633,7 +6650,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
       <c r="L64" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M64" t="s">
         <v>36</v>
@@ -6659,13 +6676,13 @@
         <v>22</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>43</v>
@@ -6676,7 +6693,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
       <c r="L65" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="M65" t="s">
         <v>280</v>
@@ -6726,7 +6743,7 @@
         <v>286</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>287</v>
@@ -6742,7 +6759,7 @@
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M66" t="s">
         <v>36</v>
@@ -6771,7 +6788,7 @@
         <v>288</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>289</v>
@@ -6787,7 +6804,7 @@
       </c>
       <c r="K67" s="2"/>
       <c r="L67" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M67" t="s">
         <v>36</v>
@@ -6813,13 +6830,13 @@
         <v>22</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>108</v>
@@ -6879,13 +6896,13 @@
         <v>22</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>296</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>43</v>
@@ -6896,7 +6913,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
       <c r="L69" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="M69" t="s">
         <v>290</v>
@@ -6943,13 +6960,13 @@
         <v>22</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>596</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>43</v>
@@ -6959,10 +6976,10 @@
       <c r="I70" s="3"/>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="L70" s="2" t="s">
         <v>597</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>598</v>
       </c>
       <c r="M70" t="s">
         <v>36</v>
@@ -6991,7 +7008,7 @@
         <v>22</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>426</v>
@@ -7007,10 +7024,10 @@
       <c r="I71" s="3"/>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="M71" t="s">
         <v>36</v>
@@ -7036,13 +7053,13 @@
         <v>22</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>428</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>43</v>
@@ -7051,13 +7068,13 @@
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M72" t="s">
         <v>36</v>
@@ -7083,13 +7100,13 @@
         <v>22</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>429</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>43</v>
@@ -7098,11 +7115,11 @@
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
       <c r="J73" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K73" s="2"/>
       <c r="L73" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M73" t="s">
         <v>430</v>
@@ -7146,13 +7163,13 @@
         <v>22</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>436</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>43</v>
@@ -7161,13 +7178,13 @@
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="2" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M74" t="s">
         <v>437</v>
@@ -7214,13 +7231,13 @@
         <v>22</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>108</v>
@@ -7229,7 +7246,7 @@
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
@@ -7246,10 +7263,10 @@
         <v>445</v>
       </c>
       <c r="Z75" s="1" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="76" spans="1:26" ht="270" x14ac:dyDescent="0.25">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7257,13 +7274,13 @@
         <v>22</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D76" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>43</v>
@@ -7289,7 +7306,7 @@
         <v>52</v>
       </c>
       <c r="Z76" s="1" t="s">
-        <v>447</v>
+        <v>749</v>
       </c>
     </row>
     <row r="77" spans="1:26" ht="390" x14ac:dyDescent="0.25">
@@ -7316,10 +7333,10 @@
       <c r="I77" s="3"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="L77" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="L77" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="M77" t="s">
         <v>301</v>
@@ -7369,10 +7386,10 @@
         <v>307</v>
       </c>
       <c r="D78" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>614</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>43</v>
@@ -7381,13 +7398,13 @@
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
       <c r="J78" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="K78" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="K78" s="2" t="s">
+      <c r="L78" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="L78" s="2" t="s">
-        <v>617</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>308</v>
@@ -7437,10 +7454,10 @@
         <v>316</v>
       </c>
       <c r="D79" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>618</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>619</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>43</v>
@@ -7448,14 +7465,14 @@
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="J79" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="J79" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="K79" s="2"/>
       <c r="L79" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M79" t="s">
         <v>317</v>
@@ -7505,10 +7522,10 @@
         <v>322</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>622</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>623</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>43</v>
@@ -7516,14 +7533,14 @@
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="K80" s="2"/>
       <c r="L80" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M80" t="s">
         <v>317</v>
@@ -7570,10 +7587,10 @@
         <v>325</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E81" s="3" t="s">
         <v>625</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>626</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>43</v>
@@ -7581,14 +7598,14 @@
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
       <c r="I81" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="K81" s="2"/>
       <c r="L81" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M81" t="s">
         <v>326</v>
@@ -7635,10 +7652,10 @@
         <v>329</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>628</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>629</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>43</v>
@@ -7646,14 +7663,14 @@
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
       <c r="I82" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="K82" s="2"/>
       <c r="L82" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M82" t="s">
         <v>330</v>
@@ -7697,13 +7714,13 @@
         <v>22</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D83" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>631</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>632</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>43</v>
@@ -7711,14 +7728,14 @@
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="K83" s="2"/>
       <c r="L83" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M83" t="s">
         <v>36</v>
@@ -7762,13 +7779,13 @@
         <v>22</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D84" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>634</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>635</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>43</v>
@@ -7776,14 +7793,14 @@
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="K84" s="2"/>
       <c r="L84" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M84" t="s">
         <v>36</v>
@@ -7830,10 +7847,10 @@
         <v>333</v>
       </c>
       <c r="D85" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>637</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>638</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>43</v>
@@ -7841,16 +7858,16 @@
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
       <c r="I85" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="J85" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="J85" s="2" t="s">
+      <c r="K85" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="K85" s="2" t="s">
-        <v>641</v>
-      </c>
       <c r="L85" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M85" t="s">
         <v>334</v>
@@ -7897,10 +7914,10 @@
         <v>337</v>
       </c>
       <c r="D86" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>642</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>643</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>43</v>
@@ -7908,14 +7925,14 @@
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="5" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="K86" s="4"/>
       <c r="L86" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>338</v>
@@ -7948,7 +7965,7 @@
         <v>298</v>
       </c>
       <c r="Z86" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="87" spans="1:26" ht="409.5" x14ac:dyDescent="0.25">
@@ -7962,10 +7979,10 @@
         <v>339</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>43</v>
@@ -7974,11 +7991,11 @@
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
       <c r="J87" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="K87" s="2"/>
       <c r="L87" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>340</v>
@@ -8022,13 +8039,13 @@
         <v>22</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D88" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>43</v>
@@ -8036,16 +8053,16 @@
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
       <c r="I88" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="K88" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="J88" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>651</v>
-      </c>
       <c r="L88" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M88" t="s">
         <v>346</v>
@@ -8108,10 +8125,10 @@
       <c r="I89" s="3"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="L89" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="M89" t="s">
         <v>346</v>
@@ -8164,7 +8181,7 @@
         <v>354</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>43</v>
@@ -8173,13 +8190,13 @@
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="K90" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="K90" s="2" t="s">
-        <v>656</v>
-      </c>
       <c r="L90" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M90" t="s">
         <v>355</v>
@@ -8229,7 +8246,7 @@
         <v>359</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>43</v>
@@ -8238,11 +8255,11 @@
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
       <c r="J91" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K91" s="2"/>
       <c r="L91" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M91" t="s">
         <v>355</v>
@@ -8292,7 +8309,7 @@
         <v>362</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>43</v>
@@ -8301,11 +8318,11 @@
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
       <c r="J92" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K92" s="2"/>
       <c r="L92" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M92" t="s">
         <v>355</v>
@@ -8355,7 +8372,7 @@
         <v>364</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>43</v>
@@ -8364,11 +8381,11 @@
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
       <c r="J93" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K93" s="2"/>
       <c r="L93" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M93" t="s">
         <v>355</v>
@@ -8415,10 +8432,10 @@
         <v>365</v>
       </c>
       <c r="D94" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>43</v>
@@ -8427,11 +8444,11 @@
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
       <c r="J94" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K94" s="2"/>
       <c r="L94" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M94" t="s">
         <v>355</v>
@@ -8481,7 +8498,7 @@
         <v>367</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>43</v>
@@ -8490,11 +8507,11 @@
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K95" s="2"/>
       <c r="L95" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M95" t="s">
         <v>355</v>
@@ -8541,10 +8558,10 @@
         <v>368</v>
       </c>
       <c r="D96" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>664</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>665</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>43</v>
@@ -8553,11 +8570,11 @@
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
       <c r="J96" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K96" s="2"/>
       <c r="L96" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M96" t="s">
         <v>355</v>
@@ -8607,7 +8624,7 @@
         <v>370</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>43</v>
@@ -8616,11 +8633,11 @@
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
       <c r="J97" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K97" s="2"/>
       <c r="L97" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M97" t="s">
         <v>355</v>
@@ -8670,7 +8687,7 @@
         <v>372</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>43</v>
@@ -8679,11 +8696,11 @@
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
       <c r="J98" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K98" s="2"/>
       <c r="L98" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M98" t="s">
         <v>355</v>
@@ -8733,7 +8750,7 @@
         <v>374</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>43</v>
@@ -8742,11 +8759,11 @@
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
       <c r="J99" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K99" s="2"/>
       <c r="L99" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M99" t="s">
         <v>355</v>
@@ -8796,7 +8813,7 @@
         <v>376</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>43</v>
@@ -8805,11 +8822,11 @@
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
       <c r="J100" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K100" s="2"/>
       <c r="L100" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M100" t="s">
         <v>355</v>
@@ -8859,7 +8876,7 @@
         <v>378</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>43</v>
@@ -8868,11 +8885,11 @@
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>
       <c r="J101" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K101" s="2"/>
       <c r="L101" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M101" t="s">
         <v>355</v>
@@ -8922,7 +8939,7 @@
         <v>380</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>43</v>
@@ -8931,11 +8948,11 @@
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
       <c r="J102" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K102" s="2"/>
       <c r="L102" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M102" t="s">
         <v>355</v>
@@ -8985,7 +9002,7 @@
         <v>382</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>43</v>
@@ -8994,11 +9011,11 @@
       <c r="H103" s="3"/>
       <c r="I103" s="3"/>
       <c r="J103" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K103" s="2"/>
       <c r="L103" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M103" t="s">
         <v>355</v>
@@ -9048,7 +9065,7 @@
         <v>384</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>43</v>
@@ -9057,11 +9074,11 @@
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
       <c r="J104" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K104" s="2"/>
       <c r="L104" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M104" t="s">
         <v>355</v>
@@ -9111,7 +9128,7 @@
         <v>386</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>43</v>
@@ -9120,11 +9137,11 @@
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
       <c r="J105" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K105" s="2"/>
       <c r="L105" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M105" t="s">
         <v>355</v>
@@ -9174,7 +9191,7 @@
         <v>388</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>43</v>
@@ -9183,11 +9200,11 @@
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
       <c r="J106" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K106" s="2"/>
       <c r="L106" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M106" t="s">
         <v>355</v>
@@ -9237,7 +9254,7 @@
         <v>390</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>43</v>
@@ -9246,11 +9263,11 @@
       <c r="H107" s="3"/>
       <c r="I107" s="3"/>
       <c r="J107" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K107" s="2"/>
       <c r="L107" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M107" t="s">
         <v>355</v>
@@ -9300,7 +9317,7 @@
         <v>392</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>43</v>
@@ -9309,11 +9326,11 @@
       <c r="H108" s="3"/>
       <c r="I108" s="3"/>
       <c r="J108" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K108" s="2"/>
       <c r="L108" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M108" t="s">
         <v>355</v>
@@ -9363,7 +9380,7 @@
         <v>394</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>43</v>
@@ -9372,11 +9389,11 @@
       <c r="H109" s="3"/>
       <c r="I109" s="3"/>
       <c r="J109" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="K109" s="2"/>
       <c r="L109" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M109" t="s">
         <v>355</v>
@@ -9420,13 +9437,13 @@
         <v>22</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D110" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>43</v>
@@ -9435,11 +9452,11 @@
       <c r="H110" s="3"/>
       <c r="I110" s="3"/>
       <c r="J110" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M110" t="s">
         <v>395</v>
@@ -9489,7 +9506,7 @@
         <v>399</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>43</v>
@@ -9498,11 +9515,11 @@
       <c r="H111" s="3"/>
       <c r="I111" s="3"/>
       <c r="J111" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K111" s="2"/>
       <c r="L111" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M111" t="s">
         <v>400</v>
@@ -9549,10 +9566,10 @@
         <v>404</v>
       </c>
       <c r="D112" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>43</v>
@@ -9561,11 +9578,11 @@
       <c r="H112" s="3"/>
       <c r="I112" s="3"/>
       <c r="J112" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M112" t="s">
         <v>405</v>
@@ -9609,13 +9626,13 @@
         <v>22</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>43</v>
@@ -9624,11 +9641,11 @@
       <c r="H113" s="3"/>
       <c r="I113" s="3"/>
       <c r="J113" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="K113" s="2"/>
       <c r="L113" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>409</v>
@@ -9675,7 +9692,7 @@
         <v>22</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>416</v>
@@ -9690,11 +9707,11 @@
       <c r="H114" s="3"/>
       <c r="I114" s="3"/>
       <c r="J114" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>409</v>
@@ -9741,7 +9758,7 @@
         <v>22</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>418</v>
@@ -9756,11 +9773,11 @@
       <c r="H115" s="3"/>
       <c r="I115" s="3"/>
       <c r="J115" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="K115" s="2"/>
       <c r="L115" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="M115" s="1" t="s">
         <v>409</v>
@@ -9807,13 +9824,13 @@
         <v>22</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>43</v>
@@ -9822,7 +9839,7 @@
       <c r="H116" s="3"/>
       <c r="I116" s="3"/>
       <c r="J116" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
@@ -9850,13 +9867,13 @@
         <v>22</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>43</v>
@@ -9865,7 +9882,7 @@
       <c r="H117" s="3"/>
       <c r="I117" s="3"/>
       <c r="J117" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
@@ -9893,13 +9910,13 @@
         <v>22</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>43</v>
@@ -9908,7 +9925,7 @@
       <c r="H118" s="3"/>
       <c r="I118" s="3"/>
       <c r="J118" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
@@ -9936,13 +9953,13 @@
         <v>22</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>43</v>
@@ -9951,7 +9968,7 @@
       <c r="H119" s="3"/>
       <c r="I119" s="3"/>
       <c r="J119" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
@@ -9979,13 +9996,13 @@
         <v>22</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>43</v>
@@ -9994,7 +10011,7 @@
       <c r="H120" s="3"/>
       <c r="I120" s="3"/>
       <c r="J120" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
@@ -10022,13 +10039,13 @@
         <v>22</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>43</v>
@@ -10037,7 +10054,7 @@
       <c r="H121" s="3"/>
       <c r="I121" s="3"/>
       <c r="J121" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
@@ -10083,13 +10100,13 @@
         <v>22</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>43</v>
@@ -10098,7 +10115,7 @@
       <c r="H122" s="3"/>
       <c r="I122" s="3"/>
       <c r="J122" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
@@ -10119,6 +10136,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:Z1" xr:uid="{5DD590CF-60F3-474A-8CF6-CAFB2AFA3E98}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/baseline/data_processing_elements-FRA.xlsx
+++ b/baseline/data_processing_elements-FRA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sam\Documents\Boulot\ProPASS\FRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CF1CCA-1863-4B33-A3BC-34CA21583BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8FA2F2-0CDC-4190-908B-16CDF1F89BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CCDECE63-0FFC-4822-923F-34FACAF497E3}"/>
   </bookViews>
@@ -2771,7 +2771,7 @@
 temp_dis_bath1 = as.numeric(!is.na(dis_bath1))) %&gt;%
 select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
 temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE)) == 0,NA,
+na.rm = TRUE) == 0,NA,
 rowSums(mutate(.,
 temp_dis_vigorous1 = as.numeric(!is.na(dis_vigorous1)), 
 temp_dis_moderate1 = as.numeric(!is.na(dis_moderate1)),
@@ -2785,7 +2785,7 @@
 temp_dis_bath1 = as.numeric(!is.na(dis_bath1))) %&gt;%
 select(temp_dis_vigorous1, temp_dis_moderate1, temp_dis_lift1, temp_dis_climbseveral1, temp_dis_climbone1,
 temp_dis_bending1, temp_dis_walk2km_1, temp_dis_walk1km_1, temp_dis_walk100m_1, temp_dis_bath1), 
-na.rm = TRUE)))</t>
+na.rm = TRUE))</t>
   </si>
 </sst>
 </file>
